--- a/0.xlsx
+++ b/0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a1f3150794129c75/Desktop/DIEM/BAO CAO EP NHUA/AI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="113" documentId="8_{C0AD0CA2-3160-44B1-8883-3FEEB7EB92A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E1D65464-4673-434A-972E-8DE46B9CE91A}"/>
+  <xr:revisionPtr revIDLastSave="133" documentId="8_{F252333F-CA7E-4291-8506-546ADA766E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3A923B67-4461-4953-96C4-5B59C9ACE7C4}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1234" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1394" uniqueCount="106">
   <si>
     <t>작업조</t>
   </si>
@@ -313,9 +313,6 @@
     <t>NGUYỄN NGỌC SƠN</t>
   </si>
   <si>
-    <t xml:space="preserve">TRẦN VĂN NHƠN    </t>
-  </si>
-  <si>
     <t>← 해당 색상 서식 외에는 절대 수정하지 마십시오.</t>
   </si>
   <si>
@@ -401,6 +398,12 @@
   <si>
     <t>B조
 (NGỌC)</t>
+  </si>
+  <si>
+    <t>NGUYỄN THANH VŨ</t>
+  </si>
+  <si>
+    <t>ĐẶNG THANH PHONG</t>
   </si>
 </sst>
 </file>
@@ -1650,7 +1653,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:AU160"/>
+  <dimension ref="B1:AU184"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="4.140625" style="1" customWidth="1"/>
@@ -1752,7 +1755,7 @@
     </row>
     <row r="4" spans="2:47" ht="22.5">
       <c r="B4" s="58" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C4" s="58"/>
       <c r="D4" s="58"/>
@@ -1855,7 +1858,7 @@
         <v>13</v>
       </c>
       <c r="D6" s="89" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E6" s="87"/>
       <c r="F6" s="87"/>
@@ -1865,10 +1868,10 @@
       <c r="J6" s="87"/>
       <c r="K6" s="47"/>
       <c r="L6" s="48" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="M6" s="86" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="N6" s="87"/>
       <c r="O6" s="87"/>
@@ -1910,7 +1913,7 @@
     <row r="7" spans="2:47" ht="24.95" customHeight="1">
       <c r="C7" s="3"/>
       <c r="D7" s="88" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E7" s="88"/>
       <c r="F7" s="88"/>
@@ -1921,7 +1924,7 @@
       <c r="K7" s="88"/>
       <c r="L7" s="3"/>
       <c r="M7" s="88" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N7" s="88"/>
       <c r="O7" s="88"/>
@@ -1959,7 +1962,7 @@
     </row>
     <row r="8" spans="2:47" ht="22.5">
       <c r="B8" s="57" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C8" s="58"/>
       <c r="D8" s="58"/>
@@ -2127,10 +2130,10 @@
         <v>81</v>
       </c>
       <c r="K11" s="31" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="L11" s="31" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="M11" s="31"/>
       <c r="N11" s="31"/>
@@ -2186,7 +2189,7 @@
     </row>
     <row r="13" spans="2:47" ht="54.6" customHeight="1">
       <c r="B13" s="90" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C13" s="90"/>
       <c r="D13" s="90"/>
@@ -2253,7 +2256,7 @@
         <v>73</v>
       </c>
       <c r="S14" s="56" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="T14" s="56"/>
       <c r="U14" s="56"/>
@@ -2356,7 +2359,7 @@
       </c>
       <c r="D17" s="51"/>
       <c r="E17" s="59" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F17" s="5">
         <v>0.41666666666666669</v>
@@ -2598,7 +2601,7 @@
       </c>
       <c r="V22" s="4"/>
       <c r="X22" s="54" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="Z22" s="44" t="s">
         <v>46</v>
@@ -2609,7 +2612,7 @@
       <c r="C23" s="63"/>
       <c r="D23" s="51"/>
       <c r="E23" s="59" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F23" s="5">
         <v>0.91666666666666663</v>
@@ -2642,7 +2645,7 @@
       </c>
       <c r="V23" s="4"/>
       <c r="X23" s="54" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="Z23" s="44" t="s">
         <v>45</v>
@@ -2858,10 +2861,10 @@
         <v>14</v>
       </c>
       <c r="D29" s="51" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E29" s="59" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F29" s="5">
         <v>0.41666666666666669</v>
@@ -2914,7 +2917,7 @@
       <c r="B30" s="76"/>
       <c r="C30" s="63"/>
       <c r="D30" s="52" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E30" s="60"/>
       <c r="F30" s="8">
@@ -2964,7 +2967,7 @@
       <c r="B31" s="76"/>
       <c r="C31" s="63"/>
       <c r="D31" s="52" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E31" s="60"/>
       <c r="F31" s="8">
@@ -3014,7 +3017,7 @@
       <c r="B32" s="76"/>
       <c r="C32" s="63"/>
       <c r="D32" s="52" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E32" s="60"/>
       <c r="F32" s="8">
@@ -3062,7 +3065,7 @@
       <c r="B33" s="76"/>
       <c r="C33" s="63"/>
       <c r="D33" s="52" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E33" s="60"/>
       <c r="F33" s="8">
@@ -3112,7 +3115,7 @@
       <c r="B34" s="76"/>
       <c r="C34" s="63"/>
       <c r="D34" s="53" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E34" s="61"/>
       <c r="F34" s="12">
@@ -3158,10 +3161,10 @@
       <c r="B35" s="76"/>
       <c r="C35" s="63"/>
       <c r="D35" s="51" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E35" s="59" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F35" s="5">
         <v>0.91666666666666663</v>
@@ -3212,7 +3215,7 @@
       <c r="B36" s="76"/>
       <c r="C36" s="63"/>
       <c r="D36" s="52" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E36" s="60"/>
       <c r="F36" s="8">
@@ -3258,7 +3261,7 @@
       <c r="B37" s="76"/>
       <c r="C37" s="63"/>
       <c r="D37" s="52" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E37" s="60"/>
       <c r="F37" s="8">
@@ -3304,7 +3307,7 @@
       <c r="B38" s="76"/>
       <c r="C38" s="63"/>
       <c r="D38" s="52" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E38" s="60"/>
       <c r="F38" s="8">
@@ -3352,7 +3355,7 @@
       <c r="B39" s="76"/>
       <c r="C39" s="63"/>
       <c r="D39" s="52" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E39" s="60"/>
       <c r="F39" s="8">
@@ -3398,7 +3401,7 @@
       <c r="B40" s="77"/>
       <c r="C40" s="64"/>
       <c r="D40" s="53" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E40" s="61"/>
       <c r="F40" s="12">
@@ -3450,10 +3453,10 @@
         <v>14</v>
       </c>
       <c r="D41" s="51" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E41" s="59" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F41" s="5">
         <v>0.41666666666666669</v>
@@ -3502,7 +3505,7 @@
       <c r="B42" s="76"/>
       <c r="C42" s="63"/>
       <c r="D42" s="52" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E42" s="60"/>
       <c r="F42" s="8">
@@ -3552,7 +3555,7 @@
       <c r="B43" s="76"/>
       <c r="C43" s="63"/>
       <c r="D43" s="52" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E43" s="60"/>
       <c r="F43" s="8">
@@ -3602,7 +3605,7 @@
       <c r="B44" s="76"/>
       <c r="C44" s="63"/>
       <c r="D44" s="52" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E44" s="60"/>
       <c r="F44" s="8">
@@ -3652,7 +3655,7 @@
       <c r="B45" s="76"/>
       <c r="C45" s="63"/>
       <c r="D45" s="52" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E45" s="60"/>
       <c r="F45" s="8">
@@ -3700,7 +3703,7 @@
       <c r="B46" s="76"/>
       <c r="C46" s="63"/>
       <c r="D46" s="53" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E46" s="61"/>
       <c r="F46" s="12">
@@ -3746,10 +3749,10 @@
       <c r="B47" s="76"/>
       <c r="C47" s="63"/>
       <c r="D47" s="51" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E47" s="59" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F47" s="5">
         <v>0.91666666666666663</v>
@@ -3794,7 +3797,7 @@
       <c r="B48" s="76"/>
       <c r="C48" s="63"/>
       <c r="D48" s="52" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E48" s="60"/>
       <c r="F48" s="8">
@@ -3838,7 +3841,7 @@
       <c r="B49" s="76"/>
       <c r="C49" s="63"/>
       <c r="D49" s="52" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E49" s="60"/>
       <c r="F49" s="8">
@@ -3884,7 +3887,7 @@
       <c r="B50" s="76"/>
       <c r="C50" s="63"/>
       <c r="D50" s="52" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E50" s="60"/>
       <c r="F50" s="8">
@@ -3932,7 +3935,7 @@
       <c r="B51" s="76"/>
       <c r="C51" s="63"/>
       <c r="D51" s="52" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E51" s="60"/>
       <c r="F51" s="8">
@@ -3978,7 +3981,7 @@
       <c r="B52" s="76"/>
       <c r="C52" s="63"/>
       <c r="D52" s="53" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E52" s="61"/>
       <c r="F52" s="12">
@@ -4030,10 +4033,10 @@
         <v>14</v>
       </c>
       <c r="D53" s="51" t="s">
+        <v>101</v>
+      </c>
+      <c r="E53" s="59" t="s">
         <v>102</v>
-      </c>
-      <c r="E53" s="59" t="s">
-        <v>103</v>
       </c>
       <c r="F53" s="5">
         <v>0.41666666666666669</v>
@@ -4078,7 +4081,7 @@
       <c r="B54" s="65"/>
       <c r="C54" s="63"/>
       <c r="D54" s="52" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E54" s="60"/>
       <c r="F54" s="8">
@@ -4128,7 +4131,7 @@
       <c r="B55" s="65"/>
       <c r="C55" s="63"/>
       <c r="D55" s="52" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E55" s="60"/>
       <c r="F55" s="8">
@@ -4174,7 +4177,7 @@
       <c r="B56" s="65"/>
       <c r="C56" s="63"/>
       <c r="D56" s="52" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E56" s="60"/>
       <c r="F56" s="8">
@@ -4220,7 +4223,7 @@
       <c r="B57" s="65"/>
       <c r="C57" s="63"/>
       <c r="D57" s="52" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E57" s="60"/>
       <c r="F57" s="8">
@@ -4266,7 +4269,7 @@
       <c r="B58" s="65"/>
       <c r="C58" s="63"/>
       <c r="D58" s="53" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E58" s="61"/>
       <c r="F58" s="12">
@@ -4310,10 +4313,10 @@
       <c r="B59" s="65"/>
       <c r="C59" s="63"/>
       <c r="D59" s="51" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E59" s="59" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F59" s="5">
         <v>0.91666666666666663</v>
@@ -4358,7 +4361,7 @@
       <c r="B60" s="65"/>
       <c r="C60" s="63"/>
       <c r="D60" s="52" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E60" s="60"/>
       <c r="F60" s="8">
@@ -4404,7 +4407,7 @@
       <c r="B61" s="65"/>
       <c r="C61" s="63"/>
       <c r="D61" s="52" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E61" s="60"/>
       <c r="F61" s="8">
@@ -4450,7 +4453,7 @@
       <c r="B62" s="65"/>
       <c r="C62" s="63"/>
       <c r="D62" s="52" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E62" s="60"/>
       <c r="F62" s="8">
@@ -4497,7 +4500,7 @@
       <c r="B63" s="65"/>
       <c r="C63" s="63"/>
       <c r="D63" s="52" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E63" s="60"/>
       <c r="F63" s="8">
@@ -4542,7 +4545,7 @@
       <c r="B64" s="65"/>
       <c r="C64" s="64"/>
       <c r="D64" s="53" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E64" s="61"/>
       <c r="F64" s="14">
@@ -4593,10 +4596,10 @@
         <v>14</v>
       </c>
       <c r="D65" s="51" t="s">
+        <v>101</v>
+      </c>
+      <c r="E65" s="59" t="s">
         <v>102</v>
-      </c>
-      <c r="E65" s="59" t="s">
-        <v>103</v>
       </c>
       <c r="F65" s="5">
         <v>0.41666666666666669</v>
@@ -4640,7 +4643,7 @@
       <c r="B66" s="65"/>
       <c r="C66" s="63"/>
       <c r="D66" s="52" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E66" s="60"/>
       <c r="F66" s="8">
@@ -4685,7 +4688,7 @@
       <c r="B67" s="65"/>
       <c r="C67" s="63"/>
       <c r="D67" s="52" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E67" s="60"/>
       <c r="F67" s="8">
@@ -4730,7 +4733,7 @@
       <c r="B68" s="65"/>
       <c r="C68" s="63"/>
       <c r="D68" s="52" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E68" s="60"/>
       <c r="F68" s="8">
@@ -4775,7 +4778,7 @@
       <c r="B69" s="65"/>
       <c r="C69" s="63"/>
       <c r="D69" s="52" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E69" s="60"/>
       <c r="F69" s="8">
@@ -4822,7 +4825,7 @@
       <c r="B70" s="65"/>
       <c r="C70" s="63"/>
       <c r="D70" s="53" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E70" s="61"/>
       <c r="F70" s="12">
@@ -4865,10 +4868,10 @@
       <c r="B71" s="65"/>
       <c r="C71" s="63"/>
       <c r="D71" s="51" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E71" s="59" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F71" s="5">
         <v>0.91666666666666663</v>
@@ -4912,7 +4915,7 @@
       <c r="B72" s="65"/>
       <c r="C72" s="63"/>
       <c r="D72" s="52" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E72" s="60"/>
       <c r="F72" s="8">
@@ -4957,7 +4960,7 @@
       <c r="B73" s="65"/>
       <c r="C73" s="63"/>
       <c r="D73" s="52" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E73" s="60"/>
       <c r="F73" s="8">
@@ -5000,7 +5003,7 @@
       <c r="B74" s="65"/>
       <c r="C74" s="63"/>
       <c r="D74" s="52" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E74" s="60"/>
       <c r="F74" s="8">
@@ -5045,7 +5048,7 @@
       <c r="B75" s="65"/>
       <c r="C75" s="63"/>
       <c r="D75" s="52" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E75" s="60"/>
       <c r="F75" s="8">
@@ -5088,7 +5091,7 @@
       <c r="B76" s="65"/>
       <c r="C76" s="64"/>
       <c r="D76" s="53" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E76" s="61"/>
       <c r="F76" s="14">
@@ -5135,10 +5138,10 @@
         <v>14</v>
       </c>
       <c r="D77" s="51" t="s">
+        <v>101</v>
+      </c>
+      <c r="E77" s="59" t="s">
         <v>102</v>
-      </c>
-      <c r="E77" s="59" t="s">
-        <v>103</v>
       </c>
       <c r="F77" s="5">
         <v>0.41666666666666669</v>
@@ -5182,7 +5185,7 @@
       <c r="B78" s="65"/>
       <c r="C78" s="63"/>
       <c r="D78" s="52" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E78" s="60"/>
       <c r="F78" s="8">
@@ -5229,7 +5232,7 @@
       <c r="B79" s="65"/>
       <c r="C79" s="63"/>
       <c r="D79" s="52" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E79" s="60"/>
       <c r="F79" s="8">
@@ -5274,7 +5277,7 @@
       <c r="B80" s="65"/>
       <c r="C80" s="63"/>
       <c r="D80" s="52" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E80" s="60"/>
       <c r="F80" s="8">
@@ -5319,7 +5322,7 @@
       <c r="B81" s="65"/>
       <c r="C81" s="63"/>
       <c r="D81" s="52" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E81" s="60"/>
       <c r="F81" s="8">
@@ -5366,7 +5369,7 @@
       <c r="B82" s="65"/>
       <c r="C82" s="63"/>
       <c r="D82" s="53" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E82" s="61"/>
       <c r="F82" s="12">
@@ -5409,10 +5412,10 @@
       <c r="B83" s="65"/>
       <c r="C83" s="63"/>
       <c r="D83" s="51" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E83" s="59" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F83" s="5">
         <v>0.91666666666666663</v>
@@ -5456,7 +5459,7 @@
       <c r="B84" s="65"/>
       <c r="C84" s="63"/>
       <c r="D84" s="52" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E84" s="60"/>
       <c r="F84" s="8">
@@ -5501,7 +5504,7 @@
       <c r="B85" s="65"/>
       <c r="C85" s="63"/>
       <c r="D85" s="52" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E85" s="60"/>
       <c r="F85" s="8">
@@ -5546,7 +5549,7 @@
       <c r="B86" s="65"/>
       <c r="C86" s="63"/>
       <c r="D86" s="52" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E86" s="60"/>
       <c r="F86" s="8">
@@ -5591,7 +5594,7 @@
       <c r="B87" s="65"/>
       <c r="C87" s="63"/>
       <c r="D87" s="52" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E87" s="60"/>
       <c r="F87" s="8">
@@ -5634,7 +5637,7 @@
       <c r="B88" s="65"/>
       <c r="C88" s="64"/>
       <c r="D88" s="53" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E88" s="61"/>
       <c r="F88" s="14">
@@ -5683,10 +5686,10 @@
         <v>14</v>
       </c>
       <c r="D89" s="51" t="s">
+        <v>101</v>
+      </c>
+      <c r="E89" s="59" t="s">
         <v>102</v>
-      </c>
-      <c r="E89" s="59" t="s">
-        <v>103</v>
       </c>
       <c r="F89" s="5">
         <v>0.41666666666666669</v>
@@ -5730,7 +5733,7 @@
       <c r="B90" s="65"/>
       <c r="C90" s="63"/>
       <c r="D90" s="52" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E90" s="60"/>
       <c r="F90" s="8">
@@ -5777,7 +5780,7 @@
       <c r="B91" s="65"/>
       <c r="C91" s="63"/>
       <c r="D91" s="52" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E91" s="60"/>
       <c r="F91" s="8">
@@ -5822,7 +5825,7 @@
       <c r="B92" s="65"/>
       <c r="C92" s="63"/>
       <c r="D92" s="52" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E92" s="60"/>
       <c r="F92" s="8">
@@ -5867,7 +5870,7 @@
       <c r="B93" s="65"/>
       <c r="C93" s="63"/>
       <c r="D93" s="52" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E93" s="60"/>
       <c r="F93" s="8">
@@ -5914,7 +5917,7 @@
       <c r="B94" s="65"/>
       <c r="C94" s="63"/>
       <c r="D94" s="53" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E94" s="61"/>
       <c r="F94" s="12">
@@ -5957,10 +5960,10 @@
       <c r="B95" s="65"/>
       <c r="C95" s="63"/>
       <c r="D95" s="51" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E95" s="59" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F95" s="5">
         <v>0.91666666666666663</v>
@@ -6004,7 +6007,7 @@
       <c r="B96" s="65"/>
       <c r="C96" s="63"/>
       <c r="D96" s="52" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E96" s="60"/>
       <c r="F96" s="8">
@@ -6049,7 +6052,7 @@
       <c r="B97" s="65"/>
       <c r="C97" s="63"/>
       <c r="D97" s="52" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E97" s="60"/>
       <c r="F97" s="8">
@@ -6094,7 +6097,7 @@
       <c r="B98" s="65"/>
       <c r="C98" s="63"/>
       <c r="D98" s="52" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E98" s="60"/>
       <c r="F98" s="8">
@@ -6141,7 +6144,7 @@
       <c r="B99" s="65"/>
       <c r="C99" s="63"/>
       <c r="D99" s="52" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E99" s="60"/>
       <c r="F99" s="8">
@@ -6184,7 +6187,7 @@
       <c r="B100" s="65"/>
       <c r="C100" s="64"/>
       <c r="D100" s="53" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E100" s="61"/>
       <c r="F100" s="14">
@@ -6236,7 +6239,7 @@
         <v>60</v>
       </c>
       <c r="E101" s="59" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F101" s="5">
         <v>0.41666666666666669</v>
@@ -6508,7 +6511,7 @@
         <v>60</v>
       </c>
       <c r="E107" s="59" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F107" s="5">
         <v>0.91666666666666663</v>
@@ -6786,7 +6789,7 @@
         <v>60</v>
       </c>
       <c r="E113" s="59" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F113" s="5">
         <v>0.41666666666666669</v>
@@ -7062,7 +7065,7 @@
         <v>59</v>
       </c>
       <c r="E119" s="59" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F119" s="5">
         <v>0.91666666666666663</v>
@@ -7342,7 +7345,7 @@
         <v>59</v>
       </c>
       <c r="E125" s="59" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F125" s="5">
         <v>0.41666666666666669</v>
@@ -7513,7 +7516,7 @@
       <c r="B129" s="65"/>
       <c r="C129" s="63"/>
       <c r="D129" s="52" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E129" s="60"/>
       <c r="F129" s="8">
@@ -7560,7 +7563,7 @@
       <c r="B130" s="65"/>
       <c r="C130" s="63"/>
       <c r="D130" s="53" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E130" s="61"/>
       <c r="F130" s="12">
@@ -7603,10 +7606,10 @@
       <c r="B131" s="65"/>
       <c r="C131" s="63"/>
       <c r="D131" s="51" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E131" s="59" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F131" s="5">
         <v>0.91666666666666663</v>
@@ -7650,7 +7653,7 @@
       <c r="B132" s="65"/>
       <c r="C132" s="63"/>
       <c r="D132" s="52" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E132" s="60"/>
       <c r="F132" s="8">
@@ -7695,7 +7698,7 @@
       <c r="B133" s="65"/>
       <c r="C133" s="63"/>
       <c r="D133" s="52" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E133" s="60"/>
       <c r="F133" s="8">
@@ -7740,7 +7743,7 @@
       <c r="B134" s="65"/>
       <c r="C134" s="63"/>
       <c r="D134" s="52" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E134" s="60"/>
       <c r="F134" s="8">
@@ -7787,7 +7790,7 @@
       <c r="B135" s="65"/>
       <c r="C135" s="63"/>
       <c r="D135" s="52" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E135" s="60"/>
       <c r="F135" s="8">
@@ -7832,7 +7835,7 @@
       <c r="B136" s="65"/>
       <c r="C136" s="64"/>
       <c r="D136" s="53" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E136" s="61"/>
       <c r="F136" s="14">
@@ -7882,21 +7885,29 @@
       <c r="C137" s="62" t="s">
         <v>14</v>
       </c>
-      <c r="D137" s="51"/>
+      <c r="D137" s="51" t="s">
+        <v>101</v>
+      </c>
       <c r="E137" s="59" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F137" s="5">
         <v>0.41666666666666669</v>
       </c>
-      <c r="G137" s="73"/>
+      <c r="G137" s="73" t="s">
+        <v>74</v>
+      </c>
       <c r="H137" s="74"/>
-      <c r="I137" s="34"/>
-      <c r="J137" s="6" t="str">
+      <c r="I137" s="34">
+        <v>31</v>
+      </c>
+      <c r="J137" s="6">
         <f t="shared" ref="J137:J148" si="31">IFERROR(S137/I137,"")</f>
-        <v/>
-      </c>
-      <c r="K137" s="38"/>
+        <v>6.4516129032258063E-2</v>
+      </c>
+      <c r="K137" s="38">
+        <v>2</v>
+      </c>
       <c r="L137" s="38"/>
       <c r="M137" s="38"/>
       <c r="N137" s="38"/>
@@ -7906,14 +7917,14 @@
       <c r="R137" s="38"/>
       <c r="S137" s="7">
         <f>SUM(K137:R137)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T137" s="7">
         <v>100000</v>
       </c>
       <c r="U137" s="7">
         <f>T137*S137</f>
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="V137" s="4"/>
       <c r="W137" s="4"/>
@@ -7923,21 +7934,29 @@
     <row r="138" spans="2:25" ht="18.75">
       <c r="B138" s="65"/>
       <c r="C138" s="63"/>
-      <c r="D138" s="52"/>
+      <c r="D138" s="52" t="s">
+        <v>101</v>
+      </c>
       <c r="E138" s="60"/>
       <c r="F138" s="8">
         <v>0.5</v>
       </c>
-      <c r="G138" s="78"/>
+      <c r="G138" s="78" t="s">
+        <v>74</v>
+      </c>
       <c r="H138" s="79"/>
-      <c r="I138" s="35"/>
-      <c r="J138" s="9" t="str">
+      <c r="I138" s="35">
+        <v>35</v>
+      </c>
+      <c r="J138" s="9">
         <f t="shared" si="31"/>
-        <v/>
+        <v>0.14285714285714285</v>
       </c>
       <c r="K138" s="39"/>
       <c r="L138" s="39"/>
-      <c r="M138" s="39"/>
+      <c r="M138" s="39">
+        <v>5</v>
+      </c>
       <c r="N138" s="39"/>
       <c r="O138" s="39"/>
       <c r="P138" s="39"/>
@@ -7945,14 +7964,14 @@
       <c r="R138" s="39"/>
       <c r="S138" s="10">
         <f t="shared" ref="S138:S148" si="32">SUM(K138:R138)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T138" s="10">
         <v>100000</v>
       </c>
       <c r="U138" s="10">
         <f t="shared" ref="U138:U139" si="33">T138*S138</f>
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="V138" s="4"/>
       <c r="W138" s="4"/>
@@ -7962,21 +7981,29 @@
     <row r="139" spans="2:25" ht="18.75">
       <c r="B139" s="65"/>
       <c r="C139" s="63"/>
-      <c r="D139" s="52"/>
+      <c r="D139" s="52" t="s">
+        <v>101</v>
+      </c>
       <c r="E139" s="60"/>
       <c r="F139" s="8">
         <v>0.58333333333333337</v>
       </c>
-      <c r="G139" s="78"/>
+      <c r="G139" s="78" t="s">
+        <v>74</v>
+      </c>
       <c r="H139" s="79"/>
-      <c r="I139" s="35"/>
-      <c r="J139" s="9" t="str">
+      <c r="I139" s="35">
+        <v>35</v>
+      </c>
+      <c r="J139" s="9">
         <f t="shared" si="31"/>
-        <v/>
+        <v>0.14285714285714285</v>
       </c>
       <c r="K139" s="39"/>
       <c r="L139" s="39"/>
-      <c r="M139" s="39"/>
+      <c r="M139" s="39">
+        <v>5</v>
+      </c>
       <c r="N139" s="39"/>
       <c r="O139" s="39"/>
       <c r="P139" s="39"/>
@@ -7984,14 +8011,14 @@
       <c r="R139" s="39"/>
       <c r="S139" s="10">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T139" s="10">
         <v>100000</v>
       </c>
       <c r="U139" s="10">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="V139" s="4"/>
       <c r="W139" s="4"/>
@@ -8001,17 +8028,23 @@
     <row r="140" spans="2:25" ht="18.75">
       <c r="B140" s="65"/>
       <c r="C140" s="63"/>
-      <c r="D140" s="52"/>
+      <c r="D140" s="52" t="s">
+        <v>101</v>
+      </c>
       <c r="E140" s="60"/>
       <c r="F140" s="8">
         <v>0.66666666666666663</v>
       </c>
-      <c r="G140" s="78"/>
+      <c r="G140" s="78" t="s">
+        <v>74</v>
+      </c>
       <c r="H140" s="79"/>
-      <c r="I140" s="35"/>
-      <c r="J140" s="9" t="str">
+      <c r="I140" s="35">
+        <v>53</v>
+      </c>
+      <c r="J140" s="9">
         <f t="shared" si="31"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K140" s="39"/>
       <c r="L140" s="39"/>
@@ -8040,17 +8073,23 @@
     <row r="141" spans="2:25" ht="18.75">
       <c r="B141" s="65"/>
       <c r="C141" s="63"/>
-      <c r="D141" s="52"/>
+      <c r="D141" s="52" t="s">
+        <v>101</v>
+      </c>
       <c r="E141" s="60"/>
       <c r="F141" s="8">
         <v>0.75</v>
       </c>
-      <c r="G141" s="78"/>
+      <c r="G141" s="78" t="s">
+        <v>74</v>
+      </c>
       <c r="H141" s="79"/>
-      <c r="I141" s="35"/>
-      <c r="J141" s="9" t="str">
+      <c r="I141" s="35">
+        <v>53</v>
+      </c>
+      <c r="J141" s="9">
         <f t="shared" si="31"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K141" s="39"/>
       <c r="L141" s="39"/>
@@ -8079,17 +8118,23 @@
     <row r="142" spans="2:25" ht="18.75">
       <c r="B142" s="65"/>
       <c r="C142" s="63"/>
-      <c r="D142" s="53"/>
+      <c r="D142" s="53" t="s">
+        <v>101</v>
+      </c>
       <c r="E142" s="61"/>
       <c r="F142" s="12">
         <v>0.83333333333333337</v>
       </c>
-      <c r="G142" s="78"/>
+      <c r="G142" s="78" t="s">
+        <v>74</v>
+      </c>
       <c r="H142" s="79"/>
-      <c r="I142" s="36"/>
-      <c r="J142" s="9" t="str">
+      <c r="I142" s="36">
+        <v>53</v>
+      </c>
+      <c r="J142" s="9">
         <f t="shared" si="31"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K142" s="41"/>
       <c r="L142" s="41"/>
@@ -8116,21 +8161,29 @@
     <row r="143" spans="2:25" ht="18.75">
       <c r="B143" s="65"/>
       <c r="C143" s="63"/>
-      <c r="D143" s="51"/>
+      <c r="D143" s="51" t="s">
+        <v>101</v>
+      </c>
       <c r="E143" s="59" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F143" s="5">
         <v>0.91666666666666663</v>
       </c>
-      <c r="G143" s="73"/>
+      <c r="G143" s="73" t="s">
+        <v>89</v>
+      </c>
       <c r="H143" s="74"/>
-      <c r="I143" s="34"/>
-      <c r="J143" s="6" t="str">
+      <c r="I143" s="34">
+        <v>50</v>
+      </c>
+      <c r="J143" s="6">
         <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="K143" s="38"/>
+        <v>0.04</v>
+      </c>
+      <c r="K143" s="38">
+        <v>2</v>
+      </c>
       <c r="L143" s="38"/>
       <c r="M143" s="38"/>
       <c r="N143" s="38"/>
@@ -8140,14 +8193,14 @@
       <c r="R143" s="38"/>
       <c r="S143" s="7">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T143" s="7">
         <v>100000</v>
       </c>
       <c r="U143" s="7">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="V143" s="4"/>
       <c r="Y143" s="4"/>
@@ -8155,21 +8208,29 @@
     <row r="144" spans="2:25" ht="18.75">
       <c r="B144" s="65"/>
       <c r="C144" s="63"/>
-      <c r="D144" s="52"/>
+      <c r="D144" s="52" t="s">
+        <v>101</v>
+      </c>
       <c r="E144" s="60"/>
       <c r="F144" s="8">
         <v>1</v>
       </c>
-      <c r="G144" s="78"/>
+      <c r="G144" s="78" t="s">
+        <v>89</v>
+      </c>
       <c r="H144" s="79"/>
-      <c r="I144" s="35"/>
-      <c r="J144" s="9" t="str">
+      <c r="I144" s="35">
+        <v>50</v>
+      </c>
+      <c r="J144" s="9">
         <f t="shared" si="31"/>
-        <v/>
+        <v>0.02</v>
       </c>
       <c r="K144" s="39"/>
       <c r="L144" s="39"/>
-      <c r="M144" s="39"/>
+      <c r="M144" s="39">
+        <v>1</v>
+      </c>
       <c r="N144" s="39"/>
       <c r="O144" s="39"/>
       <c r="P144" s="39"/>
@@ -8177,14 +8238,14 @@
       <c r="R144" s="39"/>
       <c r="S144" s="10">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T144" s="10">
         <v>100000</v>
       </c>
       <c r="U144" s="10">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="V144" s="4"/>
       <c r="Y144" s="4"/>
@@ -8192,21 +8253,29 @@
     <row r="145" spans="2:25" ht="18.75">
       <c r="B145" s="65"/>
       <c r="C145" s="63"/>
-      <c r="D145" s="52"/>
+      <c r="D145" s="52" t="s">
+        <v>101</v>
+      </c>
       <c r="E145" s="60"/>
       <c r="F145" s="8">
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="G145" s="78"/>
+      <c r="G145" s="78" t="s">
+        <v>89</v>
+      </c>
       <c r="H145" s="79"/>
-      <c r="I145" s="35"/>
-      <c r="J145" s="9" t="str">
+      <c r="I145" s="35">
+        <v>50</v>
+      </c>
+      <c r="J145" s="9">
         <f t="shared" si="31"/>
-        <v/>
+        <v>0.02</v>
       </c>
       <c r="K145" s="39"/>
       <c r="L145" s="39"/>
-      <c r="M145" s="39"/>
+      <c r="M145" s="39">
+        <v>1</v>
+      </c>
       <c r="N145" s="39"/>
       <c r="O145" s="39"/>
       <c r="P145" s="39"/>
@@ -8214,14 +8283,14 @@
       <c r="R145" s="39"/>
       <c r="S145" s="10">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T145" s="10">
         <v>100000</v>
       </c>
       <c r="U145" s="10">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="V145" s="4"/>
       <c r="Y145" s="4"/>
@@ -8229,21 +8298,29 @@
     <row r="146" spans="2:25" ht="18.75">
       <c r="B146" s="65"/>
       <c r="C146" s="63"/>
-      <c r="D146" s="52"/>
+      <c r="D146" s="52" t="s">
+        <v>101</v>
+      </c>
       <c r="E146" s="60"/>
       <c r="F146" s="8">
         <v>0.16666666666666666</v>
       </c>
-      <c r="G146" s="78"/>
+      <c r="G146" s="78" t="s">
+        <v>89</v>
+      </c>
       <c r="H146" s="79"/>
-      <c r="I146" s="35"/>
-      <c r="J146" s="9" t="str">
+      <c r="I146" s="35">
+        <v>50</v>
+      </c>
+      <c r="J146" s="9">
         <f t="shared" si="31"/>
-        <v/>
+        <v>0.04</v>
       </c>
       <c r="K146" s="39"/>
       <c r="L146" s="39"/>
-      <c r="M146" s="39"/>
+      <c r="M146" s="39">
+        <v>2</v>
+      </c>
       <c r="N146" s="39"/>
       <c r="O146" s="39"/>
       <c r="P146" s="39"/>
@@ -8251,14 +8328,14 @@
       <c r="R146" s="39"/>
       <c r="S146" s="10">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T146" s="10">
         <v>100000</v>
       </c>
       <c r="U146" s="10">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="V146" s="4"/>
       <c r="W146" s="4"/>
@@ -8268,12 +8345,16 @@
     <row r="147" spans="2:25" ht="18.75">
       <c r="B147" s="65"/>
       <c r="C147" s="63"/>
-      <c r="D147" s="52"/>
+      <c r="D147" s="52" t="s">
+        <v>101</v>
+      </c>
       <c r="E147" s="60"/>
       <c r="F147" s="8">
         <v>0.25</v>
       </c>
-      <c r="G147" s="78"/>
+      <c r="G147" s="78" t="s">
+        <v>89</v>
+      </c>
       <c r="H147" s="79"/>
       <c r="I147" s="35"/>
       <c r="J147" s="9" t="str">
@@ -8305,12 +8386,16 @@
     <row r="148" spans="2:25" ht="18.75">
       <c r="B148" s="65"/>
       <c r="C148" s="64"/>
-      <c r="D148" s="53"/>
+      <c r="D148" s="53" t="s">
+        <v>101</v>
+      </c>
       <c r="E148" s="91"/>
       <c r="F148" s="14">
         <v>0.33333333333333331</v>
       </c>
-      <c r="G148" s="78"/>
+      <c r="G148" s="78" t="s">
+        <v>89</v>
+      </c>
       <c r="H148" s="79"/>
       <c r="I148" s="37"/>
       <c r="J148" s="15" t="str">
@@ -8341,23 +8426,29 @@
       <c r="X148" s="4"/>
       <c r="Y148" s="4"/>
     </row>
-    <row r="149" spans="2:25" ht="16.5" customHeight="1">
+    <row r="149" spans="2:25" ht="42.75" customHeight="1">
       <c r="B149" s="65">
         <v>46093</v>
       </c>
       <c r="C149" s="62" t="s">
         <v>14</v>
       </c>
-      <c r="D149" s="51"/>
+      <c r="D149" s="51" t="s">
+        <v>41</v>
+      </c>
       <c r="E149" s="59" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F149" s="5">
         <v>0.41666666666666669</v>
       </c>
-      <c r="G149" s="73"/>
+      <c r="G149" s="73" t="s">
+        <v>79</v>
+      </c>
       <c r="H149" s="74"/>
-      <c r="I149" s="34"/>
+      <c r="I149" s="34">
+        <v>0</v>
+      </c>
       <c r="J149" s="6" t="str">
         <f t="shared" ref="J149:J160" si="35">IFERROR(S149/I149,"")</f>
         <v/>
@@ -8368,38 +8459,46 @@
       <c r="N149" s="38"/>
       <c r="O149" s="38"/>
       <c r="P149" s="38"/>
-      <c r="Q149" s="38"/>
+      <c r="Q149" s="38">
+        <v>20</v>
+      </c>
       <c r="R149" s="38"/>
       <c r="S149" s="7">
         <f>SUM(K149:R149)</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="T149" s="7">
         <v>100000</v>
       </c>
       <c r="U149" s="7">
         <f>T149*S149</f>
-        <v>0</v>
+        <v>2000000</v>
       </c>
       <c r="V149" s="4"/>
       <c r="W149" s="4"/>
       <c r="X149" s="4"/>
       <c r="Y149" s="4"/>
     </row>
-    <row r="150" spans="2:25" ht="18.75">
+    <row r="150" spans="2:25" ht="37.5">
       <c r="B150" s="65"/>
       <c r="C150" s="63"/>
-      <c r="D150" s="52"/>
+      <c r="D150" s="52" t="s">
+        <v>41</v>
+      </c>
       <c r="E150" s="60"/>
       <c r="F150" s="8">
         <v>0.5</v>
       </c>
-      <c r="G150" s="78"/>
+      <c r="G150" s="78" t="s">
+        <v>79</v>
+      </c>
       <c r="H150" s="79"/>
-      <c r="I150" s="35"/>
-      <c r="J150" s="9" t="str">
+      <c r="I150" s="35">
+        <v>12</v>
+      </c>
+      <c r="J150" s="9">
         <f t="shared" si="35"/>
-        <v/>
+        <v>0.66666666666666663</v>
       </c>
       <c r="K150" s="39"/>
       <c r="L150" s="39"/>
@@ -8408,37 +8507,45 @@
       <c r="O150" s="39"/>
       <c r="P150" s="39"/>
       <c r="Q150" s="39"/>
-      <c r="R150" s="39"/>
+      <c r="R150" s="39">
+        <v>8</v>
+      </c>
       <c r="S150" s="10">
         <f t="shared" ref="S150:S160" si="36">SUM(K150:R150)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="T150" s="10">
         <v>100000</v>
       </c>
       <c r="U150" s="10">
         <f t="shared" ref="U150:U151" si="37">T150*S150</f>
-        <v>0</v>
+        <v>800000</v>
       </c>
       <c r="V150" s="4"/>
       <c r="W150" s="4"/>
       <c r="X150" s="4"/>
       <c r="Y150" s="4"/>
     </row>
-    <row r="151" spans="2:25" ht="18.75">
+    <row r="151" spans="2:25" ht="37.5">
       <c r="B151" s="65"/>
       <c r="C151" s="63"/>
-      <c r="D151" s="52"/>
+      <c r="D151" s="52" t="s">
+        <v>41</v>
+      </c>
       <c r="E151" s="60"/>
       <c r="F151" s="8">
         <v>0.58333333333333337</v>
       </c>
-      <c r="G151" s="78"/>
+      <c r="G151" s="78" t="s">
+        <v>79</v>
+      </c>
       <c r="H151" s="79"/>
-      <c r="I151" s="35"/>
-      <c r="J151" s="9" t="str">
+      <c r="I151" s="35">
+        <v>120</v>
+      </c>
+      <c r="J151" s="9">
         <f t="shared" si="35"/>
-        <v/>
+        <v>8.3333333333333329E-2</v>
       </c>
       <c r="K151" s="39"/>
       <c r="L151" s="39"/>
@@ -8447,37 +8554,45 @@
       <c r="O151" s="39"/>
       <c r="P151" s="39"/>
       <c r="Q151" s="39"/>
-      <c r="R151" s="39"/>
+      <c r="R151" s="39">
+        <v>10</v>
+      </c>
       <c r="S151" s="10">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="T151" s="10">
         <v>100000</v>
       </c>
       <c r="U151" s="10">
         <f t="shared" si="37"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="V151" s="4"/>
       <c r="W151" s="4"/>
       <c r="X151" s="4"/>
       <c r="Y151" s="4"/>
     </row>
-    <row r="152" spans="2:25" ht="18.75">
+    <row r="152" spans="2:25" ht="37.5">
       <c r="B152" s="65"/>
       <c r="C152" s="63"/>
-      <c r="D152" s="52"/>
+      <c r="D152" s="52" t="s">
+        <v>41</v>
+      </c>
       <c r="E152" s="60"/>
       <c r="F152" s="8">
         <v>0.66666666666666663</v>
       </c>
-      <c r="G152" s="78"/>
+      <c r="G152" s="78" t="s">
+        <v>79</v>
+      </c>
       <c r="H152" s="79"/>
-      <c r="I152" s="35"/>
-      <c r="J152" s="9" t="str">
+      <c r="I152" s="35">
+        <v>145</v>
+      </c>
+      <c r="J152" s="9">
         <f t="shared" si="35"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K152" s="39"/>
       <c r="L152" s="39"/>
@@ -8503,20 +8618,26 @@
       <c r="X152" s="4"/>
       <c r="Y152" s="4"/>
     </row>
-    <row r="153" spans="2:25" ht="18.75">
+    <row r="153" spans="2:25" ht="37.5">
       <c r="B153" s="65"/>
       <c r="C153" s="63"/>
-      <c r="D153" s="52"/>
+      <c r="D153" s="52" t="s">
+        <v>41</v>
+      </c>
       <c r="E153" s="60"/>
       <c r="F153" s="8">
         <v>0.75</v>
       </c>
-      <c r="G153" s="78"/>
+      <c r="G153" s="78" t="s">
+        <v>79</v>
+      </c>
       <c r="H153" s="79"/>
-      <c r="I153" s="35"/>
-      <c r="J153" s="9" t="str">
+      <c r="I153" s="35">
+        <v>141</v>
+      </c>
+      <c r="J153" s="9">
         <f t="shared" si="35"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K153" s="39"/>
       <c r="L153" s="39"/>
@@ -8542,20 +8663,26 @@
       <c r="X153" s="11"/>
       <c r="Y153" s="4"/>
     </row>
-    <row r="154" spans="2:25" ht="18.75">
+    <row r="154" spans="2:25" ht="37.5">
       <c r="B154" s="65"/>
       <c r="C154" s="63"/>
-      <c r="D154" s="53"/>
+      <c r="D154" s="53" t="s">
+        <v>41</v>
+      </c>
       <c r="E154" s="61"/>
       <c r="F154" s="12">
         <v>0.83333333333333337</v>
       </c>
-      <c r="G154" s="78"/>
+      <c r="G154" s="78" t="s">
+        <v>79</v>
+      </c>
       <c r="H154" s="79"/>
-      <c r="I154" s="36"/>
-      <c r="J154" s="9" t="str">
+      <c r="I154" s="36">
+        <v>142</v>
+      </c>
+      <c r="J154" s="9">
         <f t="shared" si="35"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K154" s="41"/>
       <c r="L154" s="41"/>
@@ -8579,22 +8706,28 @@
       <c r="V154" s="4"/>
       <c r="Y154" s="4"/>
     </row>
-    <row r="155" spans="2:25" ht="18.75">
+    <row r="155" spans="2:25" ht="37.5">
       <c r="B155" s="65"/>
       <c r="C155" s="63"/>
-      <c r="D155" s="51"/>
+      <c r="D155" s="51" t="s">
+        <v>41</v>
+      </c>
       <c r="E155" s="59" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F155" s="5">
         <v>0.91666666666666663</v>
       </c>
-      <c r="G155" s="73"/>
+      <c r="G155" s="73" t="s">
+        <v>86</v>
+      </c>
       <c r="H155" s="74"/>
-      <c r="I155" s="34"/>
-      <c r="J155" s="6" t="str">
+      <c r="I155" s="34">
+        <v>146</v>
+      </c>
+      <c r="J155" s="6">
         <f t="shared" si="35"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K155" s="38"/>
       <c r="L155" s="38"/>
@@ -8618,20 +8751,26 @@
       <c r="V155" s="4"/>
       <c r="Y155" s="4"/>
     </row>
-    <row r="156" spans="2:25" ht="18.75">
+    <row r="156" spans="2:25" ht="37.5">
       <c r="B156" s="65"/>
       <c r="C156" s="63"/>
-      <c r="D156" s="52"/>
+      <c r="D156" s="52" t="s">
+        <v>41</v>
+      </c>
       <c r="E156" s="60"/>
       <c r="F156" s="8">
         <v>1</v>
       </c>
-      <c r="G156" s="78"/>
+      <c r="G156" s="78" t="s">
+        <v>86</v>
+      </c>
       <c r="H156" s="79"/>
-      <c r="I156" s="35"/>
-      <c r="J156" s="9" t="str">
+      <c r="I156" s="35">
+        <v>146</v>
+      </c>
+      <c r="J156" s="9">
         <f t="shared" si="35"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K156" s="39"/>
       <c r="L156" s="39"/>
@@ -8655,20 +8794,26 @@
       <c r="V156" s="4"/>
       <c r="Y156" s="4"/>
     </row>
-    <row r="157" spans="2:25" ht="18.75">
+    <row r="157" spans="2:25" ht="37.5">
       <c r="B157" s="65"/>
       <c r="C157" s="63"/>
-      <c r="D157" s="52"/>
+      <c r="D157" s="52" t="s">
+        <v>41</v>
+      </c>
       <c r="E157" s="60"/>
       <c r="F157" s="8">
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="G157" s="78"/>
+      <c r="G157" s="78" t="s">
+        <v>86</v>
+      </c>
       <c r="H157" s="79"/>
-      <c r="I157" s="35"/>
-      <c r="J157" s="9" t="str">
+      <c r="I157" s="35">
+        <v>147</v>
+      </c>
+      <c r="J157" s="9">
         <f t="shared" si="35"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K157" s="39"/>
       <c r="L157" s="39"/>
@@ -8692,20 +8837,26 @@
       <c r="V157" s="4"/>
       <c r="Y157" s="4"/>
     </row>
-    <row r="158" spans="2:25" ht="18.75">
+    <row r="158" spans="2:25" ht="37.5">
       <c r="B158" s="65"/>
       <c r="C158" s="63"/>
-      <c r="D158" s="52"/>
+      <c r="D158" s="52" t="s">
+        <v>41</v>
+      </c>
       <c r="E158" s="60"/>
       <c r="F158" s="8">
         <v>0.16666666666666666</v>
       </c>
-      <c r="G158" s="78"/>
+      <c r="G158" s="78" t="s">
+        <v>86</v>
+      </c>
       <c r="H158" s="79"/>
-      <c r="I158" s="35"/>
-      <c r="J158" s="9" t="str">
+      <c r="I158" s="35">
+        <v>147</v>
+      </c>
+      <c r="J158" s="9">
         <f t="shared" si="35"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K158" s="39"/>
       <c r="L158" s="39"/>
@@ -8731,20 +8882,26 @@
       <c r="X158" s="4"/>
       <c r="Y158" s="4"/>
     </row>
-    <row r="159" spans="2:25" ht="18.75">
+    <row r="159" spans="2:25" ht="37.5">
       <c r="B159" s="65"/>
       <c r="C159" s="63"/>
-      <c r="D159" s="52"/>
+      <c r="D159" s="52" t="s">
+        <v>41</v>
+      </c>
       <c r="E159" s="60"/>
       <c r="F159" s="8">
         <v>0.25</v>
       </c>
-      <c r="G159" s="78"/>
+      <c r="G159" s="78" t="s">
+        <v>86</v>
+      </c>
       <c r="H159" s="79"/>
-      <c r="I159" s="35"/>
-      <c r="J159" s="9" t="str">
+      <c r="I159" s="35">
+        <v>147</v>
+      </c>
+      <c r="J159" s="9">
         <f t="shared" si="35"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K159" s="39"/>
       <c r="L159" s="39"/>
@@ -8768,20 +8925,26 @@
       <c r="V159" s="4"/>
       <c r="Y159" s="4"/>
     </row>
-    <row r="160" spans="2:25" ht="18.75">
+    <row r="160" spans="2:25" ht="37.5">
       <c r="B160" s="65"/>
       <c r="C160" s="64"/>
-      <c r="D160" s="53"/>
+      <c r="D160" s="53" t="s">
+        <v>41</v>
+      </c>
       <c r="E160" s="91"/>
       <c r="F160" s="14">
         <v>0.33333333333333331</v>
       </c>
-      <c r="G160" s="78"/>
+      <c r="G160" s="78" t="s">
+        <v>86</v>
+      </c>
       <c r="H160" s="79"/>
-      <c r="I160" s="37"/>
-      <c r="J160" s="15" t="str">
+      <c r="I160" s="37">
+        <v>147</v>
+      </c>
+      <c r="J160" s="15">
         <f t="shared" si="35"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K160" s="40"/>
       <c r="L160" s="40"/>
@@ -8807,8 +8970,972 @@
       <c r="X160" s="4"/>
       <c r="Y160" s="4"/>
     </row>
+    <row r="161" spans="2:25" ht="16.5" customHeight="1">
+      <c r="B161" s="65">
+        <v>46094</v>
+      </c>
+      <c r="C161" s="62" t="s">
+        <v>14</v>
+      </c>
+      <c r="D161" s="51"/>
+      <c r="E161" s="59" t="s">
+        <v>102</v>
+      </c>
+      <c r="F161" s="5">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="G161" s="73"/>
+      <c r="H161" s="74"/>
+      <c r="I161" s="34"/>
+      <c r="J161" s="6" t="str">
+        <f t="shared" ref="J161:J184" si="39">IFERROR(S161/I161,"")</f>
+        <v/>
+      </c>
+      <c r="K161" s="38"/>
+      <c r="L161" s="38"/>
+      <c r="M161" s="38"/>
+      <c r="N161" s="38"/>
+      <c r="O161" s="38"/>
+      <c r="P161" s="38"/>
+      <c r="Q161" s="38"/>
+      <c r="R161" s="38"/>
+      <c r="S161" s="7">
+        <f>SUM(K161:R161)</f>
+        <v>0</v>
+      </c>
+      <c r="T161" s="7">
+        <v>100000</v>
+      </c>
+      <c r="U161" s="7">
+        <f>T161*S161</f>
+        <v>0</v>
+      </c>
+      <c r="V161" s="4"/>
+      <c r="W161" s="4"/>
+      <c r="X161" s="4"/>
+      <c r="Y161" s="4"/>
+    </row>
+    <row r="162" spans="2:25" ht="18.75">
+      <c r="B162" s="65"/>
+      <c r="C162" s="63"/>
+      <c r="D162" s="52"/>
+      <c r="E162" s="60"/>
+      <c r="F162" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="G162" s="78"/>
+      <c r="H162" s="79"/>
+      <c r="I162" s="35"/>
+      <c r="J162" s="9" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="K162" s="39"/>
+      <c r="L162" s="39"/>
+      <c r="M162" s="39"/>
+      <c r="N162" s="39"/>
+      <c r="O162" s="39"/>
+      <c r="P162" s="39"/>
+      <c r="Q162" s="39"/>
+      <c r="R162" s="39"/>
+      <c r="S162" s="10">
+        <f t="shared" ref="S162:S172" si="40">SUM(K162:R162)</f>
+        <v>0</v>
+      </c>
+      <c r="T162" s="10">
+        <v>100000</v>
+      </c>
+      <c r="U162" s="10">
+        <f t="shared" ref="U162:U163" si="41">T162*S162</f>
+        <v>0</v>
+      </c>
+      <c r="V162" s="4"/>
+      <c r="W162" s="4"/>
+      <c r="X162" s="4"/>
+      <c r="Y162" s="4"/>
+    </row>
+    <row r="163" spans="2:25" ht="18.75">
+      <c r="B163" s="65"/>
+      <c r="C163" s="63"/>
+      <c r="D163" s="52"/>
+      <c r="E163" s="60"/>
+      <c r="F163" s="8">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="G163" s="78"/>
+      <c r="H163" s="79"/>
+      <c r="I163" s="35"/>
+      <c r="J163" s="9" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="K163" s="39"/>
+      <c r="L163" s="39"/>
+      <c r="M163" s="39"/>
+      <c r="N163" s="39"/>
+      <c r="O163" s="39"/>
+      <c r="P163" s="39"/>
+      <c r="Q163" s="39"/>
+      <c r="R163" s="39"/>
+      <c r="S163" s="10">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="T163" s="10">
+        <v>100000</v>
+      </c>
+      <c r="U163" s="10">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="V163" s="4"/>
+      <c r="W163" s="4"/>
+      <c r="X163" s="4"/>
+      <c r="Y163" s="4"/>
+    </row>
+    <row r="164" spans="2:25" ht="18.75">
+      <c r="B164" s="65"/>
+      <c r="C164" s="63"/>
+      <c r="D164" s="52"/>
+      <c r="E164" s="60"/>
+      <c r="F164" s="8">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="G164" s="78"/>
+      <c r="H164" s="79"/>
+      <c r="I164" s="35"/>
+      <c r="J164" s="9" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="K164" s="39"/>
+      <c r="L164" s="39"/>
+      <c r="M164" s="39"/>
+      <c r="N164" s="39"/>
+      <c r="O164" s="39"/>
+      <c r="P164" s="39"/>
+      <c r="Q164" s="39"/>
+      <c r="R164" s="39"/>
+      <c r="S164" s="10">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="T164" s="10">
+        <v>100000</v>
+      </c>
+      <c r="U164" s="10">
+        <f>T164*S164</f>
+        <v>0</v>
+      </c>
+      <c r="V164" s="4"/>
+      <c r="W164" s="4"/>
+      <c r="X164" s="4"/>
+      <c r="Y164" s="4"/>
+    </row>
+    <row r="165" spans="2:25" ht="18.75">
+      <c r="B165" s="65"/>
+      <c r="C165" s="63"/>
+      <c r="D165" s="52"/>
+      <c r="E165" s="60"/>
+      <c r="F165" s="8">
+        <v>0.75</v>
+      </c>
+      <c r="G165" s="78"/>
+      <c r="H165" s="79"/>
+      <c r="I165" s="35"/>
+      <c r="J165" s="9" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="K165" s="39"/>
+      <c r="L165" s="39"/>
+      <c r="M165" s="39"/>
+      <c r="N165" s="39"/>
+      <c r="O165" s="39"/>
+      <c r="P165" s="39"/>
+      <c r="Q165" s="39"/>
+      <c r="R165" s="39"/>
+      <c r="S165" s="10">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="T165" s="10">
+        <v>100000</v>
+      </c>
+      <c r="U165" s="10">
+        <f t="shared" ref="U165:U172" si="42">T165*S165</f>
+        <v>0</v>
+      </c>
+      <c r="V165" s="4"/>
+      <c r="W165" s="4"/>
+      <c r="X165" s="11"/>
+      <c r="Y165" s="4"/>
+    </row>
+    <row r="166" spans="2:25" ht="18.75">
+      <c r="B166" s="65"/>
+      <c r="C166" s="63"/>
+      <c r="D166" s="53"/>
+      <c r="E166" s="61"/>
+      <c r="F166" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="G166" s="78"/>
+      <c r="H166" s="79"/>
+      <c r="I166" s="36"/>
+      <c r="J166" s="9" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="K166" s="41"/>
+      <c r="L166" s="41"/>
+      <c r="M166" s="41"/>
+      <c r="N166" s="41"/>
+      <c r="O166" s="41"/>
+      <c r="P166" s="41"/>
+      <c r="Q166" s="41"/>
+      <c r="R166" s="41"/>
+      <c r="S166" s="13">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="T166" s="13">
+        <v>100000</v>
+      </c>
+      <c r="U166" s="13">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="V166" s="4"/>
+      <c r="Y166" s="4"/>
+    </row>
+    <row r="167" spans="2:25" ht="18.75">
+      <c r="B167" s="65"/>
+      <c r="C167" s="63"/>
+      <c r="D167" s="51"/>
+      <c r="E167" s="59" t="s">
+        <v>103</v>
+      </c>
+      <c r="F167" s="5">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="G167" s="73"/>
+      <c r="H167" s="74"/>
+      <c r="I167" s="34"/>
+      <c r="J167" s="6" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="K167" s="38"/>
+      <c r="L167" s="38"/>
+      <c r="M167" s="38"/>
+      <c r="N167" s="38"/>
+      <c r="O167" s="38"/>
+      <c r="P167" s="38"/>
+      <c r="Q167" s="38"/>
+      <c r="R167" s="38"/>
+      <c r="S167" s="7">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="T167" s="7">
+        <v>100000</v>
+      </c>
+      <c r="U167" s="7">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="V167" s="4"/>
+      <c r="Y167" s="4"/>
+    </row>
+    <row r="168" spans="2:25" ht="18.75">
+      <c r="B168" s="65"/>
+      <c r="C168" s="63"/>
+      <c r="D168" s="52"/>
+      <c r="E168" s="60"/>
+      <c r="F168" s="8">
+        <v>1</v>
+      </c>
+      <c r="G168" s="78"/>
+      <c r="H168" s="79"/>
+      <c r="I168" s="35"/>
+      <c r="J168" s="9" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="K168" s="39"/>
+      <c r="L168" s="39"/>
+      <c r="M168" s="39"/>
+      <c r="N168" s="39"/>
+      <c r="O168" s="39"/>
+      <c r="P168" s="39"/>
+      <c r="Q168" s="39"/>
+      <c r="R168" s="39"/>
+      <c r="S168" s="10">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="T168" s="10">
+        <v>100000</v>
+      </c>
+      <c r="U168" s="10">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="V168" s="4"/>
+      <c r="Y168" s="4"/>
+    </row>
+    <row r="169" spans="2:25" ht="18.75">
+      <c r="B169" s="65"/>
+      <c r="C169" s="63"/>
+      <c r="D169" s="52"/>
+      <c r="E169" s="60"/>
+      <c r="F169" s="8">
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="G169" s="78"/>
+      <c r="H169" s="79"/>
+      <c r="I169" s="35"/>
+      <c r="J169" s="9" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="K169" s="39"/>
+      <c r="L169" s="39"/>
+      <c r="M169" s="39"/>
+      <c r="N169" s="39"/>
+      <c r="O169" s="39"/>
+      <c r="P169" s="39"/>
+      <c r="Q169" s="39"/>
+      <c r="R169" s="39"/>
+      <c r="S169" s="10">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="T169" s="10">
+        <v>100000</v>
+      </c>
+      <c r="U169" s="10">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="V169" s="4"/>
+      <c r="Y169" s="4"/>
+    </row>
+    <row r="170" spans="2:25" ht="18.75">
+      <c r="B170" s="65"/>
+      <c r="C170" s="63"/>
+      <c r="D170" s="52"/>
+      <c r="E170" s="60"/>
+      <c r="F170" s="8">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="G170" s="78"/>
+      <c r="H170" s="79"/>
+      <c r="I170" s="35"/>
+      <c r="J170" s="9" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="K170" s="39"/>
+      <c r="L170" s="39"/>
+      <c r="M170" s="39"/>
+      <c r="N170" s="39"/>
+      <c r="O170" s="39"/>
+      <c r="P170" s="39"/>
+      <c r="Q170" s="39"/>
+      <c r="R170" s="39"/>
+      <c r="S170" s="10">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="T170" s="10">
+        <v>100000</v>
+      </c>
+      <c r="U170" s="10">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="V170" s="4"/>
+      <c r="W170" s="4"/>
+      <c r="X170" s="4"/>
+      <c r="Y170" s="4"/>
+    </row>
+    <row r="171" spans="2:25" ht="18.75">
+      <c r="B171" s="65"/>
+      <c r="C171" s="63"/>
+      <c r="D171" s="52"/>
+      <c r="E171" s="60"/>
+      <c r="F171" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="G171" s="78"/>
+      <c r="H171" s="79"/>
+      <c r="I171" s="35"/>
+      <c r="J171" s="9" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="K171" s="39"/>
+      <c r="L171" s="39"/>
+      <c r="M171" s="39"/>
+      <c r="N171" s="39"/>
+      <c r="O171" s="39"/>
+      <c r="P171" s="39"/>
+      <c r="Q171" s="39"/>
+      <c r="R171" s="39"/>
+      <c r="S171" s="10">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="T171" s="10">
+        <v>100000</v>
+      </c>
+      <c r="U171" s="10">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="V171" s="4"/>
+      <c r="Y171" s="4"/>
+    </row>
+    <row r="172" spans="2:25" ht="18.75">
+      <c r="B172" s="65"/>
+      <c r="C172" s="64"/>
+      <c r="D172" s="53"/>
+      <c r="E172" s="91"/>
+      <c r="F172" s="14">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="G172" s="78"/>
+      <c r="H172" s="79"/>
+      <c r="I172" s="37"/>
+      <c r="J172" s="15" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="K172" s="40"/>
+      <c r="L172" s="40"/>
+      <c r="M172" s="40"/>
+      <c r="N172" s="40"/>
+      <c r="O172" s="40"/>
+      <c r="P172" s="40"/>
+      <c r="Q172" s="40"/>
+      <c r="R172" s="40"/>
+      <c r="S172" s="16">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="T172" s="16">
+        <v>100000</v>
+      </c>
+      <c r="U172" s="16">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="V172" s="4"/>
+      <c r="W172" s="4"/>
+      <c r="X172" s="4"/>
+      <c r="Y172" s="4"/>
+    </row>
+    <row r="173" spans="2:25" ht="16.5" customHeight="1">
+      <c r="B173" s="65">
+        <v>46095</v>
+      </c>
+      <c r="C173" s="62" t="s">
+        <v>14</v>
+      </c>
+      <c r="D173" s="51"/>
+      <c r="E173" s="59" t="s">
+        <v>102</v>
+      </c>
+      <c r="F173" s="5">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="G173" s="73"/>
+      <c r="H173" s="74"/>
+      <c r="I173" s="34"/>
+      <c r="J173" s="6" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="K173" s="38"/>
+      <c r="L173" s="38"/>
+      <c r="M173" s="38"/>
+      <c r="N173" s="38"/>
+      <c r="O173" s="38"/>
+      <c r="P173" s="38"/>
+      <c r="Q173" s="38"/>
+      <c r="R173" s="38"/>
+      <c r="S173" s="7">
+        <f>SUM(K173:R173)</f>
+        <v>0</v>
+      </c>
+      <c r="T173" s="7">
+        <v>100000</v>
+      </c>
+      <c r="U173" s="7">
+        <f>T173*S173</f>
+        <v>0</v>
+      </c>
+      <c r="V173" s="4"/>
+      <c r="W173" s="4"/>
+      <c r="X173" s="4"/>
+      <c r="Y173" s="4"/>
+    </row>
+    <row r="174" spans="2:25" ht="18.75">
+      <c r="B174" s="65"/>
+      <c r="C174" s="63"/>
+      <c r="D174" s="52"/>
+      <c r="E174" s="60"/>
+      <c r="F174" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="G174" s="78"/>
+      <c r="H174" s="79"/>
+      <c r="I174" s="35"/>
+      <c r="J174" s="9" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="K174" s="39"/>
+      <c r="L174" s="39"/>
+      <c r="M174" s="39"/>
+      <c r="N174" s="39"/>
+      <c r="O174" s="39"/>
+      <c r="P174" s="39"/>
+      <c r="Q174" s="39"/>
+      <c r="R174" s="39"/>
+      <c r="S174" s="10">
+        <f t="shared" ref="S174:S184" si="43">SUM(K174:R174)</f>
+        <v>0</v>
+      </c>
+      <c r="T174" s="10">
+        <v>100000</v>
+      </c>
+      <c r="U174" s="10">
+        <f t="shared" ref="U174:U175" si="44">T174*S174</f>
+        <v>0</v>
+      </c>
+      <c r="V174" s="4"/>
+      <c r="W174" s="4"/>
+      <c r="X174" s="4"/>
+      <c r="Y174" s="4"/>
+    </row>
+    <row r="175" spans="2:25" ht="18.75">
+      <c r="B175" s="65"/>
+      <c r="C175" s="63"/>
+      <c r="D175" s="52"/>
+      <c r="E175" s="60"/>
+      <c r="F175" s="8">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="G175" s="78"/>
+      <c r="H175" s="79"/>
+      <c r="I175" s="35"/>
+      <c r="J175" s="9" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="K175" s="39"/>
+      <c r="L175" s="39"/>
+      <c r="M175" s="39"/>
+      <c r="N175" s="39"/>
+      <c r="O175" s="39"/>
+      <c r="P175" s="39"/>
+      <c r="Q175" s="39"/>
+      <c r="R175" s="39"/>
+      <c r="S175" s="10">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="T175" s="10">
+        <v>100000</v>
+      </c>
+      <c r="U175" s="10">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="V175" s="4"/>
+      <c r="W175" s="4"/>
+      <c r="X175" s="4"/>
+      <c r="Y175" s="4"/>
+    </row>
+    <row r="176" spans="2:25" ht="18.75">
+      <c r="B176" s="65"/>
+      <c r="C176" s="63"/>
+      <c r="D176" s="52"/>
+      <c r="E176" s="60"/>
+      <c r="F176" s="8">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="G176" s="78"/>
+      <c r="H176" s="79"/>
+      <c r="I176" s="35"/>
+      <c r="J176" s="9" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="K176" s="39"/>
+      <c r="L176" s="39"/>
+      <c r="M176" s="39"/>
+      <c r="N176" s="39"/>
+      <c r="O176" s="39"/>
+      <c r="P176" s="39"/>
+      <c r="Q176" s="39"/>
+      <c r="R176" s="39"/>
+      <c r="S176" s="10">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="T176" s="10">
+        <v>100000</v>
+      </c>
+      <c r="U176" s="10">
+        <f>T176*S176</f>
+        <v>0</v>
+      </c>
+      <c r="V176" s="4"/>
+      <c r="W176" s="4"/>
+      <c r="X176" s="4"/>
+      <c r="Y176" s="4"/>
+    </row>
+    <row r="177" spans="2:25" ht="18.75">
+      <c r="B177" s="65"/>
+      <c r="C177" s="63"/>
+      <c r="D177" s="52"/>
+      <c r="E177" s="60"/>
+      <c r="F177" s="8">
+        <v>0.75</v>
+      </c>
+      <c r="G177" s="78"/>
+      <c r="H177" s="79"/>
+      <c r="I177" s="35"/>
+      <c r="J177" s="9" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="K177" s="39"/>
+      <c r="L177" s="39"/>
+      <c r="M177" s="39"/>
+      <c r="N177" s="39"/>
+      <c r="O177" s="39"/>
+      <c r="P177" s="39"/>
+      <c r="Q177" s="39"/>
+      <c r="R177" s="39"/>
+      <c r="S177" s="10">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="T177" s="10">
+        <v>100000</v>
+      </c>
+      <c r="U177" s="10">
+        <f t="shared" ref="U177:U184" si="45">T177*S177</f>
+        <v>0</v>
+      </c>
+      <c r="V177" s="4"/>
+      <c r="W177" s="4"/>
+      <c r="X177" s="11"/>
+      <c r="Y177" s="4"/>
+    </row>
+    <row r="178" spans="2:25" ht="18.75">
+      <c r="B178" s="65"/>
+      <c r="C178" s="63"/>
+      <c r="D178" s="53"/>
+      <c r="E178" s="61"/>
+      <c r="F178" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="G178" s="78"/>
+      <c r="H178" s="79"/>
+      <c r="I178" s="36"/>
+      <c r="J178" s="9" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="K178" s="41"/>
+      <c r="L178" s="41"/>
+      <c r="M178" s="41"/>
+      <c r="N178" s="41"/>
+      <c r="O178" s="41"/>
+      <c r="P178" s="41"/>
+      <c r="Q178" s="41"/>
+      <c r="R178" s="41"/>
+      <c r="S178" s="13">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="T178" s="13">
+        <v>100000</v>
+      </c>
+      <c r="U178" s="13">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="V178" s="4"/>
+      <c r="Y178" s="4"/>
+    </row>
+    <row r="179" spans="2:25" ht="18.75">
+      <c r="B179" s="65"/>
+      <c r="C179" s="63"/>
+      <c r="D179" s="51"/>
+      <c r="E179" s="59" t="s">
+        <v>103</v>
+      </c>
+      <c r="F179" s="5">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="G179" s="73"/>
+      <c r="H179" s="74"/>
+      <c r="I179" s="34"/>
+      <c r="J179" s="6" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="K179" s="38"/>
+      <c r="L179" s="38"/>
+      <c r="M179" s="38"/>
+      <c r="N179" s="38"/>
+      <c r="O179" s="38"/>
+      <c r="P179" s="38"/>
+      <c r="Q179" s="38"/>
+      <c r="R179" s="38"/>
+      <c r="S179" s="7">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="T179" s="7">
+        <v>100000</v>
+      </c>
+      <c r="U179" s="7">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="V179" s="4"/>
+      <c r="Y179" s="4"/>
+    </row>
+    <row r="180" spans="2:25" ht="18.75">
+      <c r="B180" s="65"/>
+      <c r="C180" s="63"/>
+      <c r="D180" s="52"/>
+      <c r="E180" s="60"/>
+      <c r="F180" s="8">
+        <v>1</v>
+      </c>
+      <c r="G180" s="78"/>
+      <c r="H180" s="79"/>
+      <c r="I180" s="35"/>
+      <c r="J180" s="9" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="K180" s="39"/>
+      <c r="L180" s="39"/>
+      <c r="M180" s="39"/>
+      <c r="N180" s="39"/>
+      <c r="O180" s="39"/>
+      <c r="P180" s="39"/>
+      <c r="Q180" s="39"/>
+      <c r="R180" s="39"/>
+      <c r="S180" s="10">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="T180" s="10">
+        <v>100000</v>
+      </c>
+      <c r="U180" s="10">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="V180" s="4"/>
+      <c r="Y180" s="4"/>
+    </row>
+    <row r="181" spans="2:25" ht="18.75">
+      <c r="B181" s="65"/>
+      <c r="C181" s="63"/>
+      <c r="D181" s="52"/>
+      <c r="E181" s="60"/>
+      <c r="F181" s="8">
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="G181" s="78"/>
+      <c r="H181" s="79"/>
+      <c r="I181" s="35"/>
+      <c r="J181" s="9" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="K181" s="39"/>
+      <c r="L181" s="39"/>
+      <c r="M181" s="39"/>
+      <c r="N181" s="39"/>
+      <c r="O181" s="39"/>
+      <c r="P181" s="39"/>
+      <c r="Q181" s="39"/>
+      <c r="R181" s="39"/>
+      <c r="S181" s="10">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="T181" s="10">
+        <v>100000</v>
+      </c>
+      <c r="U181" s="10">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="V181" s="4"/>
+      <c r="Y181" s="4"/>
+    </row>
+    <row r="182" spans="2:25" ht="18.75">
+      <c r="B182" s="65"/>
+      <c r="C182" s="63"/>
+      <c r="D182" s="52"/>
+      <c r="E182" s="60"/>
+      <c r="F182" s="8">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="G182" s="78"/>
+      <c r="H182" s="79"/>
+      <c r="I182" s="35"/>
+      <c r="J182" s="9" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="K182" s="39"/>
+      <c r="L182" s="39"/>
+      <c r="M182" s="39"/>
+      <c r="N182" s="39"/>
+      <c r="O182" s="39"/>
+      <c r="P182" s="39"/>
+      <c r="Q182" s="39"/>
+      <c r="R182" s="39"/>
+      <c r="S182" s="10">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="T182" s="10">
+        <v>100000</v>
+      </c>
+      <c r="U182" s="10">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="V182" s="4"/>
+      <c r="W182" s="4"/>
+      <c r="X182" s="4"/>
+      <c r="Y182" s="4"/>
+    </row>
+    <row r="183" spans="2:25" ht="18.75">
+      <c r="B183" s="65"/>
+      <c r="C183" s="63"/>
+      <c r="D183" s="52"/>
+      <c r="E183" s="60"/>
+      <c r="F183" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="G183" s="78"/>
+      <c r="H183" s="79"/>
+      <c r="I183" s="35"/>
+      <c r="J183" s="9" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="K183" s="39"/>
+      <c r="L183" s="39"/>
+      <c r="M183" s="39"/>
+      <c r="N183" s="39"/>
+      <c r="O183" s="39"/>
+      <c r="P183" s="39"/>
+      <c r="Q183" s="39"/>
+      <c r="R183" s="39"/>
+      <c r="S183" s="10">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="T183" s="10">
+        <v>100000</v>
+      </c>
+      <c r="U183" s="10">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="V183" s="4"/>
+      <c r="Y183" s="4"/>
+    </row>
+    <row r="184" spans="2:25" ht="18.75">
+      <c r="B184" s="65"/>
+      <c r="C184" s="64"/>
+      <c r="D184" s="53"/>
+      <c r="E184" s="91"/>
+      <c r="F184" s="14">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="G184" s="78"/>
+      <c r="H184" s="79"/>
+      <c r="I184" s="37"/>
+      <c r="J184" s="15" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="K184" s="40"/>
+      <c r="L184" s="40"/>
+      <c r="M184" s="40"/>
+      <c r="N184" s="40"/>
+      <c r="O184" s="40"/>
+      <c r="P184" s="40"/>
+      <c r="Q184" s="40"/>
+      <c r="R184" s="40"/>
+      <c r="S184" s="16">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="T184" s="16">
+        <v>100000</v>
+      </c>
+      <c r="U184" s="16">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="V184" s="4"/>
+      <c r="W184" s="4"/>
+      <c r="X184" s="4"/>
+      <c r="Y184" s="4"/>
+    </row>
   </sheetData>
-  <mergeCells count="210">
+  <mergeCells count="242">
+    <mergeCell ref="B173:B184"/>
+    <mergeCell ref="C173:C184"/>
+    <mergeCell ref="E173:E178"/>
+    <mergeCell ref="G173:H173"/>
+    <mergeCell ref="G174:H174"/>
+    <mergeCell ref="G175:H175"/>
+    <mergeCell ref="G176:H176"/>
+    <mergeCell ref="G177:H177"/>
+    <mergeCell ref="G178:H178"/>
+    <mergeCell ref="E179:E184"/>
+    <mergeCell ref="G179:H179"/>
+    <mergeCell ref="G180:H180"/>
+    <mergeCell ref="G181:H181"/>
+    <mergeCell ref="G182:H182"/>
+    <mergeCell ref="G183:H183"/>
+    <mergeCell ref="G184:H184"/>
+    <mergeCell ref="B161:B172"/>
+    <mergeCell ref="C161:C172"/>
+    <mergeCell ref="E161:E166"/>
+    <mergeCell ref="G161:H161"/>
+    <mergeCell ref="G162:H162"/>
+    <mergeCell ref="G163:H163"/>
+    <mergeCell ref="G164:H164"/>
+    <mergeCell ref="G165:H165"/>
+    <mergeCell ref="G166:H166"/>
+    <mergeCell ref="E167:E172"/>
+    <mergeCell ref="G167:H167"/>
+    <mergeCell ref="G168:H168"/>
+    <mergeCell ref="G169:H169"/>
+    <mergeCell ref="G170:H170"/>
+    <mergeCell ref="G171:H171"/>
+    <mergeCell ref="G172:H172"/>
     <mergeCell ref="B149:B160"/>
     <mergeCell ref="C149:C160"/>
     <mergeCell ref="E149:E154"/>
@@ -9022,22 +10149,22 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="6">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E17 E23 E29 E41 E53 E65 E77 E89 E101 E113 E125 E137 E35 E47 E59 E71 E83 E95 E107 E119 E131 E143 E149 E155" xr:uid="{7280530E-5B8D-4438-B3BD-789763083C72}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E17 E23 E29 E41 E53 E65 E77 E89 E101 E113 E125 E137 E35 E47 E59 E71 E83 E95 E107 E119 E131 E143 E149 E155 E161 E167 E173 E179" xr:uid="{7280530E-5B8D-4438-B3BD-789763083C72}">
       <formula1>$X$22:$X$23</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C29 C125 C17 C101 C53 C77 C65 C89 C113 C41 C137 C149" xr:uid="{F1EE940D-722D-49C3-AED8-65AAA48A203D}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C29 C125 C17 C101 C53 C77 C65 C89 C113 C41 C137 C149 C161 C173" xr:uid="{F1EE940D-722D-49C3-AED8-65AAA48A203D}">
       <formula1>$X$17:$X$21</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C6" xr:uid="{6C6BE52D-388A-44ED-8B9B-93682A7F6DD3}">
       <formula1>$X$2:$X$7</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G17:G34 G41:G46 G53:G58 G65:G70 G137:G142 G89:G94 G77:G82 G101:G106 G125:G130 G113:G118 G149:G154" xr:uid="{2F19E784-04BF-4E24-BE04-CB9AC5210FA1}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G17:G34 G41:G46 G53:G58 G65:G70 G149:G154 G89:G94 G77:G82 G101:G106 G125:G130 G113:G118 G137:G142 G161:G166 G173:G178" xr:uid="{2F19E784-04BF-4E24-BE04-CB9AC5210FA1}">
       <formula1>$C$11:$S$11</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D17:D160" xr:uid="{AB6E02A6-3DF0-4EDE-8381-A768F6272CD3}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D17:D184" xr:uid="{AB6E02A6-3DF0-4EDE-8381-A768F6272CD3}">
       <formula1>$Z$21:$Z$61</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G35:H40 G47:H52 G59:H64 G71:H76 G143:H148 G95:H100 G83:H88 G119:H124 G131:H136 G107:H112 G155:H160" xr:uid="{C28E6288-565C-4B22-9955-C46161504448}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G35:H40 G47:H52 G59:H64 G71:H76 G155:H160 G95:H100 G83:H88 G119:H124 G131:H136 G107:H112 G143:H148 G167:H172 G179:H184" xr:uid="{C28E6288-565C-4B22-9955-C46161504448}">
       <formula1>$C$12:$S$12</formula1>
     </dataValidation>
   </dataValidations>
@@ -9047,7 +10174,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10425EB3-9678-42C3-8315-9CCE4CF12B97}">
-  <dimension ref="B1:AU160"/>
+  <dimension ref="B1:AU184"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="4.140625" style="1" customWidth="1"/>
@@ -9149,7 +10276,7 @@
     </row>
     <row r="4" spans="2:47" ht="22.5">
       <c r="B4" s="58" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C4" s="58"/>
       <c r="D4" s="58"/>
@@ -9249,10 +10376,10 @@
         <v>10</v>
       </c>
       <c r="C6" s="42" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D6" s="89" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E6" s="87"/>
       <c r="F6" s="87"/>
@@ -9262,10 +10389,10 @@
       <c r="J6" s="87"/>
       <c r="K6" s="47"/>
       <c r="L6" s="48" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="M6" s="86" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="N6" s="87"/>
       <c r="O6" s="87"/>
@@ -9307,7 +10434,7 @@
     <row r="7" spans="2:47" ht="24.95" customHeight="1">
       <c r="C7" s="3"/>
       <c r="D7" s="88" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E7" s="88"/>
       <c r="F7" s="88"/>
@@ -9318,7 +10445,7 @@
       <c r="K7" s="88"/>
       <c r="L7" s="3"/>
       <c r="M7" s="88" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N7" s="88"/>
       <c r="O7" s="88"/>
@@ -9356,7 +10483,7 @@
     </row>
     <row r="8" spans="2:47" ht="22.5">
       <c r="B8" s="57" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C8" s="58"/>
       <c r="D8" s="58"/>
@@ -9513,10 +10640,10 @@
         <v>81</v>
       </c>
       <c r="K11" s="31" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="L11" s="31" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="M11" s="31"/>
       <c r="N11" s="31"/>
@@ -9572,7 +10699,7 @@
     </row>
     <row r="13" spans="2:47" ht="54.6" customHeight="1">
       <c r="B13" s="90" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C13" s="90"/>
       <c r="D13" s="90"/>
@@ -9639,7 +10766,7 @@
         <v>73</v>
       </c>
       <c r="S14" s="56" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="T14" s="56"/>
       <c r="U14" s="56"/>
@@ -9742,7 +10869,7 @@
       </c>
       <c r="D17" s="51"/>
       <c r="E17" s="59" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F17" s="5">
         <v>0.41666666666666669</v>
@@ -9984,7 +11111,7 @@
       </c>
       <c r="V22" s="4"/>
       <c r="X22" s="54" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="Z22" s="44" t="s">
         <v>46</v>
@@ -9995,7 +11122,7 @@
       <c r="C23" s="63"/>
       <c r="D23" s="51"/>
       <c r="E23" s="59" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F23" s="5">
         <v>0.91666666666666663</v>
@@ -10028,7 +11155,7 @@
       </c>
       <c r="V23" s="4"/>
       <c r="X23" s="54" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="Z23" s="44" t="s">
         <v>45</v>
@@ -10245,7 +11372,7 @@
       </c>
       <c r="D29" s="51"/>
       <c r="E29" s="59" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F29" s="5">
         <v>0.41666666666666669</v>
@@ -10497,7 +11624,7 @@
       <c r="C35" s="63"/>
       <c r="D35" s="51"/>
       <c r="E35" s="59" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F35" s="5">
         <v>0.91666666666666663</v>
@@ -10747,7 +11874,7 @@
       </c>
       <c r="D41" s="51"/>
       <c r="E41" s="59" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F41" s="5">
         <v>0.41666666666666669</v>
@@ -10997,7 +12124,7 @@
         <v>57</v>
       </c>
       <c r="E47" s="59" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F47" s="5">
         <v>0.91666666666666663</v>
@@ -11283,7 +12410,7 @@
         <v>57</v>
       </c>
       <c r="E53" s="59" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F53" s="5">
         <v>0.41666666666666669</v>
@@ -11573,7 +12700,7 @@
         <v>57</v>
       </c>
       <c r="E59" s="59" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F59" s="5">
         <v>0.91666666666666663</v>
@@ -11846,7 +12973,7 @@
         <v>57</v>
       </c>
       <c r="E65" s="59" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F65" s="5">
         <v>0.41666666666666669</v>
@@ -12122,7 +13249,7 @@
         <v>57</v>
       </c>
       <c r="E71" s="59" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F71" s="5">
         <v>0.91666666666666663</v>
@@ -12402,7 +13529,7 @@
         <v>57</v>
       </c>
       <c r="E77" s="59" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F77" s="5">
         <v>0.41666666666666669</v>
@@ -12676,7 +13803,7 @@
         <v>57</v>
       </c>
       <c r="E83" s="59" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F83" s="5">
         <v>0.91666666666666663</v>
@@ -12956,7 +14083,7 @@
         <v>58</v>
       </c>
       <c r="E89" s="59" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F89" s="5">
         <v>0.41666666666666669</v>
@@ -13226,7 +14353,7 @@
         <v>58</v>
       </c>
       <c r="E95" s="59" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F95" s="5">
         <v>0.91666666666666663</v>
@@ -13496,7 +14623,7 @@
       </c>
       <c r="D101" s="51"/>
       <c r="E101" s="59" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F101" s="5">
         <v>0.41666666666666669</v>
@@ -13730,7 +14857,7 @@
       <c r="C107" s="63"/>
       <c r="D107" s="51"/>
       <c r="E107" s="59" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F107" s="5">
         <v>0.91666666666666663</v>
@@ -13962,7 +15089,7 @@
       </c>
       <c r="D113" s="51"/>
       <c r="E113" s="59" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F113" s="5">
         <v>0.41666666666666669</v>
@@ -14196,7 +15323,7 @@
       <c r="C119" s="63"/>
       <c r="D119" s="51"/>
       <c r="E119" s="59" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F119" s="5">
         <v>0.91666666666666663</v>
@@ -14428,7 +15555,7 @@
       </c>
       <c r="D125" s="51"/>
       <c r="E125" s="59" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F125" s="5">
         <v>0.41666666666666669</v>
@@ -14662,7 +15789,7 @@
       <c r="C131" s="63"/>
       <c r="D131" s="51"/>
       <c r="E131" s="59" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F131" s="5">
         <v>0.91666666666666663</v>
@@ -14894,7 +16021,7 @@
       </c>
       <c r="D137" s="51"/>
       <c r="E137" s="59" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F137" s="5">
         <v>0.41666666666666669</v>
@@ -14972,17 +16099,23 @@
     <row r="139" spans="2:25" ht="18.75">
       <c r="B139" s="65"/>
       <c r="C139" s="63"/>
-      <c r="D139" s="52"/>
+      <c r="D139" s="52" t="s">
+        <v>58</v>
+      </c>
       <c r="E139" s="60"/>
       <c r="F139" s="8">
         <v>0.58333333333333337</v>
       </c>
-      <c r="G139" s="78"/>
+      <c r="G139" s="78" t="s">
+        <v>77</v>
+      </c>
       <c r="H139" s="79"/>
-      <c r="I139" s="35"/>
-      <c r="J139" s="9" t="str">
+      <c r="I139" s="35">
+        <v>36</v>
+      </c>
+      <c r="J139" s="9">
         <f t="shared" si="31"/>
-        <v/>
+        <v>0.19444444444444445</v>
       </c>
       <c r="K139" s="39"/>
       <c r="L139" s="39"/>
@@ -14990,18 +16123,20 @@
       <c r="N139" s="39"/>
       <c r="O139" s="39"/>
       <c r="P139" s="39"/>
-      <c r="Q139" s="39"/>
+      <c r="Q139" s="39">
+        <v>7</v>
+      </c>
       <c r="R139" s="39"/>
       <c r="S139" s="10">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="T139" s="10">
         <v>100000</v>
       </c>
       <c r="U139" s="10">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>700000</v>
       </c>
       <c r="V139" s="4"/>
       <c r="W139" s="4"/>
@@ -15011,17 +16146,23 @@
     <row r="140" spans="2:25" ht="18.75">
       <c r="B140" s="65"/>
       <c r="C140" s="63"/>
-      <c r="D140" s="52"/>
+      <c r="D140" s="52" t="s">
+        <v>58</v>
+      </c>
       <c r="E140" s="60"/>
       <c r="F140" s="8">
         <v>0.66666666666666663</v>
       </c>
-      <c r="G140" s="78"/>
+      <c r="G140" s="78" t="s">
+        <v>77</v>
+      </c>
       <c r="H140" s="79"/>
-      <c r="I140" s="35"/>
-      <c r="J140" s="9" t="str">
+      <c r="I140" s="35">
+        <v>68</v>
+      </c>
+      <c r="J140" s="9">
         <f t="shared" si="31"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K140" s="39"/>
       <c r="L140" s="39"/>
@@ -15050,17 +16191,23 @@
     <row r="141" spans="2:25" ht="18.75">
       <c r="B141" s="65"/>
       <c r="C141" s="63"/>
-      <c r="D141" s="52"/>
+      <c r="D141" s="52" t="s">
+        <v>58</v>
+      </c>
       <c r="E141" s="60"/>
       <c r="F141" s="8">
         <v>0.75</v>
       </c>
-      <c r="G141" s="78"/>
+      <c r="G141" s="78" t="s">
+        <v>77</v>
+      </c>
       <c r="H141" s="79"/>
-      <c r="I141" s="35"/>
-      <c r="J141" s="9" t="str">
+      <c r="I141" s="35">
+        <v>68</v>
+      </c>
+      <c r="J141" s="9">
         <f t="shared" si="31"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K141" s="39"/>
       <c r="L141" s="39"/>
@@ -15089,17 +16236,23 @@
     <row r="142" spans="2:25" ht="18.75">
       <c r="B142" s="65"/>
       <c r="C142" s="63"/>
-      <c r="D142" s="53"/>
+      <c r="D142" s="53" t="s">
+        <v>58</v>
+      </c>
       <c r="E142" s="61"/>
       <c r="F142" s="12">
         <v>0.83333333333333337</v>
       </c>
-      <c r="G142" s="78"/>
+      <c r="G142" s="78" t="s">
+        <v>77</v>
+      </c>
       <c r="H142" s="79"/>
-      <c r="I142" s="36"/>
-      <c r="J142" s="9" t="str">
+      <c r="I142" s="36">
+        <v>68</v>
+      </c>
+      <c r="J142" s="9">
         <f t="shared" si="31"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K142" s="41"/>
       <c r="L142" s="41"/>
@@ -15126,21 +16279,29 @@
     <row r="143" spans="2:25" ht="18.75">
       <c r="B143" s="65"/>
       <c r="C143" s="63"/>
-      <c r="D143" s="51"/>
+      <c r="D143" s="51" t="s">
+        <v>58</v>
+      </c>
       <c r="E143" s="59" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F143" s="5">
         <v>0.91666666666666663</v>
       </c>
-      <c r="G143" s="73"/>
+      <c r="G143" s="73" t="s">
+        <v>84</v>
+      </c>
       <c r="H143" s="74"/>
-      <c r="I143" s="34"/>
-      <c r="J143" s="6" t="str">
+      <c r="I143" s="34">
+        <v>64</v>
+      </c>
+      <c r="J143" s="6">
         <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="K143" s="38"/>
+        <v>3.125E-2</v>
+      </c>
+      <c r="K143" s="38">
+        <v>2</v>
+      </c>
       <c r="L143" s="38"/>
       <c r="M143" s="38"/>
       <c r="N143" s="38"/>
@@ -15150,14 +16311,14 @@
       <c r="R143" s="38"/>
       <c r="S143" s="7">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T143" s="7">
         <v>100000</v>
       </c>
       <c r="U143" s="7">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="V143" s="4"/>
       <c r="Y143" s="4"/>
@@ -15165,19 +16326,27 @@
     <row r="144" spans="2:25" ht="18.75">
       <c r="B144" s="65"/>
       <c r="C144" s="63"/>
-      <c r="D144" s="52"/>
+      <c r="D144" s="52" t="s">
+        <v>58</v>
+      </c>
       <c r="E144" s="60"/>
       <c r="F144" s="8">
         <v>1</v>
       </c>
-      <c r="G144" s="78"/>
+      <c r="G144" s="78" t="s">
+        <v>84</v>
+      </c>
       <c r="H144" s="79"/>
-      <c r="I144" s="35"/>
-      <c r="J144" s="9" t="str">
+      <c r="I144" s="35">
+        <v>64</v>
+      </c>
+      <c r="J144" s="9">
         <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="K144" s="39"/>
+        <v>3.125E-2</v>
+      </c>
+      <c r="K144" s="39">
+        <v>2</v>
+      </c>
       <c r="L144" s="39"/>
       <c r="M144" s="39"/>
       <c r="N144" s="39"/>
@@ -15187,14 +16356,14 @@
       <c r="R144" s="39"/>
       <c r="S144" s="10">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T144" s="10">
         <v>100000</v>
       </c>
       <c r="U144" s="10">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="V144" s="4"/>
       <c r="Y144" s="4"/>
@@ -15202,19 +16371,27 @@
     <row r="145" spans="2:25" ht="18.75">
       <c r="B145" s="65"/>
       <c r="C145" s="63"/>
-      <c r="D145" s="52"/>
+      <c r="D145" s="52" t="s">
+        <v>58</v>
+      </c>
       <c r="E145" s="60"/>
       <c r="F145" s="8">
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="G145" s="78"/>
+      <c r="G145" s="78" t="s">
+        <v>84</v>
+      </c>
       <c r="H145" s="79"/>
-      <c r="I145" s="35"/>
-      <c r="J145" s="9" t="str">
+      <c r="I145" s="35">
+        <v>64</v>
+      </c>
+      <c r="J145" s="9">
         <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="K145" s="39"/>
+        <v>3.125E-2</v>
+      </c>
+      <c r="K145" s="39">
+        <v>2</v>
+      </c>
       <c r="L145" s="39"/>
       <c r="M145" s="39"/>
       <c r="N145" s="39"/>
@@ -15224,14 +16401,14 @@
       <c r="R145" s="39"/>
       <c r="S145" s="10">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T145" s="10">
         <v>100000</v>
       </c>
       <c r="U145" s="10">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="V145" s="4"/>
       <c r="Y145" s="4"/>
@@ -15239,17 +16416,23 @@
     <row r="146" spans="2:25" ht="18.75">
       <c r="B146" s="65"/>
       <c r="C146" s="63"/>
-      <c r="D146" s="52"/>
+      <c r="D146" s="52" t="s">
+        <v>58</v>
+      </c>
       <c r="E146" s="60"/>
       <c r="F146" s="8">
         <v>0.16666666666666666</v>
       </c>
-      <c r="G146" s="78"/>
+      <c r="G146" s="78" t="s">
+        <v>84</v>
+      </c>
       <c r="H146" s="79"/>
-      <c r="I146" s="35"/>
-      <c r="J146" s="9" t="str">
+      <c r="I146" s="35">
+        <v>64</v>
+      </c>
+      <c r="J146" s="9">
         <f t="shared" si="31"/>
-        <v/>
+        <v>3.125E-2</v>
       </c>
       <c r="K146" s="39"/>
       <c r="L146" s="39"/>
@@ -15258,17 +16441,19 @@
       <c r="O146" s="39"/>
       <c r="P146" s="39"/>
       <c r="Q146" s="39"/>
-      <c r="R146" s="39"/>
+      <c r="R146" s="39">
+        <v>2</v>
+      </c>
       <c r="S146" s="10">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T146" s="10">
         <v>100000</v>
       </c>
       <c r="U146" s="10">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="V146" s="4"/>
       <c r="W146" s="4"/>
@@ -15278,17 +16463,23 @@
     <row r="147" spans="2:25" ht="18.75">
       <c r="B147" s="65"/>
       <c r="C147" s="63"/>
-      <c r="D147" s="52"/>
+      <c r="D147" s="52" t="s">
+        <v>58</v>
+      </c>
       <c r="E147" s="60"/>
       <c r="F147" s="8">
         <v>0.25</v>
       </c>
-      <c r="G147" s="78"/>
+      <c r="G147" s="78" t="s">
+        <v>84</v>
+      </c>
       <c r="H147" s="79"/>
-      <c r="I147" s="35"/>
-      <c r="J147" s="9" t="str">
+      <c r="I147" s="35">
+        <v>64</v>
+      </c>
+      <c r="J147" s="9">
         <f t="shared" si="31"/>
-        <v/>
+        <v>3.125E-2</v>
       </c>
       <c r="K147" s="39"/>
       <c r="L147" s="39"/>
@@ -15297,17 +16488,19 @@
       <c r="O147" s="39"/>
       <c r="P147" s="39"/>
       <c r="Q147" s="39"/>
-      <c r="R147" s="39"/>
+      <c r="R147" s="39">
+        <v>2</v>
+      </c>
       <c r="S147" s="10">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T147" s="10">
         <v>100000</v>
       </c>
       <c r="U147" s="10">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="V147" s="4"/>
       <c r="Y147" s="4"/>
@@ -15315,19 +16508,27 @@
     <row r="148" spans="2:25" ht="18.75">
       <c r="B148" s="65"/>
       <c r="C148" s="64"/>
-      <c r="D148" s="53"/>
+      <c r="D148" s="53" t="s">
+        <v>58</v>
+      </c>
       <c r="E148" s="91"/>
       <c r="F148" s="14">
         <v>0.33333333333333331</v>
       </c>
-      <c r="G148" s="78"/>
+      <c r="G148" s="78" t="s">
+        <v>84</v>
+      </c>
       <c r="H148" s="79"/>
-      <c r="I148" s="37"/>
-      <c r="J148" s="15" t="str">
+      <c r="I148" s="37">
+        <v>64</v>
+      </c>
+      <c r="J148" s="15">
         <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="K148" s="40"/>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="K148" s="40">
+        <v>1</v>
+      </c>
       <c r="L148" s="40"/>
       <c r="M148" s="40"/>
       <c r="N148" s="40"/>
@@ -15337,14 +16538,14 @@
       <c r="R148" s="40"/>
       <c r="S148" s="16">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T148" s="16">
         <v>100000</v>
       </c>
       <c r="U148" s="16">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="V148" s="4"/>
       <c r="W148" s="4"/>
@@ -15358,14 +16559,18 @@
       <c r="C149" s="62" t="s">
         <v>15</v>
       </c>
-      <c r="D149" s="51"/>
+      <c r="D149" s="51" t="s">
+        <v>46</v>
+      </c>
       <c r="E149" s="59" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F149" s="5">
         <v>0.41666666666666669</v>
       </c>
-      <c r="G149" s="73"/>
+      <c r="G149" s="73" t="s">
+        <v>81</v>
+      </c>
       <c r="H149" s="74"/>
       <c r="I149" s="34"/>
       <c r="J149" s="6" t="str">
@@ -15399,12 +16604,16 @@
     <row r="150" spans="2:25" ht="18.75">
       <c r="B150" s="65"/>
       <c r="C150" s="63"/>
-      <c r="D150" s="52"/>
+      <c r="D150" s="52" t="s">
+        <v>46</v>
+      </c>
       <c r="E150" s="60"/>
       <c r="F150" s="8">
         <v>0.5</v>
       </c>
-      <c r="G150" s="78"/>
+      <c r="G150" s="78" t="s">
+        <v>81</v>
+      </c>
       <c r="H150" s="79"/>
       <c r="I150" s="35"/>
       <c r="J150" s="9" t="str">
@@ -15438,12 +16647,16 @@
     <row r="151" spans="2:25" ht="18.75">
       <c r="B151" s="65"/>
       <c r="C151" s="63"/>
-      <c r="D151" s="52"/>
+      <c r="D151" s="52" t="s">
+        <v>46</v>
+      </c>
       <c r="E151" s="60"/>
       <c r="F151" s="8">
         <v>0.58333333333333337</v>
       </c>
-      <c r="G151" s="78"/>
+      <c r="G151" s="78" t="s">
+        <v>81</v>
+      </c>
       <c r="H151" s="79"/>
       <c r="I151" s="35"/>
       <c r="J151" s="9" t="str">
@@ -15477,17 +16690,23 @@
     <row r="152" spans="2:25" ht="18.75">
       <c r="B152" s="65"/>
       <c r="C152" s="63"/>
-      <c r="D152" s="52"/>
+      <c r="D152" s="52" t="s">
+        <v>46</v>
+      </c>
       <c r="E152" s="60"/>
       <c r="F152" s="8">
         <v>0.66666666666666663</v>
       </c>
-      <c r="G152" s="78"/>
+      <c r="G152" s="78" t="s">
+        <v>81</v>
+      </c>
       <c r="H152" s="79"/>
-      <c r="I152" s="35"/>
-      <c r="J152" s="9" t="str">
+      <c r="I152" s="35">
+        <v>14</v>
+      </c>
+      <c r="J152" s="9">
         <f t="shared" si="35"/>
-        <v/>
+        <v>0.9285714285714286</v>
       </c>
       <c r="K152" s="39"/>
       <c r="L152" s="39"/>
@@ -15495,18 +16714,20 @@
       <c r="N152" s="39"/>
       <c r="O152" s="39"/>
       <c r="P152" s="39"/>
-      <c r="Q152" s="39"/>
+      <c r="Q152" s="39">
+        <v>13</v>
+      </c>
       <c r="R152" s="39"/>
       <c r="S152" s="10">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="T152" s="10">
         <v>100000</v>
       </c>
       <c r="U152" s="10">
         <f>T152*S152</f>
-        <v>0</v>
+        <v>1300000</v>
       </c>
       <c r="V152" s="4"/>
       <c r="W152" s="4"/>
@@ -15516,36 +16737,46 @@
     <row r="153" spans="2:25" ht="18.75">
       <c r="B153" s="65"/>
       <c r="C153" s="63"/>
-      <c r="D153" s="52"/>
+      <c r="D153" s="52" t="s">
+        <v>46</v>
+      </c>
       <c r="E153" s="60"/>
       <c r="F153" s="8">
         <v>0.75</v>
       </c>
-      <c r="G153" s="78"/>
+      <c r="G153" s="78" t="s">
+        <v>81</v>
+      </c>
       <c r="H153" s="79"/>
-      <c r="I153" s="35"/>
-      <c r="J153" s="9" t="str">
+      <c r="I153" s="35">
+        <v>80</v>
+      </c>
+      <c r="J153" s="9">
         <f t="shared" si="35"/>
-        <v/>
+        <v>0.2</v>
       </c>
       <c r="K153" s="39"/>
       <c r="L153" s="39"/>
-      <c r="M153" s="39"/>
+      <c r="M153" s="39">
+        <v>4</v>
+      </c>
       <c r="N153" s="39"/>
       <c r="O153" s="39"/>
       <c r="P153" s="39"/>
       <c r="Q153" s="39"/>
-      <c r="R153" s="39"/>
+      <c r="R153" s="39">
+        <v>12</v>
+      </c>
       <c r="S153" s="10">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="T153" s="10">
         <v>100000</v>
       </c>
       <c r="U153" s="10">
         <f t="shared" ref="U153:U160" si="38">T153*S153</f>
-        <v>0</v>
+        <v>1600000</v>
       </c>
       <c r="V153" s="4"/>
       <c r="W153" s="4"/>
@@ -15555,17 +16786,23 @@
     <row r="154" spans="2:25" ht="18.75">
       <c r="B154" s="65"/>
       <c r="C154" s="63"/>
-      <c r="D154" s="53"/>
+      <c r="D154" s="53" t="s">
+        <v>46</v>
+      </c>
       <c r="E154" s="61"/>
       <c r="F154" s="12">
         <v>0.83333333333333337</v>
       </c>
-      <c r="G154" s="78"/>
+      <c r="G154" s="78" t="s">
+        <v>81</v>
+      </c>
       <c r="H154" s="79"/>
-      <c r="I154" s="36"/>
-      <c r="J154" s="9" t="str">
+      <c r="I154" s="36">
+        <v>20</v>
+      </c>
+      <c r="J154" s="9">
         <f t="shared" si="35"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K154" s="41"/>
       <c r="L154" s="41"/>
@@ -15592,23 +16829,31 @@
     <row r="155" spans="2:25" ht="18.75">
       <c r="B155" s="65"/>
       <c r="C155" s="63"/>
-      <c r="D155" s="51"/>
+      <c r="D155" s="51" t="s">
+        <v>46</v>
+      </c>
       <c r="E155" s="59" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F155" s="5">
         <v>0.91666666666666663</v>
       </c>
-      <c r="G155" s="73"/>
+      <c r="G155" s="73" t="s">
+        <v>83</v>
+      </c>
       <c r="H155" s="74"/>
-      <c r="I155" s="34"/>
-      <c r="J155" s="6" t="str">
+      <c r="I155" s="34">
+        <v>76</v>
+      </c>
+      <c r="J155" s="6">
         <f t="shared" si="35"/>
-        <v/>
+        <v>2.6315789473684209E-2</v>
       </c>
       <c r="K155" s="38"/>
       <c r="L155" s="38"/>
-      <c r="M155" s="38"/>
+      <c r="M155" s="38">
+        <v>2</v>
+      </c>
       <c r="N155" s="38"/>
       <c r="O155" s="38"/>
       <c r="P155" s="38"/>
@@ -15616,14 +16861,14 @@
       <c r="R155" s="38"/>
       <c r="S155" s="7">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T155" s="7">
         <v>100000</v>
       </c>
       <c r="U155" s="7">
         <f t="shared" si="38"/>
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="V155" s="4"/>
       <c r="Y155" s="4"/>
@@ -15631,21 +16876,29 @@
     <row r="156" spans="2:25" ht="18.75">
       <c r="B156" s="65"/>
       <c r="C156" s="63"/>
-      <c r="D156" s="52"/>
+      <c r="D156" s="52" t="s">
+        <v>46</v>
+      </c>
       <c r="E156" s="60"/>
       <c r="F156" s="8">
         <v>1</v>
       </c>
-      <c r="G156" s="78"/>
+      <c r="G156" s="78" t="s">
+        <v>83</v>
+      </c>
       <c r="H156" s="79"/>
-      <c r="I156" s="35"/>
-      <c r="J156" s="9" t="str">
+      <c r="I156" s="35">
+        <v>76</v>
+      </c>
+      <c r="J156" s="9">
         <f t="shared" si="35"/>
-        <v/>
+        <v>2.6315789473684209E-2</v>
       </c>
       <c r="K156" s="39"/>
       <c r="L156" s="39"/>
-      <c r="M156" s="39"/>
+      <c r="M156" s="39">
+        <v>2</v>
+      </c>
       <c r="N156" s="39"/>
       <c r="O156" s="39"/>
       <c r="P156" s="39"/>
@@ -15653,14 +16906,14 @@
       <c r="R156" s="39"/>
       <c r="S156" s="10">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T156" s="10">
         <v>100000</v>
       </c>
       <c r="U156" s="10">
         <f t="shared" si="38"/>
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="V156" s="4"/>
       <c r="Y156" s="4"/>
@@ -15668,21 +16921,29 @@
     <row r="157" spans="2:25" ht="18.75">
       <c r="B157" s="65"/>
       <c r="C157" s="63"/>
-      <c r="D157" s="52"/>
+      <c r="D157" s="52" t="s">
+        <v>46</v>
+      </c>
       <c r="E157" s="60"/>
       <c r="F157" s="8">
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="G157" s="78"/>
+      <c r="G157" s="78" t="s">
+        <v>83</v>
+      </c>
       <c r="H157" s="79"/>
-      <c r="I157" s="35"/>
-      <c r="J157" s="9" t="str">
+      <c r="I157" s="35">
+        <v>76</v>
+      </c>
+      <c r="J157" s="9">
         <f t="shared" si="35"/>
-        <v/>
+        <v>2.6315789473684209E-2</v>
       </c>
       <c r="K157" s="39"/>
       <c r="L157" s="39"/>
-      <c r="M157" s="39"/>
+      <c r="M157" s="39">
+        <v>2</v>
+      </c>
       <c r="N157" s="39"/>
       <c r="O157" s="39"/>
       <c r="P157" s="39"/>
@@ -15690,14 +16951,14 @@
       <c r="R157" s="39"/>
       <c r="S157" s="10">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T157" s="10">
         <v>100000</v>
       </c>
       <c r="U157" s="10">
         <f t="shared" si="38"/>
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="V157" s="4"/>
       <c r="Y157" s="4"/>
@@ -15705,21 +16966,29 @@
     <row r="158" spans="2:25" ht="18.75">
       <c r="B158" s="65"/>
       <c r="C158" s="63"/>
-      <c r="D158" s="52"/>
+      <c r="D158" s="52" t="s">
+        <v>46</v>
+      </c>
       <c r="E158" s="60"/>
       <c r="F158" s="8">
         <v>0.16666666666666666</v>
       </c>
-      <c r="G158" s="78"/>
+      <c r="G158" s="78" t="s">
+        <v>83</v>
+      </c>
       <c r="H158" s="79"/>
-      <c r="I158" s="35"/>
-      <c r="J158" s="9" t="str">
+      <c r="I158" s="35">
+        <v>76</v>
+      </c>
+      <c r="J158" s="9">
         <f t="shared" si="35"/>
-        <v/>
+        <v>2.6315789473684209E-2</v>
       </c>
       <c r="K158" s="39"/>
       <c r="L158" s="39"/>
-      <c r="M158" s="39"/>
+      <c r="M158" s="39">
+        <v>2</v>
+      </c>
       <c r="N158" s="39"/>
       <c r="O158" s="39"/>
       <c r="P158" s="39"/>
@@ -15727,14 +16996,14 @@
       <c r="R158" s="39"/>
       <c r="S158" s="10">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T158" s="10">
         <v>100000</v>
       </c>
       <c r="U158" s="10">
         <f t="shared" si="38"/>
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="V158" s="4"/>
       <c r="W158" s="4"/>
@@ -15744,21 +17013,29 @@
     <row r="159" spans="2:25" ht="18.75">
       <c r="B159" s="65"/>
       <c r="C159" s="63"/>
-      <c r="D159" s="52"/>
+      <c r="D159" s="52" t="s">
+        <v>46</v>
+      </c>
       <c r="E159" s="60"/>
       <c r="F159" s="8">
         <v>0.25</v>
       </c>
-      <c r="G159" s="78"/>
+      <c r="G159" s="78" t="s">
+        <v>83</v>
+      </c>
       <c r="H159" s="79"/>
-      <c r="I159" s="35"/>
-      <c r="J159" s="9" t="str">
+      <c r="I159" s="35">
+        <v>76</v>
+      </c>
+      <c r="J159" s="9">
         <f t="shared" si="35"/>
-        <v/>
+        <v>2.6315789473684209E-2</v>
       </c>
       <c r="K159" s="39"/>
       <c r="L159" s="39"/>
-      <c r="M159" s="39"/>
+      <c r="M159" s="39">
+        <v>2</v>
+      </c>
       <c r="N159" s="39"/>
       <c r="O159" s="39"/>
       <c r="P159" s="39"/>
@@ -15766,14 +17043,14 @@
       <c r="R159" s="39"/>
       <c r="S159" s="10">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T159" s="10">
         <v>100000</v>
       </c>
       <c r="U159" s="10">
         <f t="shared" si="38"/>
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="V159" s="4"/>
       <c r="Y159" s="4"/>
@@ -15781,17 +17058,23 @@
     <row r="160" spans="2:25" ht="18.75">
       <c r="B160" s="65"/>
       <c r="C160" s="64"/>
-      <c r="D160" s="53"/>
+      <c r="D160" s="53" t="s">
+        <v>46</v>
+      </c>
       <c r="E160" s="91"/>
       <c r="F160" s="14">
         <v>0.33333333333333331</v>
       </c>
-      <c r="G160" s="78"/>
+      <c r="G160" s="78" t="s">
+        <v>83</v>
+      </c>
       <c r="H160" s="79"/>
-      <c r="I160" s="37"/>
-      <c r="J160" s="15" t="str">
+      <c r="I160" s="37">
+        <v>76</v>
+      </c>
+      <c r="J160" s="15">
         <f t="shared" si="35"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K160" s="40"/>
       <c r="L160" s="40"/>
@@ -15817,8 +17100,972 @@
       <c r="X160" s="4"/>
       <c r="Y160" s="4"/>
     </row>
+    <row r="161" spans="2:25" ht="16.5" customHeight="1">
+      <c r="B161" s="65">
+        <v>46094</v>
+      </c>
+      <c r="C161" s="62" t="s">
+        <v>15</v>
+      </c>
+      <c r="D161" s="51"/>
+      <c r="E161" s="59" t="s">
+        <v>102</v>
+      </c>
+      <c r="F161" s="5">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="G161" s="73"/>
+      <c r="H161" s="74"/>
+      <c r="I161" s="34"/>
+      <c r="J161" s="6" t="str">
+        <f t="shared" ref="J161:J184" si="39">IFERROR(S161/I161,"")</f>
+        <v/>
+      </c>
+      <c r="K161" s="38"/>
+      <c r="L161" s="38"/>
+      <c r="M161" s="38"/>
+      <c r="N161" s="38"/>
+      <c r="O161" s="38"/>
+      <c r="P161" s="38"/>
+      <c r="Q161" s="38"/>
+      <c r="R161" s="38"/>
+      <c r="S161" s="7">
+        <f>SUM(K161:R161)</f>
+        <v>0</v>
+      </c>
+      <c r="T161" s="7">
+        <v>100000</v>
+      </c>
+      <c r="U161" s="7">
+        <f>T161*S161</f>
+        <v>0</v>
+      </c>
+      <c r="V161" s="4"/>
+      <c r="W161" s="4"/>
+      <c r="X161" s="4"/>
+      <c r="Y161" s="4"/>
+    </row>
+    <row r="162" spans="2:25" ht="18.75">
+      <c r="B162" s="65"/>
+      <c r="C162" s="63"/>
+      <c r="D162" s="52"/>
+      <c r="E162" s="60"/>
+      <c r="F162" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="G162" s="78"/>
+      <c r="H162" s="79"/>
+      <c r="I162" s="35"/>
+      <c r="J162" s="9" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="K162" s="39"/>
+      <c r="L162" s="39"/>
+      <c r="M162" s="39"/>
+      <c r="N162" s="39"/>
+      <c r="O162" s="39"/>
+      <c r="P162" s="39"/>
+      <c r="Q162" s="39"/>
+      <c r="R162" s="39"/>
+      <c r="S162" s="10">
+        <f t="shared" ref="S162:S172" si="40">SUM(K162:R162)</f>
+        <v>0</v>
+      </c>
+      <c r="T162" s="10">
+        <v>100000</v>
+      </c>
+      <c r="U162" s="10">
+        <f t="shared" ref="U162:U163" si="41">T162*S162</f>
+        <v>0</v>
+      </c>
+      <c r="V162" s="4"/>
+      <c r="W162" s="4"/>
+      <c r="X162" s="4"/>
+      <c r="Y162" s="4"/>
+    </row>
+    <row r="163" spans="2:25" ht="18.75">
+      <c r="B163" s="65"/>
+      <c r="C163" s="63"/>
+      <c r="D163" s="52"/>
+      <c r="E163" s="60"/>
+      <c r="F163" s="8">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="G163" s="78"/>
+      <c r="H163" s="79"/>
+      <c r="I163" s="35"/>
+      <c r="J163" s="9" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="K163" s="39"/>
+      <c r="L163" s="39"/>
+      <c r="M163" s="39"/>
+      <c r="N163" s="39"/>
+      <c r="O163" s="39"/>
+      <c r="P163" s="39"/>
+      <c r="Q163" s="39"/>
+      <c r="R163" s="39"/>
+      <c r="S163" s="10">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="T163" s="10">
+        <v>100000</v>
+      </c>
+      <c r="U163" s="10">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="V163" s="4"/>
+      <c r="W163" s="4"/>
+      <c r="X163" s="4"/>
+      <c r="Y163" s="4"/>
+    </row>
+    <row r="164" spans="2:25" ht="18.75">
+      <c r="B164" s="65"/>
+      <c r="C164" s="63"/>
+      <c r="D164" s="52"/>
+      <c r="E164" s="60"/>
+      <c r="F164" s="8">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="G164" s="78"/>
+      <c r="H164" s="79"/>
+      <c r="I164" s="35"/>
+      <c r="J164" s="9" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="K164" s="39"/>
+      <c r="L164" s="39"/>
+      <c r="M164" s="39"/>
+      <c r="N164" s="39"/>
+      <c r="O164" s="39"/>
+      <c r="P164" s="39"/>
+      <c r="Q164" s="39"/>
+      <c r="R164" s="39"/>
+      <c r="S164" s="10">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="T164" s="10">
+        <v>100000</v>
+      </c>
+      <c r="U164" s="10">
+        <f>T164*S164</f>
+        <v>0</v>
+      </c>
+      <c r="V164" s="4"/>
+      <c r="W164" s="4"/>
+      <c r="X164" s="4"/>
+      <c r="Y164" s="4"/>
+    </row>
+    <row r="165" spans="2:25" ht="18.75">
+      <c r="B165" s="65"/>
+      <c r="C165" s="63"/>
+      <c r="D165" s="52"/>
+      <c r="E165" s="60"/>
+      <c r="F165" s="8">
+        <v>0.75</v>
+      </c>
+      <c r="G165" s="78"/>
+      <c r="H165" s="79"/>
+      <c r="I165" s="35"/>
+      <c r="J165" s="9" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="K165" s="39"/>
+      <c r="L165" s="39"/>
+      <c r="M165" s="39"/>
+      <c r="N165" s="39"/>
+      <c r="O165" s="39"/>
+      <c r="P165" s="39"/>
+      <c r="Q165" s="39"/>
+      <c r="R165" s="39"/>
+      <c r="S165" s="10">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="T165" s="10">
+        <v>100000</v>
+      </c>
+      <c r="U165" s="10">
+        <f t="shared" ref="U165:U172" si="42">T165*S165</f>
+        <v>0</v>
+      </c>
+      <c r="V165" s="4"/>
+      <c r="W165" s="4"/>
+      <c r="X165" s="11"/>
+      <c r="Y165" s="4"/>
+    </row>
+    <row r="166" spans="2:25" ht="18.75">
+      <c r="B166" s="65"/>
+      <c r="C166" s="63"/>
+      <c r="D166" s="53"/>
+      <c r="E166" s="61"/>
+      <c r="F166" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="G166" s="78"/>
+      <c r="H166" s="79"/>
+      <c r="I166" s="36"/>
+      <c r="J166" s="9" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="K166" s="41"/>
+      <c r="L166" s="41"/>
+      <c r="M166" s="41"/>
+      <c r="N166" s="41"/>
+      <c r="O166" s="41"/>
+      <c r="P166" s="41"/>
+      <c r="Q166" s="41"/>
+      <c r="R166" s="41"/>
+      <c r="S166" s="13">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="T166" s="13">
+        <v>100000</v>
+      </c>
+      <c r="U166" s="13">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="V166" s="4"/>
+      <c r="Y166" s="4"/>
+    </row>
+    <row r="167" spans="2:25" ht="18.75">
+      <c r="B167" s="65"/>
+      <c r="C167" s="63"/>
+      <c r="D167" s="51"/>
+      <c r="E167" s="59" t="s">
+        <v>103</v>
+      </c>
+      <c r="F167" s="5">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="G167" s="73"/>
+      <c r="H167" s="74"/>
+      <c r="I167" s="34"/>
+      <c r="J167" s="6" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="K167" s="38"/>
+      <c r="L167" s="38"/>
+      <c r="M167" s="38"/>
+      <c r="N167" s="38"/>
+      <c r="O167" s="38"/>
+      <c r="P167" s="38"/>
+      <c r="Q167" s="38"/>
+      <c r="R167" s="38"/>
+      <c r="S167" s="7">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="T167" s="7">
+        <v>100000</v>
+      </c>
+      <c r="U167" s="7">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="V167" s="4"/>
+      <c r="Y167" s="4"/>
+    </row>
+    <row r="168" spans="2:25" ht="18.75">
+      <c r="B168" s="65"/>
+      <c r="C168" s="63"/>
+      <c r="D168" s="52"/>
+      <c r="E168" s="60"/>
+      <c r="F168" s="8">
+        <v>1</v>
+      </c>
+      <c r="G168" s="78"/>
+      <c r="H168" s="79"/>
+      <c r="I168" s="35"/>
+      <c r="J168" s="9" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="K168" s="39"/>
+      <c r="L168" s="39"/>
+      <c r="M168" s="39"/>
+      <c r="N168" s="39"/>
+      <c r="O168" s="39"/>
+      <c r="P168" s="39"/>
+      <c r="Q168" s="39"/>
+      <c r="R168" s="39"/>
+      <c r="S168" s="10">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="T168" s="10">
+        <v>100000</v>
+      </c>
+      <c r="U168" s="10">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="V168" s="4"/>
+      <c r="Y168" s="4"/>
+    </row>
+    <row r="169" spans="2:25" ht="18.75">
+      <c r="B169" s="65"/>
+      <c r="C169" s="63"/>
+      <c r="D169" s="52"/>
+      <c r="E169" s="60"/>
+      <c r="F169" s="8">
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="G169" s="78"/>
+      <c r="H169" s="79"/>
+      <c r="I169" s="35"/>
+      <c r="J169" s="9" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="K169" s="39"/>
+      <c r="L169" s="39"/>
+      <c r="M169" s="39"/>
+      <c r="N169" s="39"/>
+      <c r="O169" s="39"/>
+      <c r="P169" s="39"/>
+      <c r="Q169" s="39"/>
+      <c r="R169" s="39"/>
+      <c r="S169" s="10">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="T169" s="10">
+        <v>100000</v>
+      </c>
+      <c r="U169" s="10">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="V169" s="4"/>
+      <c r="Y169" s="4"/>
+    </row>
+    <row r="170" spans="2:25" ht="18.75">
+      <c r="B170" s="65"/>
+      <c r="C170" s="63"/>
+      <c r="D170" s="52"/>
+      <c r="E170" s="60"/>
+      <c r="F170" s="8">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="G170" s="78"/>
+      <c r="H170" s="79"/>
+      <c r="I170" s="35"/>
+      <c r="J170" s="9" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="K170" s="39"/>
+      <c r="L170" s="39"/>
+      <c r="M170" s="39"/>
+      <c r="N170" s="39"/>
+      <c r="O170" s="39"/>
+      <c r="P170" s="39"/>
+      <c r="Q170" s="39"/>
+      <c r="R170" s="39"/>
+      <c r="S170" s="10">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="T170" s="10">
+        <v>100000</v>
+      </c>
+      <c r="U170" s="10">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="V170" s="4"/>
+      <c r="W170" s="4"/>
+      <c r="X170" s="4"/>
+      <c r="Y170" s="4"/>
+    </row>
+    <row r="171" spans="2:25" ht="18.75">
+      <c r="B171" s="65"/>
+      <c r="C171" s="63"/>
+      <c r="D171" s="52"/>
+      <c r="E171" s="60"/>
+      <c r="F171" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="G171" s="78"/>
+      <c r="H171" s="79"/>
+      <c r="I171" s="35"/>
+      <c r="J171" s="9" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="K171" s="39"/>
+      <c r="L171" s="39"/>
+      <c r="M171" s="39"/>
+      <c r="N171" s="39"/>
+      <c r="O171" s="39"/>
+      <c r="P171" s="39"/>
+      <c r="Q171" s="39"/>
+      <c r="R171" s="39"/>
+      <c r="S171" s="10">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="T171" s="10">
+        <v>100000</v>
+      </c>
+      <c r="U171" s="10">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="V171" s="4"/>
+      <c r="Y171" s="4"/>
+    </row>
+    <row r="172" spans="2:25" ht="18.75">
+      <c r="B172" s="65"/>
+      <c r="C172" s="64"/>
+      <c r="D172" s="53"/>
+      <c r="E172" s="91"/>
+      <c r="F172" s="14">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="G172" s="78"/>
+      <c r="H172" s="79"/>
+      <c r="I172" s="37"/>
+      <c r="J172" s="15" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="K172" s="40"/>
+      <c r="L172" s="40"/>
+      <c r="M172" s="40"/>
+      <c r="N172" s="40"/>
+      <c r="O172" s="40"/>
+      <c r="P172" s="40"/>
+      <c r="Q172" s="40"/>
+      <c r="R172" s="40"/>
+      <c r="S172" s="16">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="T172" s="16">
+        <v>100000</v>
+      </c>
+      <c r="U172" s="16">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="V172" s="4"/>
+      <c r="W172" s="4"/>
+      <c r="X172" s="4"/>
+      <c r="Y172" s="4"/>
+    </row>
+    <row r="173" spans="2:25" ht="16.5" customHeight="1">
+      <c r="B173" s="65">
+        <v>46095</v>
+      </c>
+      <c r="C173" s="62" t="s">
+        <v>15</v>
+      </c>
+      <c r="D173" s="51"/>
+      <c r="E173" s="59" t="s">
+        <v>102</v>
+      </c>
+      <c r="F173" s="5">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="G173" s="73"/>
+      <c r="H173" s="74"/>
+      <c r="I173" s="34"/>
+      <c r="J173" s="6" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="K173" s="38"/>
+      <c r="L173" s="38"/>
+      <c r="M173" s="38"/>
+      <c r="N173" s="38"/>
+      <c r="O173" s="38"/>
+      <c r="P173" s="38"/>
+      <c r="Q173" s="38"/>
+      <c r="R173" s="38"/>
+      <c r="S173" s="7">
+        <f>SUM(K173:R173)</f>
+        <v>0</v>
+      </c>
+      <c r="T173" s="7">
+        <v>100000</v>
+      </c>
+      <c r="U173" s="7">
+        <f>T173*S173</f>
+        <v>0</v>
+      </c>
+      <c r="V173" s="4"/>
+      <c r="W173" s="4"/>
+      <c r="X173" s="4"/>
+      <c r="Y173" s="4"/>
+    </row>
+    <row r="174" spans="2:25" ht="18.75">
+      <c r="B174" s="65"/>
+      <c r="C174" s="63"/>
+      <c r="D174" s="52"/>
+      <c r="E174" s="60"/>
+      <c r="F174" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="G174" s="78"/>
+      <c r="H174" s="79"/>
+      <c r="I174" s="35"/>
+      <c r="J174" s="9" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="K174" s="39"/>
+      <c r="L174" s="39"/>
+      <c r="M174" s="39"/>
+      <c r="N174" s="39"/>
+      <c r="O174" s="39"/>
+      <c r="P174" s="39"/>
+      <c r="Q174" s="39"/>
+      <c r="R174" s="39"/>
+      <c r="S174" s="10">
+        <f t="shared" ref="S174:S184" si="43">SUM(K174:R174)</f>
+        <v>0</v>
+      </c>
+      <c r="T174" s="10">
+        <v>100000</v>
+      </c>
+      <c r="U174" s="10">
+        <f t="shared" ref="U174:U175" si="44">T174*S174</f>
+        <v>0</v>
+      </c>
+      <c r="V174" s="4"/>
+      <c r="W174" s="4"/>
+      <c r="X174" s="4"/>
+      <c r="Y174" s="4"/>
+    </row>
+    <row r="175" spans="2:25" ht="18.75">
+      <c r="B175" s="65"/>
+      <c r="C175" s="63"/>
+      <c r="D175" s="52"/>
+      <c r="E175" s="60"/>
+      <c r="F175" s="8">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="G175" s="78"/>
+      <c r="H175" s="79"/>
+      <c r="I175" s="35"/>
+      <c r="J175" s="9" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="K175" s="39"/>
+      <c r="L175" s="39"/>
+      <c r="M175" s="39"/>
+      <c r="N175" s="39"/>
+      <c r="O175" s="39"/>
+      <c r="P175" s="39"/>
+      <c r="Q175" s="39"/>
+      <c r="R175" s="39"/>
+      <c r="S175" s="10">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="T175" s="10">
+        <v>100000</v>
+      </c>
+      <c r="U175" s="10">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="V175" s="4"/>
+      <c r="W175" s="4"/>
+      <c r="X175" s="4"/>
+      <c r="Y175" s="4"/>
+    </row>
+    <row r="176" spans="2:25" ht="18.75">
+      <c r="B176" s="65"/>
+      <c r="C176" s="63"/>
+      <c r="D176" s="52"/>
+      <c r="E176" s="60"/>
+      <c r="F176" s="8">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="G176" s="78"/>
+      <c r="H176" s="79"/>
+      <c r="I176" s="35"/>
+      <c r="J176" s="9" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="K176" s="39"/>
+      <c r="L176" s="39"/>
+      <c r="M176" s="39"/>
+      <c r="N176" s="39"/>
+      <c r="O176" s="39"/>
+      <c r="P176" s="39"/>
+      <c r="Q176" s="39"/>
+      <c r="R176" s="39"/>
+      <c r="S176" s="10">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="T176" s="10">
+        <v>100000</v>
+      </c>
+      <c r="U176" s="10">
+        <f>T176*S176</f>
+        <v>0</v>
+      </c>
+      <c r="V176" s="4"/>
+      <c r="W176" s="4"/>
+      <c r="X176" s="4"/>
+      <c r="Y176" s="4"/>
+    </row>
+    <row r="177" spans="2:25" ht="18.75">
+      <c r="B177" s="65"/>
+      <c r="C177" s="63"/>
+      <c r="D177" s="52"/>
+      <c r="E177" s="60"/>
+      <c r="F177" s="8">
+        <v>0.75</v>
+      </c>
+      <c r="G177" s="78"/>
+      <c r="H177" s="79"/>
+      <c r="I177" s="35"/>
+      <c r="J177" s="9" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="K177" s="39"/>
+      <c r="L177" s="39"/>
+      <c r="M177" s="39"/>
+      <c r="N177" s="39"/>
+      <c r="O177" s="39"/>
+      <c r="P177" s="39"/>
+      <c r="Q177" s="39"/>
+      <c r="R177" s="39"/>
+      <c r="S177" s="10">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="T177" s="10">
+        <v>100000</v>
+      </c>
+      <c r="U177" s="10">
+        <f t="shared" ref="U177:U184" si="45">T177*S177</f>
+        <v>0</v>
+      </c>
+      <c r="V177" s="4"/>
+      <c r="W177" s="4"/>
+      <c r="X177" s="11"/>
+      <c r="Y177" s="4"/>
+    </row>
+    <row r="178" spans="2:25" ht="18.75">
+      <c r="B178" s="65"/>
+      <c r="C178" s="63"/>
+      <c r="D178" s="53"/>
+      <c r="E178" s="61"/>
+      <c r="F178" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="G178" s="78"/>
+      <c r="H178" s="79"/>
+      <c r="I178" s="36"/>
+      <c r="J178" s="9" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="K178" s="41"/>
+      <c r="L178" s="41"/>
+      <c r="M178" s="41"/>
+      <c r="N178" s="41"/>
+      <c r="O178" s="41"/>
+      <c r="P178" s="41"/>
+      <c r="Q178" s="41"/>
+      <c r="R178" s="41"/>
+      <c r="S178" s="13">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="T178" s="13">
+        <v>100000</v>
+      </c>
+      <c r="U178" s="13">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="V178" s="4"/>
+      <c r="Y178" s="4"/>
+    </row>
+    <row r="179" spans="2:25" ht="18.75">
+      <c r="B179" s="65"/>
+      <c r="C179" s="63"/>
+      <c r="D179" s="51"/>
+      <c r="E179" s="59" t="s">
+        <v>103</v>
+      </c>
+      <c r="F179" s="5">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="G179" s="73"/>
+      <c r="H179" s="74"/>
+      <c r="I179" s="34"/>
+      <c r="J179" s="6" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="K179" s="38"/>
+      <c r="L179" s="38"/>
+      <c r="M179" s="38"/>
+      <c r="N179" s="38"/>
+      <c r="O179" s="38"/>
+      <c r="P179" s="38"/>
+      <c r="Q179" s="38"/>
+      <c r="R179" s="38"/>
+      <c r="S179" s="7">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="T179" s="7">
+        <v>100000</v>
+      </c>
+      <c r="U179" s="7">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="V179" s="4"/>
+      <c r="Y179" s="4"/>
+    </row>
+    <row r="180" spans="2:25" ht="18.75">
+      <c r="B180" s="65"/>
+      <c r="C180" s="63"/>
+      <c r="D180" s="52"/>
+      <c r="E180" s="60"/>
+      <c r="F180" s="8">
+        <v>1</v>
+      </c>
+      <c r="G180" s="78"/>
+      <c r="H180" s="79"/>
+      <c r="I180" s="35"/>
+      <c r="J180" s="9" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="K180" s="39"/>
+      <c r="L180" s="39"/>
+      <c r="M180" s="39"/>
+      <c r="N180" s="39"/>
+      <c r="O180" s="39"/>
+      <c r="P180" s="39"/>
+      <c r="Q180" s="39"/>
+      <c r="R180" s="39"/>
+      <c r="S180" s="10">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="T180" s="10">
+        <v>100000</v>
+      </c>
+      <c r="U180" s="10">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="V180" s="4"/>
+      <c r="Y180" s="4"/>
+    </row>
+    <row r="181" spans="2:25" ht="18.75">
+      <c r="B181" s="65"/>
+      <c r="C181" s="63"/>
+      <c r="D181" s="52"/>
+      <c r="E181" s="60"/>
+      <c r="F181" s="8">
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="G181" s="78"/>
+      <c r="H181" s="79"/>
+      <c r="I181" s="35"/>
+      <c r="J181" s="9" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="K181" s="39"/>
+      <c r="L181" s="39"/>
+      <c r="M181" s="39"/>
+      <c r="N181" s="39"/>
+      <c r="O181" s="39"/>
+      <c r="P181" s="39"/>
+      <c r="Q181" s="39"/>
+      <c r="R181" s="39"/>
+      <c r="S181" s="10">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="T181" s="10">
+        <v>100000</v>
+      </c>
+      <c r="U181" s="10">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="V181" s="4"/>
+      <c r="Y181" s="4"/>
+    </row>
+    <row r="182" spans="2:25" ht="18.75">
+      <c r="B182" s="65"/>
+      <c r="C182" s="63"/>
+      <c r="D182" s="52"/>
+      <c r="E182" s="60"/>
+      <c r="F182" s="8">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="G182" s="78"/>
+      <c r="H182" s="79"/>
+      <c r="I182" s="35"/>
+      <c r="J182" s="9" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="K182" s="39"/>
+      <c r="L182" s="39"/>
+      <c r="M182" s="39"/>
+      <c r="N182" s="39"/>
+      <c r="O182" s="39"/>
+      <c r="P182" s="39"/>
+      <c r="Q182" s="39"/>
+      <c r="R182" s="39"/>
+      <c r="S182" s="10">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="T182" s="10">
+        <v>100000</v>
+      </c>
+      <c r="U182" s="10">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="V182" s="4"/>
+      <c r="W182" s="4"/>
+      <c r="X182" s="4"/>
+      <c r="Y182" s="4"/>
+    </row>
+    <row r="183" spans="2:25" ht="18.75">
+      <c r="B183" s="65"/>
+      <c r="C183" s="63"/>
+      <c r="D183" s="52"/>
+      <c r="E183" s="60"/>
+      <c r="F183" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="G183" s="78"/>
+      <c r="H183" s="79"/>
+      <c r="I183" s="35"/>
+      <c r="J183" s="9" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="K183" s="39"/>
+      <c r="L183" s="39"/>
+      <c r="M183" s="39"/>
+      <c r="N183" s="39"/>
+      <c r="O183" s="39"/>
+      <c r="P183" s="39"/>
+      <c r="Q183" s="39"/>
+      <c r="R183" s="39"/>
+      <c r="S183" s="10">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="T183" s="10">
+        <v>100000</v>
+      </c>
+      <c r="U183" s="10">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="V183" s="4"/>
+      <c r="Y183" s="4"/>
+    </row>
+    <row r="184" spans="2:25" ht="18.75">
+      <c r="B184" s="65"/>
+      <c r="C184" s="64"/>
+      <c r="D184" s="53"/>
+      <c r="E184" s="91"/>
+      <c r="F184" s="14">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="G184" s="78"/>
+      <c r="H184" s="79"/>
+      <c r="I184" s="37"/>
+      <c r="J184" s="15" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="K184" s="40"/>
+      <c r="L184" s="40"/>
+      <c r="M184" s="40"/>
+      <c r="N184" s="40"/>
+      <c r="O184" s="40"/>
+      <c r="P184" s="40"/>
+      <c r="Q184" s="40"/>
+      <c r="R184" s="40"/>
+      <c r="S184" s="16">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="T184" s="16">
+        <v>100000</v>
+      </c>
+      <c r="U184" s="16">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="V184" s="4"/>
+      <c r="W184" s="4"/>
+      <c r="X184" s="4"/>
+      <c r="Y184" s="4"/>
+    </row>
   </sheetData>
-  <mergeCells count="210">
+  <mergeCells count="242">
+    <mergeCell ref="B173:B184"/>
+    <mergeCell ref="C173:C184"/>
+    <mergeCell ref="E173:E178"/>
+    <mergeCell ref="G173:H173"/>
+    <mergeCell ref="G174:H174"/>
+    <mergeCell ref="G175:H175"/>
+    <mergeCell ref="G176:H176"/>
+    <mergeCell ref="G177:H177"/>
+    <mergeCell ref="G178:H178"/>
+    <mergeCell ref="E179:E184"/>
+    <mergeCell ref="G179:H179"/>
+    <mergeCell ref="G180:H180"/>
+    <mergeCell ref="G181:H181"/>
+    <mergeCell ref="G182:H182"/>
+    <mergeCell ref="G183:H183"/>
+    <mergeCell ref="G184:H184"/>
+    <mergeCell ref="B161:B172"/>
+    <mergeCell ref="C161:C172"/>
+    <mergeCell ref="E161:E166"/>
+    <mergeCell ref="G161:H161"/>
+    <mergeCell ref="G162:H162"/>
+    <mergeCell ref="G163:H163"/>
+    <mergeCell ref="G164:H164"/>
+    <mergeCell ref="G165:H165"/>
+    <mergeCell ref="G166:H166"/>
+    <mergeCell ref="E167:E172"/>
+    <mergeCell ref="G167:H167"/>
+    <mergeCell ref="G168:H168"/>
+    <mergeCell ref="G169:H169"/>
+    <mergeCell ref="G170:H170"/>
+    <mergeCell ref="G171:H171"/>
+    <mergeCell ref="G172:H172"/>
     <mergeCell ref="B149:B160"/>
     <mergeCell ref="C149:C160"/>
     <mergeCell ref="E149:E154"/>
@@ -16031,19 +18278,19 @@
     <mergeCell ref="T15:U15"/>
   </mergeCells>
   <dataValidations count="6">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G17:G22 G29:G34 G41:G46 G53:G58 G65:G70 G137:G142 G77:G82 G101:G106 G113:G118 G125:G130 G89:G94 G149:G154" xr:uid="{12AFEA37-DE9D-4331-8D26-58A87B462F74}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G17:G22 G29:G34 G41:G46 G53:G58 G65:G70 G137:G142 G77:G82 G101:G106 G113:G118 G125:G130 G89:G94 G149:G154 G161:G166 G173:G178" xr:uid="{12AFEA37-DE9D-4331-8D26-58A87B462F74}">
       <formula1>$C$11:$S$11</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C125 C17 C29 C41 C53 C65 C77 C89 C101 C113 C137 C149" xr:uid="{34E88085-362B-4A10-BF54-835362F6EE09}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C125 C17 C29 C41 C53 C65 C77 C89 C101 C113 C137 C149 C161 C173" xr:uid="{34E88085-362B-4A10-BF54-835362F6EE09}">
       <formula1>$X$17:$X$21</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E17 E23 E29 E41 E53 E65 E77 E89 E101 E113 E125 E137 E35 E47 E59 E71 E83 E95 E107 E119 E131 E143 E149 E155" xr:uid="{217D092B-4D1C-4387-AF95-F593535398E8}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E17 E23 E29 E41 E53 E65 E77 E89 E101 E113 E125 E137 E35 E47 E59 E71 E83 E95 E107 E119 E131 E143 E149 E155 E161 E167 E173 E179" xr:uid="{217D092B-4D1C-4387-AF95-F593535398E8}">
       <formula1>$X$22:$X$23</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D17:D160" xr:uid="{0E1E66B1-9B0F-460C-928B-E32F49E51B4F}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D17:D184" xr:uid="{0E1E66B1-9B0F-460C-928B-E32F49E51B4F}">
       <formula1>$Z$21:$Z$61</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G23:H28 G35:H40 G143:H148 G59:H64 G71:H76 G47:H52 G83:H88 G107:H112 G119:H124 G131:H136 G95:H100 G155:H160" xr:uid="{BBCD1210-CEA0-4BC9-94EF-37762961F608}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G23:H28 G35:H40 G143:H148 G59:H64 G71:H76 G47:H52 G83:H88 G107:H112 G119:H124 G131:H136 G95:H100 G155:H160 G167:H172 G179:H184" xr:uid="{BBCD1210-CEA0-4BC9-94EF-37762961F608}">
       <formula1>$C$12:$S$12</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C6" xr:uid="{02C5D8BD-F18A-4262-BE87-765D29D27F95}">
@@ -16056,7 +18303,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FD96DA7-E256-4F0F-A2D9-7B8F0AC97C99}">
-  <dimension ref="B1:AU160"/>
+  <dimension ref="B1:AU184"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="4.140625" style="1" customWidth="1"/>
@@ -16158,7 +18405,7 @@
     </row>
     <row r="4" spans="2:47" ht="22.5">
       <c r="B4" s="58" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C4" s="58"/>
       <c r="D4" s="58"/>
@@ -16261,7 +18508,7 @@
         <v>13</v>
       </c>
       <c r="D6" s="89" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E6" s="87"/>
       <c r="F6" s="87"/>
@@ -16271,10 +18518,10 @@
       <c r="J6" s="87"/>
       <c r="K6" s="47"/>
       <c r="L6" s="48" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="M6" s="86" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="N6" s="87"/>
       <c r="O6" s="87"/>
@@ -16316,7 +18563,7 @@
     <row r="7" spans="2:47" ht="24.95" customHeight="1">
       <c r="C7" s="3"/>
       <c r="D7" s="88" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E7" s="88"/>
       <c r="F7" s="88"/>
@@ -16327,7 +18574,7 @@
       <c r="K7" s="88"/>
       <c r="L7" s="3"/>
       <c r="M7" s="88" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N7" s="88"/>
       <c r="O7" s="88"/>
@@ -16365,7 +18612,7 @@
     </row>
     <row r="8" spans="2:47" ht="22.5">
       <c r="B8" s="57" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C8" s="58"/>
       <c r="D8" s="58"/>
@@ -16533,10 +18780,10 @@
         <v>81</v>
       </c>
       <c r="K11" s="31" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="L11" s="31" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="M11" s="31"/>
       <c r="N11" s="31"/>
@@ -16592,7 +18839,7 @@
     </row>
     <row r="13" spans="2:47" ht="54.6" customHeight="1">
       <c r="B13" s="90" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C13" s="90"/>
       <c r="D13" s="90"/>
@@ -16659,7 +18906,7 @@
         <v>73</v>
       </c>
       <c r="S14" s="56" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="T14" s="56"/>
       <c r="U14" s="56"/>
@@ -16762,7 +19009,7 @@
       </c>
       <c r="D17" s="51"/>
       <c r="E17" s="59" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F17" s="5">
         <v>0.41666666666666669</v>
@@ -17004,7 +19251,7 @@
       </c>
       <c r="V22" s="4"/>
       <c r="X22" s="54" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="Z22" s="44" t="s">
         <v>46</v>
@@ -17015,7 +19262,7 @@
       <c r="C23" s="63"/>
       <c r="D23" s="51"/>
       <c r="E23" s="59" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F23" s="5">
         <v>0.91666666666666663</v>
@@ -17048,7 +19295,7 @@
       </c>
       <c r="V23" s="4"/>
       <c r="X23" s="54" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="Z23" s="44" t="s">
         <v>45</v>
@@ -17267,7 +19514,7 @@
         <v>56</v>
       </c>
       <c r="E29" s="59" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F29" s="5">
         <v>0.41666666666666669</v>
@@ -17567,7 +19814,7 @@
         <v>56</v>
       </c>
       <c r="E35" s="59" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F35" s="5">
         <v>0.91666666666666663</v>
@@ -17859,7 +20106,7 @@
         <v>60</v>
       </c>
       <c r="E41" s="59" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F41" s="5">
         <v>0.41666666666666669</v>
@@ -18151,7 +20398,7 @@
         <v>60</v>
       </c>
       <c r="E47" s="59" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F47" s="5">
         <v>0.91666666666666663</v>
@@ -18439,7 +20686,7 @@
         <v>59</v>
       </c>
       <c r="E53" s="59" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F53" s="5">
         <v>0.41666666666666669</v>
@@ -18723,7 +20970,7 @@
         <v>47</v>
       </c>
       <c r="E59" s="59" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F59" s="5">
         <v>0.91666666666666663</v>
@@ -19002,7 +21249,7 @@
         <v>47</v>
       </c>
       <c r="E65" s="59" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F65" s="5">
         <v>0.41666666666666669</v>
@@ -19274,7 +21521,7 @@
         <v>47</v>
       </c>
       <c r="E71" s="59" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F71" s="5">
         <v>0.91666666666666663</v>
@@ -19548,7 +21795,7 @@
         <v>47</v>
       </c>
       <c r="E77" s="59" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F77" s="5">
         <v>0.41666666666666669</v>
@@ -19822,7 +22069,7 @@
         <v>47</v>
       </c>
       <c r="E83" s="59" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F83" s="5">
         <v>0.91666666666666663</v>
@@ -20094,7 +22341,7 @@
         <v>54</v>
       </c>
       <c r="E89" s="59" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F89" s="5">
         <v>0.41666666666666669</v>
@@ -20362,7 +22609,7 @@
         <v>54</v>
       </c>
       <c r="E95" s="59" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F95" s="5">
         <v>0.91666666666666663</v>
@@ -20632,7 +22879,7 @@
       </c>
       <c r="D101" s="51"/>
       <c r="E101" s="59" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F101" s="5">
         <v>0.41666666666666669</v>
@@ -20866,7 +23113,7 @@
       <c r="C107" s="63"/>
       <c r="D107" s="51"/>
       <c r="E107" s="59" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F107" s="5">
         <v>0.91666666666666663</v>
@@ -21100,7 +23347,7 @@
         <v>54</v>
       </c>
       <c r="E113" s="59" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F113" s="5">
         <v>0.41666666666666669</v>
@@ -21366,7 +23613,7 @@
       <c r="C119" s="63"/>
       <c r="D119" s="51"/>
       <c r="E119" s="59" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F119" s="5">
         <v>0.91666666666666663</v>
@@ -21600,7 +23847,7 @@
         <v>53</v>
       </c>
       <c r="E125" s="59" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F125" s="5">
         <v>0.41666666666666669</v>
@@ -21874,7 +24121,7 @@
         <v>53</v>
       </c>
       <c r="E131" s="59" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F131" s="5">
         <v>0.91666666666666663</v>
@@ -22148,7 +24395,7 @@
       </c>
       <c r="D137" s="51"/>
       <c r="E137" s="59" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F137" s="5">
         <v>0.41666666666666669</v>
@@ -22377,24 +24624,32 @@
       <c r="V142" s="4"/>
       <c r="Y142" s="4"/>
     </row>
-    <row r="143" spans="2:25" ht="18.75">
+    <row r="143" spans="2:25" ht="37.5">
       <c r="B143" s="65"/>
       <c r="C143" s="63"/>
-      <c r="D143" s="51"/>
+      <c r="D143" s="51" t="s">
+        <v>53</v>
+      </c>
       <c r="E143" s="59" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F143" s="5">
         <v>0.91666666666666663</v>
       </c>
-      <c r="G143" s="73"/>
+      <c r="G143" s="73" t="s">
+        <v>85</v>
+      </c>
       <c r="H143" s="74"/>
-      <c r="I143" s="34"/>
-      <c r="J143" s="6" t="str">
+      <c r="I143" s="34">
+        <v>60</v>
+      </c>
+      <c r="J143" s="6">
         <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="K143" s="38"/>
+        <v>1.6666666666666666E-2</v>
+      </c>
+      <c r="K143" s="38">
+        <v>1</v>
+      </c>
       <c r="L143" s="38"/>
       <c r="M143" s="38"/>
       <c r="N143" s="38"/>
@@ -22404,36 +24659,44 @@
       <c r="R143" s="38"/>
       <c r="S143" s="7">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T143" s="7">
         <v>100000</v>
       </c>
       <c r="U143" s="7">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="V143" s="4"/>
       <c r="Y143" s="4"/>
     </row>
-    <row r="144" spans="2:25" ht="18.75">
+    <row r="144" spans="2:25" ht="37.5">
       <c r="B144" s="65"/>
       <c r="C144" s="63"/>
-      <c r="D144" s="52"/>
+      <c r="D144" s="52" t="s">
+        <v>53</v>
+      </c>
       <c r="E144" s="60"/>
       <c r="F144" s="8">
         <v>1</v>
       </c>
-      <c r="G144" s="78"/>
+      <c r="G144" s="78" t="s">
+        <v>85</v>
+      </c>
       <c r="H144" s="79"/>
-      <c r="I144" s="35"/>
-      <c r="J144" s="9" t="str">
+      <c r="I144" s="35">
+        <v>60</v>
+      </c>
+      <c r="J144" s="9">
         <f t="shared" si="31"/>
-        <v/>
+        <v>1.6666666666666666E-2</v>
       </c>
       <c r="K144" s="39"/>
       <c r="L144" s="39"/>
-      <c r="M144" s="39"/>
+      <c r="M144" s="39">
+        <v>1</v>
+      </c>
       <c r="N144" s="39"/>
       <c r="O144" s="39"/>
       <c r="P144" s="39"/>
@@ -22441,32 +24704,38 @@
       <c r="R144" s="39"/>
       <c r="S144" s="10">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T144" s="10">
         <v>100000</v>
       </c>
       <c r="U144" s="10">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="V144" s="4"/>
       <c r="Y144" s="4"/>
     </row>
-    <row r="145" spans="2:25" ht="18.75">
+    <row r="145" spans="2:25" ht="37.5">
       <c r="B145" s="65"/>
       <c r="C145" s="63"/>
-      <c r="D145" s="52"/>
+      <c r="D145" s="52" t="s">
+        <v>53</v>
+      </c>
       <c r="E145" s="60"/>
       <c r="F145" s="8">
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="G145" s="78"/>
+      <c r="G145" s="78" t="s">
+        <v>85</v>
+      </c>
       <c r="H145" s="79"/>
-      <c r="I145" s="35"/>
-      <c r="J145" s="9" t="str">
+      <c r="I145" s="35">
+        <v>60</v>
+      </c>
+      <c r="J145" s="9">
         <f t="shared" si="31"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K145" s="39"/>
       <c r="L145" s="39"/>
@@ -22490,20 +24759,26 @@
       <c r="V145" s="4"/>
       <c r="Y145" s="4"/>
     </row>
-    <row r="146" spans="2:25" ht="18.75">
+    <row r="146" spans="2:25" ht="37.5">
       <c r="B146" s="65"/>
       <c r="C146" s="63"/>
-      <c r="D146" s="52"/>
+      <c r="D146" s="52" t="s">
+        <v>53</v>
+      </c>
       <c r="E146" s="60"/>
       <c r="F146" s="8">
         <v>0.16666666666666666</v>
       </c>
-      <c r="G146" s="78"/>
+      <c r="G146" s="78" t="s">
+        <v>85</v>
+      </c>
       <c r="H146" s="79"/>
-      <c r="I146" s="35"/>
-      <c r="J146" s="9" t="str">
+      <c r="I146" s="35">
+        <v>60</v>
+      </c>
+      <c r="J146" s="9">
         <f t="shared" si="31"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K146" s="39"/>
       <c r="L146" s="39"/>
@@ -22529,20 +24804,26 @@
       <c r="X146" s="4"/>
       <c r="Y146" s="4"/>
     </row>
-    <row r="147" spans="2:25" ht="18.75">
+    <row r="147" spans="2:25" ht="37.5">
       <c r="B147" s="65"/>
       <c r="C147" s="63"/>
-      <c r="D147" s="52"/>
+      <c r="D147" s="52" t="s">
+        <v>53</v>
+      </c>
       <c r="E147" s="60"/>
       <c r="F147" s="8">
         <v>0.25</v>
       </c>
-      <c r="G147" s="78"/>
+      <c r="G147" s="78" t="s">
+        <v>85</v>
+      </c>
       <c r="H147" s="79"/>
-      <c r="I147" s="35"/>
-      <c r="J147" s="9" t="str">
+      <c r="I147" s="35">
+        <v>60</v>
+      </c>
+      <c r="J147" s="9">
         <f t="shared" si="31"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K147" s="39"/>
       <c r="L147" s="39"/>
@@ -22566,17 +24847,23 @@
       <c r="V147" s="4"/>
       <c r="Y147" s="4"/>
     </row>
-    <row r="148" spans="2:25" ht="18.75">
+    <row r="148" spans="2:25" ht="37.5">
       <c r="B148" s="65"/>
       <c r="C148" s="64"/>
-      <c r="D148" s="53"/>
+      <c r="D148" s="53" t="s">
+        <v>53</v>
+      </c>
       <c r="E148" s="91"/>
       <c r="F148" s="14">
         <v>0.33333333333333331</v>
       </c>
-      <c r="G148" s="78"/>
+      <c r="G148" s="78" t="s">
+        <v>85</v>
+      </c>
       <c r="H148" s="79"/>
-      <c r="I148" s="37"/>
+      <c r="I148" s="37">
+        <v>0</v>
+      </c>
       <c r="J148" s="15" t="str">
         <f t="shared" si="31"/>
         <v/>
@@ -22605,26 +24892,32 @@
       <c r="X148" s="4"/>
       <c r="Y148" s="4"/>
     </row>
-    <row r="149" spans="2:25" ht="16.5" customHeight="1">
+    <row r="149" spans="2:25" ht="32.25" customHeight="1">
       <c r="B149" s="65">
         <v>46093</v>
       </c>
       <c r="C149" s="62" t="s">
         <v>16</v>
       </c>
-      <c r="D149" s="51"/>
+      <c r="D149" s="51" t="s">
+        <v>47</v>
+      </c>
       <c r="E149" s="59" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F149" s="5">
         <v>0.41666666666666669</v>
       </c>
-      <c r="G149" s="73"/>
+      <c r="G149" s="73" t="s">
+        <v>74</v>
+      </c>
       <c r="H149" s="74"/>
-      <c r="I149" s="34"/>
-      <c r="J149" s="6" t="str">
+      <c r="I149" s="34">
+        <v>58</v>
+      </c>
+      <c r="J149" s="6">
         <f t="shared" ref="J149:J160" si="35">IFERROR(S149/I149,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K149" s="38"/>
       <c r="L149" s="38"/>
@@ -22650,20 +24943,26 @@
       <c r="X149" s="4"/>
       <c r="Y149" s="4"/>
     </row>
-    <row r="150" spans="2:25" ht="18.75">
+    <row r="150" spans="2:25" ht="37.5">
       <c r="B150" s="65"/>
       <c r="C150" s="63"/>
-      <c r="D150" s="52"/>
+      <c r="D150" s="52" t="s">
+        <v>47</v>
+      </c>
       <c r="E150" s="60"/>
       <c r="F150" s="8">
         <v>0.5</v>
       </c>
-      <c r="G150" s="78"/>
+      <c r="G150" s="78" t="s">
+        <v>74</v>
+      </c>
       <c r="H150" s="79"/>
-      <c r="I150" s="35"/>
-      <c r="J150" s="9" t="str">
+      <c r="I150" s="35">
+        <v>41</v>
+      </c>
+      <c r="J150" s="9">
         <f t="shared" si="35"/>
-        <v/>
+        <v>0.12195121951219512</v>
       </c>
       <c r="K150" s="39"/>
       <c r="L150" s="39"/>
@@ -22672,37 +24971,45 @@
       <c r="O150" s="39"/>
       <c r="P150" s="39"/>
       <c r="Q150" s="39"/>
-      <c r="R150" s="39"/>
+      <c r="R150" s="39">
+        <v>5</v>
+      </c>
       <c r="S150" s="10">
         <f t="shared" ref="S150:S160" si="36">SUM(K150:R150)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T150" s="10">
         <v>100000</v>
       </c>
       <c r="U150" s="10">
         <f t="shared" ref="U150:U151" si="37">T150*S150</f>
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="V150" s="4"/>
       <c r="W150" s="4"/>
       <c r="X150" s="4"/>
       <c r="Y150" s="4"/>
     </row>
-    <row r="151" spans="2:25" ht="18.75">
+    <row r="151" spans="2:25" ht="37.5">
       <c r="B151" s="65"/>
       <c r="C151" s="63"/>
-      <c r="D151" s="52"/>
+      <c r="D151" s="52" t="s">
+        <v>47</v>
+      </c>
       <c r="E151" s="60"/>
       <c r="F151" s="8">
         <v>0.58333333333333337</v>
       </c>
-      <c r="G151" s="78"/>
+      <c r="G151" s="78" t="s">
+        <v>74</v>
+      </c>
       <c r="H151" s="79"/>
-      <c r="I151" s="35"/>
-      <c r="J151" s="9" t="str">
+      <c r="I151" s="35">
+        <v>38</v>
+      </c>
+      <c r="J151" s="9">
         <f t="shared" si="35"/>
-        <v/>
+        <v>0.21052631578947367</v>
       </c>
       <c r="K151" s="39"/>
       <c r="L151" s="39"/>
@@ -22710,38 +25017,46 @@
       <c r="N151" s="39"/>
       <c r="O151" s="39"/>
       <c r="P151" s="39"/>
-      <c r="Q151" s="39"/>
+      <c r="Q151" s="39">
+        <v>8</v>
+      </c>
       <c r="R151" s="39"/>
       <c r="S151" s="10">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="T151" s="10">
         <v>100000</v>
       </c>
       <c r="U151" s="10">
         <f t="shared" si="37"/>
-        <v>0</v>
+        <v>800000</v>
       </c>
       <c r="V151" s="4"/>
       <c r="W151" s="4"/>
       <c r="X151" s="4"/>
       <c r="Y151" s="4"/>
     </row>
-    <row r="152" spans="2:25" ht="18.75">
+    <row r="152" spans="2:25" ht="37.5">
       <c r="B152" s="65"/>
       <c r="C152" s="63"/>
-      <c r="D152" s="52"/>
+      <c r="D152" s="52" t="s">
+        <v>47</v>
+      </c>
       <c r="E152" s="60"/>
       <c r="F152" s="8">
         <v>0.66666666666666663</v>
       </c>
-      <c r="G152" s="78"/>
+      <c r="G152" s="78" t="s">
+        <v>74</v>
+      </c>
       <c r="H152" s="79"/>
-      <c r="I152" s="35"/>
-      <c r="J152" s="9" t="str">
+      <c r="I152" s="35">
+        <v>59</v>
+      </c>
+      <c r="J152" s="9">
         <f t="shared" si="35"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K152" s="39"/>
       <c r="L152" s="39"/>
@@ -22767,20 +25082,26 @@
       <c r="X152" s="4"/>
       <c r="Y152" s="4"/>
     </row>
-    <row r="153" spans="2:25" ht="18.75">
+    <row r="153" spans="2:25" ht="37.5">
       <c r="B153" s="65"/>
       <c r="C153" s="63"/>
-      <c r="D153" s="52"/>
+      <c r="D153" s="52" t="s">
+        <v>47</v>
+      </c>
       <c r="E153" s="60"/>
       <c r="F153" s="8">
         <v>0.75</v>
       </c>
-      <c r="G153" s="78"/>
+      <c r="G153" s="78" t="s">
+        <v>74</v>
+      </c>
       <c r="H153" s="79"/>
-      <c r="I153" s="35"/>
-      <c r="J153" s="9" t="str">
+      <c r="I153" s="35">
+        <v>34</v>
+      </c>
+      <c r="J153" s="9">
         <f t="shared" si="35"/>
-        <v/>
+        <v>8.8235294117647065E-2</v>
       </c>
       <c r="K153" s="39"/>
       <c r="L153" s="39"/>
@@ -22788,38 +25109,46 @@
       <c r="N153" s="39"/>
       <c r="O153" s="39"/>
       <c r="P153" s="39"/>
-      <c r="Q153" s="39"/>
+      <c r="Q153" s="39">
+        <v>3</v>
+      </c>
       <c r="R153" s="39"/>
       <c r="S153" s="10">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T153" s="10">
         <v>100000</v>
       </c>
       <c r="U153" s="10">
         <f t="shared" ref="U153:U160" si="38">T153*S153</f>
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="V153" s="4"/>
       <c r="W153" s="4"/>
       <c r="X153" s="11"/>
       <c r="Y153" s="4"/>
     </row>
-    <row r="154" spans="2:25" ht="18.75">
+    <row r="154" spans="2:25" ht="37.5">
       <c r="B154" s="65"/>
       <c r="C154" s="63"/>
-      <c r="D154" s="53"/>
+      <c r="D154" s="53" t="s">
+        <v>47</v>
+      </c>
       <c r="E154" s="61"/>
       <c r="F154" s="12">
         <v>0.83333333333333337</v>
       </c>
-      <c r="G154" s="78"/>
+      <c r="G154" s="78" t="s">
+        <v>74</v>
+      </c>
       <c r="H154" s="79"/>
-      <c r="I154" s="36"/>
-      <c r="J154" s="9" t="str">
+      <c r="I154" s="36">
+        <v>50</v>
+      </c>
+      <c r="J154" s="9">
         <f t="shared" si="35"/>
-        <v/>
+        <v>0.1</v>
       </c>
       <c r="K154" s="41"/>
       <c r="L154" s="41"/>
@@ -22828,39 +25157,49 @@
       <c r="O154" s="41"/>
       <c r="P154" s="41"/>
       <c r="Q154" s="41"/>
-      <c r="R154" s="41"/>
+      <c r="R154" s="41">
+        <v>5</v>
+      </c>
       <c r="S154" s="13">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T154" s="13">
         <v>100000</v>
       </c>
       <c r="U154" s="13">
         <f t="shared" si="38"/>
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="V154" s="4"/>
       <c r="Y154" s="4"/>
     </row>
-    <row r="155" spans="2:25" ht="18.75">
+    <row r="155" spans="2:25" ht="37.5">
       <c r="B155" s="65"/>
       <c r="C155" s="63"/>
-      <c r="D155" s="51"/>
+      <c r="D155" s="51" t="s">
+        <v>47</v>
+      </c>
       <c r="E155" s="59" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F155" s="5">
         <v>0.91666666666666663</v>
       </c>
-      <c r="G155" s="73"/>
+      <c r="G155" s="73" t="s">
+        <v>85</v>
+      </c>
       <c r="H155" s="74"/>
-      <c r="I155" s="34"/>
-      <c r="J155" s="6" t="str">
+      <c r="I155" s="34">
+        <v>63</v>
+      </c>
+      <c r="J155" s="6">
         <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="K155" s="38"/>
+        <v>3.1746031746031744E-2</v>
+      </c>
+      <c r="K155" s="38">
+        <v>2</v>
+      </c>
       <c r="L155" s="38"/>
       <c r="M155" s="38"/>
       <c r="N155" s="38"/>
@@ -22870,34 +25209,42 @@
       <c r="R155" s="38"/>
       <c r="S155" s="7">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T155" s="7">
         <v>100000</v>
       </c>
       <c r="U155" s="7">
         <f t="shared" si="38"/>
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="V155" s="4"/>
       <c r="Y155" s="4"/>
     </row>
-    <row r="156" spans="2:25" ht="18.75">
+    <row r="156" spans="2:25" ht="37.5">
       <c r="B156" s="65"/>
       <c r="C156" s="63"/>
-      <c r="D156" s="52"/>
+      <c r="D156" s="52" t="s">
+        <v>47</v>
+      </c>
       <c r="E156" s="60"/>
       <c r="F156" s="8">
         <v>1</v>
       </c>
-      <c r="G156" s="78"/>
+      <c r="G156" s="78" t="s">
+        <v>85</v>
+      </c>
       <c r="H156" s="79"/>
-      <c r="I156" s="35"/>
-      <c r="J156" s="9" t="str">
+      <c r="I156" s="35">
+        <v>30</v>
+      </c>
+      <c r="J156" s="9">
         <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="K156" s="39"/>
+        <v>6.6666666666666666E-2</v>
+      </c>
+      <c r="K156" s="39">
+        <v>2</v>
+      </c>
       <c r="L156" s="39"/>
       <c r="M156" s="39"/>
       <c r="N156" s="39"/>
@@ -22907,34 +25254,42 @@
       <c r="R156" s="39"/>
       <c r="S156" s="10">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T156" s="10">
         <v>100000</v>
       </c>
       <c r="U156" s="10">
         <f t="shared" si="38"/>
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="V156" s="4"/>
       <c r="Y156" s="4"/>
     </row>
-    <row r="157" spans="2:25" ht="18.75">
+    <row r="157" spans="2:25" ht="37.5">
       <c r="B157" s="65"/>
       <c r="C157" s="63"/>
-      <c r="D157" s="52"/>
+      <c r="D157" s="52" t="s">
+        <v>47</v>
+      </c>
       <c r="E157" s="60"/>
       <c r="F157" s="8">
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="G157" s="78"/>
+      <c r="G157" s="78" t="s">
+        <v>85</v>
+      </c>
       <c r="H157" s="79"/>
-      <c r="I157" s="35"/>
-      <c r="J157" s="9" t="str">
+      <c r="I157" s="35">
+        <v>30</v>
+      </c>
+      <c r="J157" s="9">
         <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="K157" s="39"/>
+        <v>6.6666666666666666E-2</v>
+      </c>
+      <c r="K157" s="39">
+        <v>2</v>
+      </c>
       <c r="L157" s="39"/>
       <c r="M157" s="39"/>
       <c r="N157" s="39"/>
@@ -22944,34 +25299,42 @@
       <c r="R157" s="39"/>
       <c r="S157" s="10">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T157" s="10">
         <v>100000</v>
       </c>
       <c r="U157" s="10">
         <f t="shared" si="38"/>
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="V157" s="4"/>
       <c r="Y157" s="4"/>
     </row>
-    <row r="158" spans="2:25" ht="18.75">
+    <row r="158" spans="2:25" ht="37.5">
       <c r="B158" s="65"/>
       <c r="C158" s="63"/>
-      <c r="D158" s="52"/>
+      <c r="D158" s="52" t="s">
+        <v>47</v>
+      </c>
       <c r="E158" s="60"/>
       <c r="F158" s="8">
         <v>0.16666666666666666</v>
       </c>
-      <c r="G158" s="78"/>
+      <c r="G158" s="78" t="s">
+        <v>85</v>
+      </c>
       <c r="H158" s="79"/>
-      <c r="I158" s="35"/>
-      <c r="J158" s="9" t="str">
+      <c r="I158" s="35">
+        <v>63</v>
+      </c>
+      <c r="J158" s="9">
         <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="K158" s="39"/>
+        <v>3.1746031746031744E-2</v>
+      </c>
+      <c r="K158" s="39">
+        <v>2</v>
+      </c>
       <c r="L158" s="39"/>
       <c r="M158" s="39"/>
       <c r="N158" s="39"/>
@@ -22981,36 +25344,44 @@
       <c r="R158" s="39"/>
       <c r="S158" s="10">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T158" s="10">
         <v>100000</v>
       </c>
       <c r="U158" s="10">
         <f t="shared" si="38"/>
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="V158" s="4"/>
       <c r="W158" s="4"/>
       <c r="X158" s="4"/>
       <c r="Y158" s="4"/>
     </row>
-    <row r="159" spans="2:25" ht="18.75">
+    <row r="159" spans="2:25" ht="37.5">
       <c r="B159" s="65"/>
       <c r="C159" s="63"/>
-      <c r="D159" s="52"/>
+      <c r="D159" s="52" t="s">
+        <v>47</v>
+      </c>
       <c r="E159" s="60"/>
       <c r="F159" s="8">
         <v>0.25</v>
       </c>
-      <c r="G159" s="78"/>
+      <c r="G159" s="78" t="s">
+        <v>85</v>
+      </c>
       <c r="H159" s="79"/>
-      <c r="I159" s="35"/>
-      <c r="J159" s="9" t="str">
+      <c r="I159" s="35">
+        <v>50</v>
+      </c>
+      <c r="J159" s="9">
         <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="K159" s="39"/>
+        <v>0.04</v>
+      </c>
+      <c r="K159" s="39">
+        <v>2</v>
+      </c>
       <c r="L159" s="39"/>
       <c r="M159" s="39"/>
       <c r="N159" s="39"/>
@@ -23020,34 +25391,42 @@
       <c r="R159" s="39"/>
       <c r="S159" s="10">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T159" s="10">
         <v>100000</v>
       </c>
       <c r="U159" s="10">
         <f t="shared" si="38"/>
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="V159" s="4"/>
       <c r="Y159" s="4"/>
     </row>
-    <row r="160" spans="2:25" ht="18.75">
+    <row r="160" spans="2:25" ht="37.5">
       <c r="B160" s="65"/>
       <c r="C160" s="64"/>
-      <c r="D160" s="53"/>
+      <c r="D160" s="53" t="s">
+        <v>47</v>
+      </c>
       <c r="E160" s="91"/>
       <c r="F160" s="14">
         <v>0.33333333333333331</v>
       </c>
-      <c r="G160" s="78"/>
+      <c r="G160" s="78" t="s">
+        <v>85</v>
+      </c>
       <c r="H160" s="79"/>
-      <c r="I160" s="37"/>
-      <c r="J160" s="15" t="str">
+      <c r="I160" s="37">
+        <v>64</v>
+      </c>
+      <c r="J160" s="15">
         <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="K160" s="40"/>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="K160" s="40">
+        <v>1</v>
+      </c>
       <c r="L160" s="40"/>
       <c r="M160" s="40"/>
       <c r="N160" s="40"/>
@@ -23057,22 +25436,986 @@
       <c r="R160" s="40"/>
       <c r="S160" s="16">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T160" s="16">
         <v>100000</v>
       </c>
       <c r="U160" s="16">
         <f t="shared" si="38"/>
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="V160" s="4"/>
       <c r="W160" s="4"/>
       <c r="X160" s="4"/>
       <c r="Y160" s="4"/>
     </row>
+    <row r="161" spans="2:25" ht="16.5" customHeight="1">
+      <c r="B161" s="65">
+        <v>46094</v>
+      </c>
+      <c r="C161" s="62" t="s">
+        <v>16</v>
+      </c>
+      <c r="D161" s="51"/>
+      <c r="E161" s="59" t="s">
+        <v>102</v>
+      </c>
+      <c r="F161" s="5">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="G161" s="73"/>
+      <c r="H161" s="74"/>
+      <c r="I161" s="34"/>
+      <c r="J161" s="6" t="str">
+        <f t="shared" ref="J161:J184" si="39">IFERROR(S161/I161,"")</f>
+        <v/>
+      </c>
+      <c r="K161" s="38"/>
+      <c r="L161" s="38"/>
+      <c r="M161" s="38"/>
+      <c r="N161" s="38"/>
+      <c r="O161" s="38"/>
+      <c r="P161" s="38"/>
+      <c r="Q161" s="38"/>
+      <c r="R161" s="38"/>
+      <c r="S161" s="7">
+        <f>SUM(K161:R161)</f>
+        <v>0</v>
+      </c>
+      <c r="T161" s="7">
+        <v>100000</v>
+      </c>
+      <c r="U161" s="7">
+        <f>T161*S161</f>
+        <v>0</v>
+      </c>
+      <c r="V161" s="4"/>
+      <c r="W161" s="4"/>
+      <c r="X161" s="4"/>
+      <c r="Y161" s="4"/>
+    </row>
+    <row r="162" spans="2:25" ht="18.75">
+      <c r="B162" s="65"/>
+      <c r="C162" s="63"/>
+      <c r="D162" s="52"/>
+      <c r="E162" s="60"/>
+      <c r="F162" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="G162" s="78"/>
+      <c r="H162" s="79"/>
+      <c r="I162" s="35"/>
+      <c r="J162" s="9" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="K162" s="39"/>
+      <c r="L162" s="39"/>
+      <c r="M162" s="39"/>
+      <c r="N162" s="39"/>
+      <c r="O162" s="39"/>
+      <c r="P162" s="39"/>
+      <c r="Q162" s="39"/>
+      <c r="R162" s="39"/>
+      <c r="S162" s="10">
+        <f t="shared" ref="S162:S172" si="40">SUM(K162:R162)</f>
+        <v>0</v>
+      </c>
+      <c r="T162" s="10">
+        <v>100000</v>
+      </c>
+      <c r="U162" s="10">
+        <f t="shared" ref="U162:U163" si="41">T162*S162</f>
+        <v>0</v>
+      </c>
+      <c r="V162" s="4"/>
+      <c r="W162" s="4"/>
+      <c r="X162" s="4"/>
+      <c r="Y162" s="4"/>
+    </row>
+    <row r="163" spans="2:25" ht="18.75">
+      <c r="B163" s="65"/>
+      <c r="C163" s="63"/>
+      <c r="D163" s="52"/>
+      <c r="E163" s="60"/>
+      <c r="F163" s="8">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="G163" s="78"/>
+      <c r="H163" s="79"/>
+      <c r="I163" s="35"/>
+      <c r="J163" s="9" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="K163" s="39"/>
+      <c r="L163" s="39"/>
+      <c r="M163" s="39"/>
+      <c r="N163" s="39"/>
+      <c r="O163" s="39"/>
+      <c r="P163" s="39"/>
+      <c r="Q163" s="39"/>
+      <c r="R163" s="39"/>
+      <c r="S163" s="10">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="T163" s="10">
+        <v>100000</v>
+      </c>
+      <c r="U163" s="10">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="V163" s="4"/>
+      <c r="W163" s="4"/>
+      <c r="X163" s="4"/>
+      <c r="Y163" s="4"/>
+    </row>
+    <row r="164" spans="2:25" ht="18.75">
+      <c r="B164" s="65"/>
+      <c r="C164" s="63"/>
+      <c r="D164" s="52"/>
+      <c r="E164" s="60"/>
+      <c r="F164" s="8">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="G164" s="78"/>
+      <c r="H164" s="79"/>
+      <c r="I164" s="35"/>
+      <c r="J164" s="9" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="K164" s="39"/>
+      <c r="L164" s="39"/>
+      <c r="M164" s="39"/>
+      <c r="N164" s="39"/>
+      <c r="O164" s="39"/>
+      <c r="P164" s="39"/>
+      <c r="Q164" s="39"/>
+      <c r="R164" s="39"/>
+      <c r="S164" s="10">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="T164" s="10">
+        <v>100000</v>
+      </c>
+      <c r="U164" s="10">
+        <f>T164*S164</f>
+        <v>0</v>
+      </c>
+      <c r="V164" s="4"/>
+      <c r="W164" s="4"/>
+      <c r="X164" s="4"/>
+      <c r="Y164" s="4"/>
+    </row>
+    <row r="165" spans="2:25" ht="18.75">
+      <c r="B165" s="65"/>
+      <c r="C165" s="63"/>
+      <c r="D165" s="52"/>
+      <c r="E165" s="60"/>
+      <c r="F165" s="8">
+        <v>0.75</v>
+      </c>
+      <c r="G165" s="78"/>
+      <c r="H165" s="79"/>
+      <c r="I165" s="35"/>
+      <c r="J165" s="9" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="K165" s="39"/>
+      <c r="L165" s="39"/>
+      <c r="M165" s="39"/>
+      <c r="N165" s="39"/>
+      <c r="O165" s="39"/>
+      <c r="P165" s="39"/>
+      <c r="Q165" s="39"/>
+      <c r="R165" s="39"/>
+      <c r="S165" s="10">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="T165" s="10">
+        <v>100000</v>
+      </c>
+      <c r="U165" s="10">
+        <f t="shared" ref="U165:U172" si="42">T165*S165</f>
+        <v>0</v>
+      </c>
+      <c r="V165" s="4"/>
+      <c r="W165" s="4"/>
+      <c r="X165" s="11"/>
+      <c r="Y165" s="4"/>
+    </row>
+    <row r="166" spans="2:25" ht="18.75">
+      <c r="B166" s="65"/>
+      <c r="C166" s="63"/>
+      <c r="D166" s="53"/>
+      <c r="E166" s="61"/>
+      <c r="F166" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="G166" s="78"/>
+      <c r="H166" s="79"/>
+      <c r="I166" s="36"/>
+      <c r="J166" s="9" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="K166" s="41"/>
+      <c r="L166" s="41"/>
+      <c r="M166" s="39"/>
+      <c r="N166" s="41"/>
+      <c r="O166" s="41"/>
+      <c r="P166" s="41"/>
+      <c r="Q166" s="41"/>
+      <c r="R166" s="41"/>
+      <c r="S166" s="13">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="T166" s="13">
+        <v>100000</v>
+      </c>
+      <c r="U166" s="13">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="V166" s="4"/>
+      <c r="Y166" s="4"/>
+    </row>
+    <row r="167" spans="2:25" ht="18.75">
+      <c r="B167" s="65"/>
+      <c r="C167" s="63"/>
+      <c r="D167" s="51"/>
+      <c r="E167" s="59" t="s">
+        <v>103</v>
+      </c>
+      <c r="F167" s="5">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="G167" s="73"/>
+      <c r="H167" s="74"/>
+      <c r="I167" s="34"/>
+      <c r="J167" s="6" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="K167" s="38"/>
+      <c r="L167" s="38"/>
+      <c r="M167" s="38"/>
+      <c r="N167" s="38"/>
+      <c r="O167" s="38"/>
+      <c r="P167" s="38"/>
+      <c r="Q167" s="38"/>
+      <c r="R167" s="38"/>
+      <c r="S167" s="7">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="T167" s="7">
+        <v>100000</v>
+      </c>
+      <c r="U167" s="7">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="V167" s="4"/>
+      <c r="Y167" s="4"/>
+    </row>
+    <row r="168" spans="2:25" ht="18.75">
+      <c r="B168" s="65"/>
+      <c r="C168" s="63"/>
+      <c r="D168" s="52"/>
+      <c r="E168" s="60"/>
+      <c r="F168" s="8">
+        <v>1</v>
+      </c>
+      <c r="G168" s="78"/>
+      <c r="H168" s="79"/>
+      <c r="I168" s="35"/>
+      <c r="J168" s="9" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="K168" s="39"/>
+      <c r="L168" s="39"/>
+      <c r="M168" s="39"/>
+      <c r="N168" s="39"/>
+      <c r="O168" s="39"/>
+      <c r="P168" s="39"/>
+      <c r="Q168" s="39"/>
+      <c r="R168" s="39"/>
+      <c r="S168" s="10">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="T168" s="10">
+        <v>100000</v>
+      </c>
+      <c r="U168" s="10">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="V168" s="4"/>
+      <c r="Y168" s="4"/>
+    </row>
+    <row r="169" spans="2:25" ht="18.75">
+      <c r="B169" s="65"/>
+      <c r="C169" s="63"/>
+      <c r="D169" s="52"/>
+      <c r="E169" s="60"/>
+      <c r="F169" s="8">
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="G169" s="78"/>
+      <c r="H169" s="79"/>
+      <c r="I169" s="35"/>
+      <c r="J169" s="9" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="K169" s="39"/>
+      <c r="L169" s="39"/>
+      <c r="M169" s="39"/>
+      <c r="N169" s="39"/>
+      <c r="O169" s="39"/>
+      <c r="P169" s="39"/>
+      <c r="Q169" s="39"/>
+      <c r="R169" s="39"/>
+      <c r="S169" s="10">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="T169" s="10">
+        <v>100000</v>
+      </c>
+      <c r="U169" s="10">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="V169" s="4"/>
+      <c r="Y169" s="4"/>
+    </row>
+    <row r="170" spans="2:25" ht="18.75">
+      <c r="B170" s="65"/>
+      <c r="C170" s="63"/>
+      <c r="D170" s="52"/>
+      <c r="E170" s="60"/>
+      <c r="F170" s="8">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="G170" s="78"/>
+      <c r="H170" s="79"/>
+      <c r="I170" s="35"/>
+      <c r="J170" s="9" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="K170" s="39"/>
+      <c r="L170" s="39"/>
+      <c r="M170" s="39"/>
+      <c r="N170" s="39"/>
+      <c r="O170" s="39"/>
+      <c r="P170" s="39"/>
+      <c r="Q170" s="39"/>
+      <c r="R170" s="39"/>
+      <c r="S170" s="10">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="T170" s="10">
+        <v>100000</v>
+      </c>
+      <c r="U170" s="10">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="V170" s="4"/>
+      <c r="W170" s="4"/>
+      <c r="X170" s="4"/>
+      <c r="Y170" s="4"/>
+    </row>
+    <row r="171" spans="2:25" ht="18.75">
+      <c r="B171" s="65"/>
+      <c r="C171" s="63"/>
+      <c r="D171" s="52"/>
+      <c r="E171" s="60"/>
+      <c r="F171" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="G171" s="78"/>
+      <c r="H171" s="79"/>
+      <c r="I171" s="35"/>
+      <c r="J171" s="9" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="K171" s="39"/>
+      <c r="L171" s="39"/>
+      <c r="M171" s="39"/>
+      <c r="N171" s="39"/>
+      <c r="O171" s="39"/>
+      <c r="P171" s="39"/>
+      <c r="Q171" s="39"/>
+      <c r="R171" s="39"/>
+      <c r="S171" s="10">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="T171" s="10">
+        <v>100000</v>
+      </c>
+      <c r="U171" s="10">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="V171" s="4"/>
+      <c r="Y171" s="4"/>
+    </row>
+    <row r="172" spans="2:25" ht="18.75">
+      <c r="B172" s="65"/>
+      <c r="C172" s="64"/>
+      <c r="D172" s="53"/>
+      <c r="E172" s="91"/>
+      <c r="F172" s="14">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="G172" s="78"/>
+      <c r="H172" s="79"/>
+      <c r="I172" s="37"/>
+      <c r="J172" s="15" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="K172" s="40"/>
+      <c r="L172" s="40"/>
+      <c r="M172" s="40"/>
+      <c r="N172" s="40"/>
+      <c r="O172" s="40"/>
+      <c r="P172" s="40"/>
+      <c r="Q172" s="40"/>
+      <c r="R172" s="40"/>
+      <c r="S172" s="16">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="T172" s="16">
+        <v>100000</v>
+      </c>
+      <c r="U172" s="16">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="V172" s="4"/>
+      <c r="W172" s="4"/>
+      <c r="X172" s="4"/>
+      <c r="Y172" s="4"/>
+    </row>
+    <row r="173" spans="2:25" ht="16.5" customHeight="1">
+      <c r="B173" s="65">
+        <v>46095</v>
+      </c>
+      <c r="C173" s="62" t="s">
+        <v>16</v>
+      </c>
+      <c r="D173" s="51"/>
+      <c r="E173" s="59" t="s">
+        <v>102</v>
+      </c>
+      <c r="F173" s="5">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="G173" s="73"/>
+      <c r="H173" s="74"/>
+      <c r="I173" s="34"/>
+      <c r="J173" s="6" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="K173" s="38"/>
+      <c r="L173" s="38"/>
+      <c r="M173" s="38"/>
+      <c r="N173" s="38"/>
+      <c r="O173" s="38"/>
+      <c r="P173" s="38"/>
+      <c r="Q173" s="38"/>
+      <c r="R173" s="38"/>
+      <c r="S173" s="7">
+        <f>SUM(K173:R173)</f>
+        <v>0</v>
+      </c>
+      <c r="T173" s="7">
+        <v>100000</v>
+      </c>
+      <c r="U173" s="7">
+        <f>T173*S173</f>
+        <v>0</v>
+      </c>
+      <c r="V173" s="4"/>
+      <c r="W173" s="4"/>
+      <c r="X173" s="4"/>
+      <c r="Y173" s="4"/>
+    </row>
+    <row r="174" spans="2:25" ht="18.75">
+      <c r="B174" s="65"/>
+      <c r="C174" s="63"/>
+      <c r="D174" s="52"/>
+      <c r="E174" s="60"/>
+      <c r="F174" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="G174" s="78"/>
+      <c r="H174" s="79"/>
+      <c r="I174" s="35"/>
+      <c r="J174" s="9" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="K174" s="39"/>
+      <c r="L174" s="39"/>
+      <c r="M174" s="39"/>
+      <c r="N174" s="39"/>
+      <c r="O174" s="39"/>
+      <c r="P174" s="39"/>
+      <c r="Q174" s="39"/>
+      <c r="R174" s="39"/>
+      <c r="S174" s="10">
+        <f t="shared" ref="S174:S184" si="43">SUM(K174:R174)</f>
+        <v>0</v>
+      </c>
+      <c r="T174" s="10">
+        <v>100000</v>
+      </c>
+      <c r="U174" s="10">
+        <f t="shared" ref="U174:U175" si="44">T174*S174</f>
+        <v>0</v>
+      </c>
+      <c r="V174" s="4"/>
+      <c r="W174" s="4"/>
+      <c r="X174" s="4"/>
+      <c r="Y174" s="4"/>
+    </row>
+    <row r="175" spans="2:25" ht="18.75">
+      <c r="B175" s="65"/>
+      <c r="C175" s="63"/>
+      <c r="D175" s="52"/>
+      <c r="E175" s="60"/>
+      <c r="F175" s="8">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="G175" s="78"/>
+      <c r="H175" s="79"/>
+      <c r="I175" s="35"/>
+      <c r="J175" s="9" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="K175" s="39"/>
+      <c r="L175" s="39"/>
+      <c r="M175" s="39"/>
+      <c r="N175" s="39"/>
+      <c r="O175" s="39"/>
+      <c r="P175" s="39"/>
+      <c r="Q175" s="39"/>
+      <c r="R175" s="39"/>
+      <c r="S175" s="10">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="T175" s="10">
+        <v>100000</v>
+      </c>
+      <c r="U175" s="10">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="V175" s="4"/>
+      <c r="W175" s="4"/>
+      <c r="X175" s="4"/>
+      <c r="Y175" s="4"/>
+    </row>
+    <row r="176" spans="2:25" ht="18.75">
+      <c r="B176" s="65"/>
+      <c r="C176" s="63"/>
+      <c r="D176" s="52"/>
+      <c r="E176" s="60"/>
+      <c r="F176" s="8">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="G176" s="78"/>
+      <c r="H176" s="79"/>
+      <c r="I176" s="35"/>
+      <c r="J176" s="9" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="K176" s="39"/>
+      <c r="L176" s="39"/>
+      <c r="M176" s="39"/>
+      <c r="N176" s="39"/>
+      <c r="O176" s="39"/>
+      <c r="P176" s="39"/>
+      <c r="Q176" s="39"/>
+      <c r="R176" s="39"/>
+      <c r="S176" s="10">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="T176" s="10">
+        <v>100000</v>
+      </c>
+      <c r="U176" s="10">
+        <f>T176*S176</f>
+        <v>0</v>
+      </c>
+      <c r="V176" s="4"/>
+      <c r="W176" s="4"/>
+      <c r="X176" s="4"/>
+      <c r="Y176" s="4"/>
+    </row>
+    <row r="177" spans="2:25" ht="18.75">
+      <c r="B177" s="65"/>
+      <c r="C177" s="63"/>
+      <c r="D177" s="52"/>
+      <c r="E177" s="60"/>
+      <c r="F177" s="8">
+        <v>0.75</v>
+      </c>
+      <c r="G177" s="78"/>
+      <c r="H177" s="79"/>
+      <c r="I177" s="35"/>
+      <c r="J177" s="9" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="K177" s="39"/>
+      <c r="L177" s="39"/>
+      <c r="M177" s="39"/>
+      <c r="N177" s="39"/>
+      <c r="O177" s="39"/>
+      <c r="P177" s="39"/>
+      <c r="Q177" s="39"/>
+      <c r="R177" s="39"/>
+      <c r="S177" s="10">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="T177" s="10">
+        <v>100000</v>
+      </c>
+      <c r="U177" s="10">
+        <f t="shared" ref="U177:U184" si="45">T177*S177</f>
+        <v>0</v>
+      </c>
+      <c r="V177" s="4"/>
+      <c r="W177" s="4"/>
+      <c r="X177" s="11"/>
+      <c r="Y177" s="4"/>
+    </row>
+    <row r="178" spans="2:25" ht="18.75">
+      <c r="B178" s="65"/>
+      <c r="C178" s="63"/>
+      <c r="D178" s="53"/>
+      <c r="E178" s="61"/>
+      <c r="F178" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="G178" s="78"/>
+      <c r="H178" s="79"/>
+      <c r="I178" s="36"/>
+      <c r="J178" s="9" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="K178" s="41"/>
+      <c r="L178" s="41"/>
+      <c r="M178" s="39"/>
+      <c r="N178" s="41"/>
+      <c r="O178" s="41"/>
+      <c r="P178" s="41"/>
+      <c r="Q178" s="41"/>
+      <c r="R178" s="41"/>
+      <c r="S178" s="13">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="T178" s="13">
+        <v>100000</v>
+      </c>
+      <c r="U178" s="13">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="V178" s="4"/>
+      <c r="Y178" s="4"/>
+    </row>
+    <row r="179" spans="2:25" ht="18.75">
+      <c r="B179" s="65"/>
+      <c r="C179" s="63"/>
+      <c r="D179" s="51"/>
+      <c r="E179" s="59" t="s">
+        <v>103</v>
+      </c>
+      <c r="F179" s="5">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="G179" s="73"/>
+      <c r="H179" s="74"/>
+      <c r="I179" s="34"/>
+      <c r="J179" s="6" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="K179" s="38"/>
+      <c r="L179" s="38"/>
+      <c r="M179" s="38"/>
+      <c r="N179" s="38"/>
+      <c r="O179" s="38"/>
+      <c r="P179" s="38"/>
+      <c r="Q179" s="38"/>
+      <c r="R179" s="38"/>
+      <c r="S179" s="7">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="T179" s="7">
+        <v>100000</v>
+      </c>
+      <c r="U179" s="7">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="V179" s="4"/>
+      <c r="Y179" s="4"/>
+    </row>
+    <row r="180" spans="2:25" ht="18.75">
+      <c r="B180" s="65"/>
+      <c r="C180" s="63"/>
+      <c r="D180" s="52"/>
+      <c r="E180" s="60"/>
+      <c r="F180" s="8">
+        <v>1</v>
+      </c>
+      <c r="G180" s="78"/>
+      <c r="H180" s="79"/>
+      <c r="I180" s="35"/>
+      <c r="J180" s="9" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="K180" s="39"/>
+      <c r="L180" s="39"/>
+      <c r="M180" s="39"/>
+      <c r="N180" s="39"/>
+      <c r="O180" s="39"/>
+      <c r="P180" s="39"/>
+      <c r="Q180" s="39"/>
+      <c r="R180" s="39"/>
+      <c r="S180" s="10">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="T180" s="10">
+        <v>100000</v>
+      </c>
+      <c r="U180" s="10">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="V180" s="4"/>
+      <c r="Y180" s="4"/>
+    </row>
+    <row r="181" spans="2:25" ht="18.75">
+      <c r="B181" s="65"/>
+      <c r="C181" s="63"/>
+      <c r="D181" s="52"/>
+      <c r="E181" s="60"/>
+      <c r="F181" s="8">
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="G181" s="78"/>
+      <c r="H181" s="79"/>
+      <c r="I181" s="35"/>
+      <c r="J181" s="9" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="K181" s="39"/>
+      <c r="L181" s="39"/>
+      <c r="M181" s="39"/>
+      <c r="N181" s="39"/>
+      <c r="O181" s="39"/>
+      <c r="P181" s="39"/>
+      <c r="Q181" s="39"/>
+      <c r="R181" s="39"/>
+      <c r="S181" s="10">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="T181" s="10">
+        <v>100000</v>
+      </c>
+      <c r="U181" s="10">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="V181" s="4"/>
+      <c r="Y181" s="4"/>
+    </row>
+    <row r="182" spans="2:25" ht="18.75">
+      <c r="B182" s="65"/>
+      <c r="C182" s="63"/>
+      <c r="D182" s="52"/>
+      <c r="E182" s="60"/>
+      <c r="F182" s="8">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="G182" s="78"/>
+      <c r="H182" s="79"/>
+      <c r="I182" s="35"/>
+      <c r="J182" s="9" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="K182" s="39"/>
+      <c r="L182" s="39"/>
+      <c r="M182" s="39"/>
+      <c r="N182" s="39"/>
+      <c r="O182" s="39"/>
+      <c r="P182" s="39"/>
+      <c r="Q182" s="39"/>
+      <c r="R182" s="39"/>
+      <c r="S182" s="10">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="T182" s="10">
+        <v>100000</v>
+      </c>
+      <c r="U182" s="10">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="V182" s="4"/>
+      <c r="W182" s="4"/>
+      <c r="X182" s="4"/>
+      <c r="Y182" s="4"/>
+    </row>
+    <row r="183" spans="2:25" ht="18.75">
+      <c r="B183" s="65"/>
+      <c r="C183" s="63"/>
+      <c r="D183" s="52"/>
+      <c r="E183" s="60"/>
+      <c r="F183" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="G183" s="78"/>
+      <c r="H183" s="79"/>
+      <c r="I183" s="35"/>
+      <c r="J183" s="9" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="K183" s="39"/>
+      <c r="L183" s="39"/>
+      <c r="M183" s="39"/>
+      <c r="N183" s="39"/>
+      <c r="O183" s="39"/>
+      <c r="P183" s="39"/>
+      <c r="Q183" s="39"/>
+      <c r="R183" s="39"/>
+      <c r="S183" s="10">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="T183" s="10">
+        <v>100000</v>
+      </c>
+      <c r="U183" s="10">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="V183" s="4"/>
+      <c r="Y183" s="4"/>
+    </row>
+    <row r="184" spans="2:25" ht="18.75">
+      <c r="B184" s="65"/>
+      <c r="C184" s="64"/>
+      <c r="D184" s="53"/>
+      <c r="E184" s="91"/>
+      <c r="F184" s="14">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="G184" s="78"/>
+      <c r="H184" s="79"/>
+      <c r="I184" s="37"/>
+      <c r="J184" s="15" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="K184" s="40"/>
+      <c r="L184" s="40"/>
+      <c r="M184" s="40"/>
+      <c r="N184" s="40"/>
+      <c r="O184" s="40"/>
+      <c r="P184" s="40"/>
+      <c r="Q184" s="40"/>
+      <c r="R184" s="40"/>
+      <c r="S184" s="16">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="T184" s="16">
+        <v>100000</v>
+      </c>
+      <c r="U184" s="16">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="V184" s="4"/>
+      <c r="W184" s="4"/>
+      <c r="X184" s="4"/>
+      <c r="Y184" s="4"/>
+    </row>
   </sheetData>
-  <mergeCells count="210">
+  <mergeCells count="242">
+    <mergeCell ref="B173:B184"/>
+    <mergeCell ref="C173:C184"/>
+    <mergeCell ref="E173:E178"/>
+    <mergeCell ref="G173:H173"/>
+    <mergeCell ref="G174:H174"/>
+    <mergeCell ref="G175:H175"/>
+    <mergeCell ref="G176:H176"/>
+    <mergeCell ref="G177:H177"/>
+    <mergeCell ref="G178:H178"/>
+    <mergeCell ref="E179:E184"/>
+    <mergeCell ref="G179:H179"/>
+    <mergeCell ref="G180:H180"/>
+    <mergeCell ref="G181:H181"/>
+    <mergeCell ref="G182:H182"/>
+    <mergeCell ref="G183:H183"/>
+    <mergeCell ref="G184:H184"/>
+    <mergeCell ref="B161:B172"/>
+    <mergeCell ref="C161:C172"/>
+    <mergeCell ref="E161:E166"/>
+    <mergeCell ref="G161:H161"/>
+    <mergeCell ref="G162:H162"/>
+    <mergeCell ref="G163:H163"/>
+    <mergeCell ref="G164:H164"/>
+    <mergeCell ref="G165:H165"/>
+    <mergeCell ref="G166:H166"/>
+    <mergeCell ref="E167:E172"/>
+    <mergeCell ref="G167:H167"/>
+    <mergeCell ref="G168:H168"/>
+    <mergeCell ref="G169:H169"/>
+    <mergeCell ref="G170:H170"/>
+    <mergeCell ref="G171:H171"/>
+    <mergeCell ref="G172:H172"/>
     <mergeCell ref="B149:B160"/>
     <mergeCell ref="C149:C160"/>
     <mergeCell ref="E149:E154"/>
@@ -23285,22 +26628,22 @@
     <mergeCell ref="T15:U15"/>
   </mergeCells>
   <dataValidations count="6">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E17 E23 E29 E41 E53 E65 E77 E89 E101 E113 E125 E137 E35 E47 E59 E71 E83 E95 E107 E119 E131 E143 E149 E155" xr:uid="{3F97067F-1D22-46C9-8EB2-36D4E853411F}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E17 E23 E29 E41 E53 E65 E77 E89 E101 E113 E125 E137 E35 E47 E59 E71 E83 E95 E107 E119 E131 E143 E149 E155 E161 E167 E173 E179" xr:uid="{3F97067F-1D22-46C9-8EB2-36D4E853411F}">
       <formula1>$X$22:$X$23</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C125 C17 C29 C41 C53 C65 C77 C89 C101 C113 C137 C149" xr:uid="{6FBB2D4D-D80C-4833-87A8-7A0E96CAD28D}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C125 C17 C29 C41 C53 C65 C77 C89 C101 C113 C137 C149 C161 C173" xr:uid="{6FBB2D4D-D80C-4833-87A8-7A0E96CAD28D}">
       <formula1>$X$17:$X$21</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C6" xr:uid="{3DB528DA-384D-4E01-A775-48E30DF63DB2}">
       <formula1>$X$2:$X$7</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G17:G22 G29:G34 G41:G46 G53:G58 G65:G70 G137:G142 G77:G82 G101:G106 G113:G118 G89:G94 G125:G130 G149:G154" xr:uid="{F42A6AB3-C955-4CC2-BF5D-289F6217FA8D}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G17:G22 G29:G34 G41:G46 G53:G58 G65:G70 G137:G142 G77:G82 G101:G106 G113:G118 G89:G94 G125:G130 G173:G178 G161:G166 G149:G154" xr:uid="{F42A6AB3-C955-4CC2-BF5D-289F6217FA8D}">
       <formula1>$C$11:$S$11</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D17:D160" xr:uid="{9AC609EF-5D24-477A-8FC3-B2A5F74CC194}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D17:D184" xr:uid="{9AC609EF-5D24-477A-8FC3-B2A5F74CC194}">
       <formula1>$Z$21:$Z$61</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G23:H28 G35:H40 G47:H52 G59:H64 G71:H76 G83:H88 G143:H148 G107:H112 G119:H124 G131:H136 G95:H100 G155:H160" xr:uid="{71EFA27C-F2C6-4CBC-A44C-3C0C036C5150}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G23:H28 G35:H40 G47:H52 G59:H64 G71:H76 G83:H88 G143:H148 G107:H112 G119:H124 G131:H136 G95:H100 G179:H184 G167:H172 G155:H160" xr:uid="{71EFA27C-F2C6-4CBC-A44C-3C0C036C5150}">
       <formula1>$C$12:$S$12</formula1>
     </dataValidation>
   </dataValidations>
@@ -23412,7 +26755,7 @@
     </row>
     <row r="4" spans="2:47" ht="22.5">
       <c r="B4" s="58" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C4" s="58"/>
       <c r="D4" s="58"/>
@@ -23512,10 +26855,10 @@
         <v>12</v>
       </c>
       <c r="C6" s="42" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="D6" s="89" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E6" s="87"/>
       <c r="F6" s="87"/>
@@ -23525,10 +26868,10 @@
       <c r="J6" s="87"/>
       <c r="K6" s="47"/>
       <c r="L6" s="48" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="M6" s="86" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="N6" s="87"/>
       <c r="O6" s="87"/>
@@ -23570,7 +26913,7 @@
     <row r="7" spans="2:47" ht="24.95" customHeight="1">
       <c r="C7" s="3"/>
       <c r="D7" s="88" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E7" s="88"/>
       <c r="F7" s="88"/>
@@ -23581,7 +26924,7 @@
       <c r="K7" s="88"/>
       <c r="L7" s="3"/>
       <c r="M7" s="88" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N7" s="88"/>
       <c r="O7" s="88"/>
@@ -23619,7 +26962,7 @@
     </row>
     <row r="8" spans="2:47" ht="22.5">
       <c r="B8" s="57" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C8" s="58"/>
       <c r="D8" s="58"/>
@@ -23787,10 +27130,10 @@
         <v>81</v>
       </c>
       <c r="K11" s="31" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="L11" s="31" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="M11" s="31"/>
       <c r="N11" s="31"/>
@@ -23846,7 +27189,7 @@
     </row>
     <row r="13" spans="2:47" ht="54.6" customHeight="1">
       <c r="B13" s="90" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C13" s="90"/>
       <c r="D13" s="90"/>
@@ -23913,7 +27256,7 @@
         <v>73</v>
       </c>
       <c r="S14" s="56" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="T14" s="56"/>
       <c r="U14" s="56"/>
@@ -24016,7 +27359,7 @@
       </c>
       <c r="D17" s="51"/>
       <c r="E17" s="59" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F17" s="5">
         <v>0.41666666666666669</v>
@@ -24258,7 +27601,7 @@
       </c>
       <c r="V22" s="4"/>
       <c r="X22" s="54" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="Z22" s="44" t="s">
         <v>46</v>
@@ -24269,7 +27612,7 @@
       <c r="C23" s="63"/>
       <c r="D23" s="51"/>
       <c r="E23" s="59" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F23" s="5">
         <v>0.91666666666666663</v>
@@ -24302,7 +27645,7 @@
       </c>
       <c r="V23" s="4"/>
       <c r="X23" s="54" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="Z23" s="44" t="s">
         <v>45</v>
@@ -24520,7 +27863,7 @@
       </c>
       <c r="D29" s="51"/>
       <c r="E29" s="59" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F29" s="5">
         <v>0.41666666666666669</v>
@@ -24772,7 +28115,7 @@
       <c r="C35" s="63"/>
       <c r="D35" s="51"/>
       <c r="E35" s="59" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F35" s="5">
         <v>0.91666666666666663</v>
@@ -25024,7 +28367,7 @@
         <v>42</v>
       </c>
       <c r="E41" s="59" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F41" s="5">
         <v>0.41666666666666669</v>
@@ -25288,7 +28631,7 @@
       <c r="C47" s="63"/>
       <c r="D47" s="51"/>
       <c r="E47" s="59" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F47" s="5">
         <v>0.91666666666666663</v>
@@ -25528,7 +28871,7 @@
         <v>42</v>
       </c>
       <c r="E53" s="59" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F53" s="5">
         <v>0.41666666666666669</v>
@@ -25818,7 +29161,7 @@
         <v>42</v>
       </c>
       <c r="E59" s="59" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F59" s="5">
         <v>0.91666666666666663</v>
@@ -26103,13 +29446,13 @@
         <v>43</v>
       </c>
       <c r="E65" s="59" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F65" s="5">
         <v>0.41666666666666669</v>
       </c>
       <c r="G65" s="73" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H65" s="74"/>
       <c r="I65" s="34"/>
@@ -26154,7 +29497,7 @@
         <v>0.5</v>
       </c>
       <c r="G66" s="78" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H66" s="79"/>
       <c r="I66" s="35"/>
@@ -26197,7 +29540,7 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="G67" s="78" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H67" s="79"/>
       <c r="I67" s="35">
@@ -26244,7 +29587,7 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="G68" s="78" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H68" s="79"/>
       <c r="I68" s="35">
@@ -26291,7 +29634,7 @@
         <v>0.75</v>
       </c>
       <c r="G69" s="78" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H69" s="79"/>
       <c r="I69" s="35">
@@ -26338,7 +29681,7 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="G70" s="78" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H70" s="79"/>
       <c r="I70" s="36"/>
@@ -26375,7 +29718,7 @@
         <v>43</v>
       </c>
       <c r="E71" s="59" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F71" s="5">
         <v>0.91666666666666663</v>
@@ -26655,13 +29998,13 @@
         <v>43</v>
       </c>
       <c r="E77" s="59" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F77" s="5">
         <v>0.41666666666666669</v>
       </c>
       <c r="G77" s="73" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H77" s="74"/>
       <c r="I77" s="34">
@@ -26708,7 +30051,7 @@
         <v>0.5</v>
       </c>
       <c r="G78" s="78" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H78" s="79"/>
       <c r="I78" s="35">
@@ -26755,7 +30098,7 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="G79" s="78" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H79" s="79"/>
       <c r="I79" s="35">
@@ -26800,7 +30143,7 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="G80" s="78" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H80" s="79"/>
       <c r="I80" s="35">
@@ -26845,7 +30188,7 @@
         <v>0.75</v>
       </c>
       <c r="G81" s="78" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H81" s="79"/>
       <c r="I81" s="35">
@@ -26890,7 +30233,7 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="G82" s="78" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H82" s="79"/>
       <c r="I82" s="36">
@@ -26929,7 +30272,7 @@
         <v>43</v>
       </c>
       <c r="E83" s="59" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F83" s="5">
         <v>0.91666666666666663</v>
@@ -27203,7 +30546,7 @@
         <v>43</v>
       </c>
       <c r="E89" s="59" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F89" s="5">
         <v>0.41666666666666669</v>
@@ -27477,7 +30820,7 @@
         <v>43</v>
       </c>
       <c r="E95" s="59" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F95" s="5">
         <v>0.91666666666666663</v>
@@ -27755,7 +31098,7 @@
         <v>43</v>
       </c>
       <c r="E101" s="59" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F101" s="5">
         <v>0.41666666666666669</v>
@@ -28025,7 +31368,7 @@
         <v>43</v>
       </c>
       <c r="E107" s="59" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F107" s="5">
         <v>0.91666666666666663</v>
@@ -28303,7 +31646,7 @@
         <v>43</v>
       </c>
       <c r="E113" s="59" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F113" s="5">
         <v>0.41666666666666669</v>
@@ -28571,7 +31914,7 @@
         <v>43</v>
       </c>
       <c r="E119" s="59" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F119" s="5">
         <v>0.91666666666666663</v>
@@ -28845,7 +32188,7 @@
         <v>43</v>
       </c>
       <c r="E125" s="59" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F125" s="5">
         <v>0.41666666666666669</v>
@@ -29123,7 +32466,7 @@
         <v>43</v>
       </c>
       <c r="E131" s="59" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F131" s="5">
         <v>0.91666666666666663</v>
@@ -29386,26 +32729,32 @@
       <c r="X136" s="4"/>
       <c r="Y136" s="4"/>
     </row>
-    <row r="137" spans="2:25" ht="16.5" customHeight="1">
+    <row r="137" spans="2:25" ht="39" customHeight="1">
       <c r="B137" s="65">
         <v>46092</v>
       </c>
       <c r="C137" s="62" t="s">
         <v>17</v>
       </c>
-      <c r="D137" s="51"/>
+      <c r="D137" s="51" t="s">
+        <v>43</v>
+      </c>
       <c r="E137" s="59" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F137" s="5">
         <v>0.41666666666666669</v>
       </c>
-      <c r="G137" s="73"/>
+      <c r="G137" s="73" t="s">
+        <v>79</v>
+      </c>
       <c r="H137" s="74"/>
-      <c r="I137" s="34"/>
-      <c r="J137" s="6" t="str">
+      <c r="I137" s="34">
+        <v>38</v>
+      </c>
+      <c r="J137" s="6">
         <f t="shared" ref="J137:J148" si="31">IFERROR(S137/I137,"")</f>
-        <v/>
+        <v>7.8947368421052627E-2</v>
       </c>
       <c r="K137" s="38"/>
       <c r="L137" s="38"/>
@@ -29413,18 +32762,22 @@
       <c r="N137" s="38"/>
       <c r="O137" s="38"/>
       <c r="P137" s="38"/>
-      <c r="Q137" s="38"/>
-      <c r="R137" s="38"/>
+      <c r="Q137" s="38">
+        <v>2</v>
+      </c>
+      <c r="R137" s="38">
+        <v>1</v>
+      </c>
       <c r="S137" s="7">
         <f>SUM(K137:R137)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T137" s="7">
         <v>100000</v>
       </c>
       <c r="U137" s="7">
         <f>T137*S137</f>
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="V137" s="4"/>
       <c r="W137" s="4"/>
@@ -29624,24 +32977,32 @@
       <c r="V142" s="4"/>
       <c r="Y142" s="4"/>
     </row>
-    <row r="143" spans="2:25" ht="18.75">
+    <row r="143" spans="2:25" ht="37.5">
       <c r="B143" s="65"/>
       <c r="C143" s="63"/>
-      <c r="D143" s="51"/>
+      <c r="D143" s="51" t="s">
+        <v>43</v>
+      </c>
       <c r="E143" s="59" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F143" s="5">
         <v>0.91666666666666663</v>
       </c>
-      <c r="G143" s="73"/>
+      <c r="G143" s="73" t="s">
+        <v>83</v>
+      </c>
       <c r="H143" s="74"/>
-      <c r="I143" s="34"/>
-      <c r="J143" s="6" t="str">
+      <c r="I143" s="34">
+        <v>53</v>
+      </c>
+      <c r="J143" s="6">
         <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="K143" s="38"/>
+        <v>1.8867924528301886E-2</v>
+      </c>
+      <c r="K143" s="38">
+        <v>1</v>
+      </c>
       <c r="L143" s="38"/>
       <c r="M143" s="38"/>
       <c r="N143" s="38"/>
@@ -29651,34 +33012,42 @@
       <c r="R143" s="38"/>
       <c r="S143" s="7">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T143" s="7">
         <v>100000</v>
       </c>
       <c r="U143" s="7">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="V143" s="4"/>
       <c r="Y143" s="4"/>
     </row>
-    <row r="144" spans="2:25" ht="18.75">
+    <row r="144" spans="2:25" ht="37.5">
       <c r="B144" s="65"/>
       <c r="C144" s="63"/>
-      <c r="D144" s="52"/>
+      <c r="D144" s="52" t="s">
+        <v>43</v>
+      </c>
       <c r="E144" s="60"/>
       <c r="F144" s="8">
         <v>1</v>
       </c>
-      <c r="G144" s="78"/>
+      <c r="G144" s="78" t="s">
+        <v>83</v>
+      </c>
       <c r="H144" s="79"/>
-      <c r="I144" s="35"/>
-      <c r="J144" s="9" t="str">
+      <c r="I144" s="35">
+        <v>53</v>
+      </c>
+      <c r="J144" s="9">
         <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="K144" s="39"/>
+        <v>1.8867924528301886E-2</v>
+      </c>
+      <c r="K144" s="39">
+        <v>1</v>
+      </c>
       <c r="L144" s="39"/>
       <c r="M144" s="39"/>
       <c r="N144" s="39"/>
@@ -29688,34 +33057,42 @@
       <c r="R144" s="39"/>
       <c r="S144" s="10">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T144" s="10">
         <v>100000</v>
       </c>
       <c r="U144" s="10">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="V144" s="4"/>
       <c r="Y144" s="4"/>
     </row>
-    <row r="145" spans="2:25" ht="18.75">
+    <row r="145" spans="2:25" ht="37.5">
       <c r="B145" s="65"/>
       <c r="C145" s="63"/>
-      <c r="D145" s="52"/>
+      <c r="D145" s="52" t="s">
+        <v>43</v>
+      </c>
       <c r="E145" s="60"/>
       <c r="F145" s="8">
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="G145" s="78"/>
+      <c r="G145" s="78" t="s">
+        <v>83</v>
+      </c>
       <c r="H145" s="79"/>
-      <c r="I145" s="35"/>
-      <c r="J145" s="9" t="str">
+      <c r="I145" s="35">
+        <v>53</v>
+      </c>
+      <c r="J145" s="9">
         <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="K145" s="39"/>
+        <v>1.8867924528301886E-2</v>
+      </c>
+      <c r="K145" s="39">
+        <v>1</v>
+      </c>
       <c r="L145" s="39"/>
       <c r="M145" s="39"/>
       <c r="N145" s="39"/>
@@ -29725,32 +33102,38 @@
       <c r="R145" s="39"/>
       <c r="S145" s="10">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T145" s="10">
         <v>100000</v>
       </c>
       <c r="U145" s="10">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="V145" s="4"/>
       <c r="Y145" s="4"/>
     </row>
-    <row r="146" spans="2:25" ht="18.75">
+    <row r="146" spans="2:25" ht="37.5">
       <c r="B146" s="65"/>
       <c r="C146" s="63"/>
-      <c r="D146" s="52"/>
+      <c r="D146" s="52" t="s">
+        <v>43</v>
+      </c>
       <c r="E146" s="60"/>
       <c r="F146" s="8">
         <v>0.16666666666666666</v>
       </c>
-      <c r="G146" s="78"/>
+      <c r="G146" s="78" t="s">
+        <v>83</v>
+      </c>
       <c r="H146" s="79"/>
-      <c r="I146" s="35"/>
-      <c r="J146" s="9" t="str">
+      <c r="I146" s="35">
+        <v>54</v>
+      </c>
+      <c r="J146" s="9">
         <f t="shared" si="31"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K146" s="39"/>
       <c r="L146" s="39"/>
@@ -29776,20 +33159,26 @@
       <c r="X146" s="4"/>
       <c r="Y146" s="4"/>
     </row>
-    <row r="147" spans="2:25" ht="18.75">
+    <row r="147" spans="2:25" ht="37.5">
       <c r="B147" s="65"/>
       <c r="C147" s="63"/>
-      <c r="D147" s="52"/>
+      <c r="D147" s="52" t="s">
+        <v>43</v>
+      </c>
       <c r="E147" s="60"/>
       <c r="F147" s="8">
         <v>0.25</v>
       </c>
-      <c r="G147" s="78"/>
+      <c r="G147" s="78" t="s">
+        <v>83</v>
+      </c>
       <c r="H147" s="79"/>
-      <c r="I147" s="35"/>
-      <c r="J147" s="9" t="str">
+      <c r="I147" s="35">
+        <v>54</v>
+      </c>
+      <c r="J147" s="9">
         <f t="shared" si="31"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K147" s="39"/>
       <c r="L147" s="39"/>
@@ -29813,20 +33202,26 @@
       <c r="V147" s="4"/>
       <c r="Y147" s="4"/>
     </row>
-    <row r="148" spans="2:25" ht="18.75">
+    <row r="148" spans="2:25" ht="37.5">
       <c r="B148" s="65"/>
       <c r="C148" s="64"/>
-      <c r="D148" s="53"/>
+      <c r="D148" s="53" t="s">
+        <v>43</v>
+      </c>
       <c r="E148" s="91"/>
       <c r="F148" s="14">
         <v>0.33333333333333331</v>
       </c>
-      <c r="G148" s="78"/>
+      <c r="G148" s="78" t="s">
+        <v>83</v>
+      </c>
       <c r="H148" s="79"/>
-      <c r="I148" s="37"/>
-      <c r="J148" s="15" t="str">
+      <c r="I148" s="37">
+        <v>56</v>
+      </c>
+      <c r="J148" s="15">
         <f t="shared" si="31"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K148" s="40"/>
       <c r="L148" s="40"/>
@@ -29861,7 +33256,7 @@
       </c>
       <c r="D149" s="51"/>
       <c r="E149" s="59" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F149" s="5">
         <v>0.41666666666666669</v>
@@ -30095,7 +33490,7 @@
       <c r="C155" s="63"/>
       <c r="D155" s="51"/>
       <c r="E155" s="59" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F155" s="5">
         <v>0.91666666666666663</v>
@@ -30548,7 +33943,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D17:D160" xr:uid="{7E874D98-D5E9-44FC-BBBE-1D6FB0116A76}">
       <formula1>$Z$21:$Z$61</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G23:H28 G35:H40 G47:H52 G59:H64 G71:H76 G143:H148 G83:H88 G107:H112 G119:H124 G95:H100 G131:H136 G155:H160" xr:uid="{DF8987A4-84F3-48A9-AA6D-BBB2D93082AD}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G23:H28 G35:H40 G47:H52 G59:H64 G71:H76 G155:H160 G83:H88 G107:H112 G119:H124 G95:H100 G131:H136 G143:H148" xr:uid="{DF8987A4-84F3-48A9-AA6D-BBB2D93082AD}">
       <formula1>$C$12:$S$12</formula1>
     </dataValidation>
   </dataValidations>
